--- a/AAII_Financials/Quarterly/TATYY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/TATYY_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,7 +17,7 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
@@ -761,25 +761,25 @@
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>1063200</v>
+        <v>1092800</v>
       </c>
       <c r="E8" s="3">
-        <v>1119000</v>
+        <v>1150100</v>
       </c>
       <c r="F8" s="3">
-        <v>1053300</v>
+        <v>1082600</v>
       </c>
       <c r="G8" s="3">
-        <v>892000</v>
+        <v>916800</v>
       </c>
       <c r="H8" s="3">
-        <v>813800</v>
+        <v>836500</v>
       </c>
       <c r="I8" s="3">
-        <v>767900</v>
+        <v>789300</v>
       </c>
       <c r="J8" s="3">
-        <v>734400</v>
+        <v>754900</v>
       </c>
       <c r="K8" s="3">
         <v>1781800</v>
@@ -1095,25 +1095,25 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>9900</v>
+        <v>10200</v>
       </c>
       <c r="E14" s="3">
-        <v>21100</v>
+        <v>21700</v>
       </c>
       <c r="F14" s="3">
-        <v>13600</v>
+        <v>14000</v>
       </c>
       <c r="G14" s="3">
-        <v>29800</v>
+        <v>30600</v>
       </c>
       <c r="H14" s="3">
-        <v>73200</v>
+        <v>75200</v>
       </c>
       <c r="I14" s="3">
-        <v>23600</v>
+        <v>24200</v>
       </c>
       <c r="J14" s="3">
-        <v>18600</v>
+        <v>19100</v>
       </c>
       <c r="K14" s="3" t="s">
         <v>5</v>
@@ -1160,22 +1160,22 @@
         <v>5</v>
       </c>
       <c r="E15" s="3">
-        <v>29800</v>
+        <v>30600</v>
       </c>
       <c r="F15" s="3">
-        <v>14900</v>
+        <v>15300</v>
       </c>
       <c r="G15" s="3">
-        <v>23600</v>
+        <v>24200</v>
       </c>
       <c r="H15" s="3">
-        <v>6200</v>
+        <v>6400</v>
       </c>
       <c r="I15" s="3">
-        <v>26100</v>
+        <v>26800</v>
       </c>
       <c r="J15" s="3">
-        <v>6200</v>
+        <v>6400</v>
       </c>
       <c r="K15" s="3" t="s">
         <v>5</v>
@@ -1240,25 +1240,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>910600</v>
+        <v>935900</v>
       </c>
       <c r="E17" s="3">
-        <v>1017300</v>
+        <v>1045600</v>
       </c>
       <c r="F17" s="3">
-        <v>911800</v>
+        <v>937200</v>
       </c>
       <c r="G17" s="3">
-        <v>849800</v>
+        <v>873400</v>
       </c>
       <c r="H17" s="3">
-        <v>772900</v>
+        <v>794400</v>
       </c>
       <c r="I17" s="3">
-        <v>712100</v>
+        <v>731900</v>
       </c>
       <c r="J17" s="3">
-        <v>646400</v>
+        <v>664300</v>
       </c>
       <c r="K17" s="3">
         <v>1617100</v>
@@ -1302,25 +1302,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>152600</v>
+        <v>156800</v>
       </c>
       <c r="E18" s="3">
-        <v>101700</v>
+        <v>104600</v>
       </c>
       <c r="F18" s="3">
-        <v>141400</v>
+        <v>145400</v>
       </c>
       <c r="G18" s="3">
-        <v>42200</v>
+        <v>43400</v>
       </c>
       <c r="H18" s="3">
-        <v>40900</v>
+        <v>42100</v>
       </c>
       <c r="I18" s="3">
-        <v>55800</v>
+        <v>57400</v>
       </c>
       <c r="J18" s="3">
-        <v>88100</v>
+        <v>90500</v>
       </c>
       <c r="K18" s="3">
         <v>164700</v>
@@ -1388,25 +1388,25 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>8700</v>
+        <v>8900</v>
       </c>
       <c r="E20" s="3">
-        <v>2500</v>
+        <v>2600</v>
       </c>
       <c r="F20" s="3">
-        <v>-57100</v>
+        <v>-58700</v>
       </c>
       <c r="G20" s="3">
-        <v>-16100</v>
+        <v>-16600</v>
       </c>
       <c r="H20" s="3">
-        <v>-14900</v>
+        <v>-15300</v>
       </c>
       <c r="I20" s="3">
-        <v>-16100</v>
+        <v>-16600</v>
       </c>
       <c r="J20" s="3">
-        <v>-16100</v>
+        <v>-16600</v>
       </c>
       <c r="K20" s="3">
         <v>2500</v>
@@ -1450,25 +1450,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>219600</v>
+        <v>225700</v>
       </c>
       <c r="E21" s="3">
-        <v>163800</v>
+        <v>168300</v>
       </c>
       <c r="F21" s="3">
-        <v>142700</v>
+        <v>146600</v>
       </c>
       <c r="G21" s="3">
-        <v>74400</v>
+        <v>76500</v>
       </c>
       <c r="H21" s="3">
-        <v>101700</v>
+        <v>104600</v>
       </c>
       <c r="I21" s="3">
-        <v>147600</v>
+        <v>151700</v>
       </c>
       <c r="J21" s="3">
-        <v>181100</v>
+        <v>186200</v>
       </c>
       <c r="K21" s="3">
         <v>262300</v>
@@ -1574,25 +1574,25 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>161300</v>
+        <v>165800</v>
       </c>
       <c r="E23" s="3">
-        <v>104200</v>
+        <v>107100</v>
       </c>
       <c r="F23" s="3">
-        <v>84400</v>
+        <v>86700</v>
       </c>
       <c r="G23" s="3">
-        <v>26100</v>
+        <v>26800</v>
       </c>
       <c r="H23" s="3">
-        <v>26100</v>
+        <v>26800</v>
       </c>
       <c r="I23" s="3">
-        <v>39700</v>
+        <v>40800</v>
       </c>
       <c r="J23" s="3">
-        <v>72000</v>
+        <v>74000</v>
       </c>
       <c r="K23" s="3">
         <v>167300</v>
@@ -1636,25 +1636,25 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>37200</v>
+        <v>38300</v>
       </c>
       <c r="E24" s="3">
-        <v>21100</v>
+        <v>21700</v>
       </c>
       <c r="F24" s="3">
-        <v>17400</v>
+        <v>17900</v>
       </c>
       <c r="G24" s="3">
-        <v>-5000</v>
+        <v>-5100</v>
       </c>
       <c r="H24" s="3">
-        <v>16100</v>
+        <v>16600</v>
       </c>
       <c r="I24" s="3">
-        <v>-3700</v>
+        <v>-3800</v>
       </c>
       <c r="J24" s="3">
-        <v>19800</v>
+        <v>20400</v>
       </c>
       <c r="K24" s="3">
         <v>22800</v>
@@ -1760,25 +1760,25 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>124100</v>
+        <v>127500</v>
       </c>
       <c r="E26" s="3">
-        <v>83100</v>
+        <v>85400</v>
       </c>
       <c r="F26" s="3">
-        <v>67000</v>
+        <v>68900</v>
       </c>
       <c r="G26" s="3">
-        <v>31000</v>
+        <v>31900</v>
       </c>
       <c r="H26" s="3">
-        <v>9900</v>
+        <v>10200</v>
       </c>
       <c r="I26" s="3">
-        <v>43400</v>
+        <v>44600</v>
       </c>
       <c r="J26" s="3">
-        <v>52100</v>
+        <v>53600</v>
       </c>
       <c r="K26" s="3">
         <v>144500</v>
@@ -1822,25 +1822,25 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>124100</v>
+        <v>127500</v>
       </c>
       <c r="E27" s="3">
-        <v>83100</v>
+        <v>85400</v>
       </c>
       <c r="F27" s="3">
-        <v>67000</v>
+        <v>68900</v>
       </c>
       <c r="G27" s="3">
-        <v>31000</v>
+        <v>31900</v>
       </c>
       <c r="H27" s="3">
-        <v>9900</v>
+        <v>10200</v>
       </c>
       <c r="I27" s="3">
-        <v>43400</v>
+        <v>44600</v>
       </c>
       <c r="J27" s="3">
-        <v>52100</v>
+        <v>53600</v>
       </c>
       <c r="K27" s="3">
         <v>144500</v>
@@ -1946,25 +1946,25 @@
         <v>24</v>
       </c>
       <c r="D29" s="3">
-        <v>2500</v>
+        <v>2600</v>
       </c>
       <c r="E29" s="3">
-        <v>2500</v>
+        <v>2600</v>
       </c>
       <c r="F29" s="3">
-        <v>83100</v>
+        <v>85400</v>
       </c>
       <c r="G29" s="3">
-        <v>135200</v>
+        <v>139000</v>
       </c>
       <c r="H29" s="3">
-        <v>116600</v>
+        <v>119900</v>
       </c>
       <c r="I29" s="3">
-        <v>105500</v>
+        <v>108400</v>
       </c>
       <c r="J29" s="3">
-        <v>112900</v>
+        <v>116000</v>
       </c>
       <c r="K29" s="3">
         <v>0</v>
@@ -2132,25 +2132,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-8700</v>
+        <v>-8900</v>
       </c>
       <c r="E32" s="3">
-        <v>-2500</v>
+        <v>-2600</v>
       </c>
       <c r="F32" s="3">
-        <v>57100</v>
+        <v>58700</v>
       </c>
       <c r="G32" s="3">
-        <v>16100</v>
+        <v>16600</v>
       </c>
       <c r="H32" s="3">
-        <v>14900</v>
+        <v>15300</v>
       </c>
       <c r="I32" s="3">
-        <v>16100</v>
+        <v>16600</v>
       </c>
       <c r="J32" s="3">
-        <v>16100</v>
+        <v>16600</v>
       </c>
       <c r="K32" s="3">
         <v>-2500</v>
@@ -2194,25 +2194,25 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>126500</v>
+        <v>130100</v>
       </c>
       <c r="E33" s="3">
-        <v>85600</v>
+        <v>88000</v>
       </c>
       <c r="F33" s="3">
-        <v>150100</v>
+        <v>154300</v>
       </c>
       <c r="G33" s="3">
-        <v>166200</v>
+        <v>170900</v>
       </c>
       <c r="H33" s="3">
-        <v>126500</v>
+        <v>130100</v>
       </c>
       <c r="I33" s="3">
-        <v>148900</v>
+        <v>153000</v>
       </c>
       <c r="J33" s="3">
-        <v>165000</v>
+        <v>169600</v>
       </c>
       <c r="K33" s="3">
         <v>144500</v>
@@ -2318,25 +2318,25 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>126500</v>
+        <v>130100</v>
       </c>
       <c r="E35" s="3">
-        <v>85600</v>
+        <v>88000</v>
       </c>
       <c r="F35" s="3">
-        <v>150100</v>
+        <v>154300</v>
       </c>
       <c r="G35" s="3">
-        <v>166200</v>
+        <v>170900</v>
       </c>
       <c r="H35" s="3">
-        <v>126500</v>
+        <v>130100</v>
       </c>
       <c r="I35" s="3">
-        <v>148900</v>
+        <v>153000</v>
       </c>
       <c r="J35" s="3">
-        <v>165000</v>
+        <v>169600</v>
       </c>
       <c r="K35" s="3">
         <v>144500</v>
@@ -2495,25 +2495,25 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>485100</v>
+        <v>498600</v>
       </c>
       <c r="E41" s="3">
-        <v>589300</v>
+        <v>605700</v>
       </c>
       <c r="F41" s="3">
-        <v>640100</v>
+        <v>658000</v>
       </c>
       <c r="G41" s="3">
-        <v>136500</v>
+        <v>140300</v>
       </c>
       <c r="H41" s="3">
-        <v>477600</v>
+        <v>490900</v>
       </c>
       <c r="I41" s="3">
-        <v>460300</v>
+        <v>473100</v>
       </c>
       <c r="J41" s="3">
-        <v>600500</v>
+        <v>617100</v>
       </c>
       <c r="K41" s="3">
         <v>343400</v>
@@ -2566,16 +2566,16 @@
         <v>0</v>
       </c>
       <c r="G42" s="3">
-        <v>2500</v>
+        <v>2600</v>
       </c>
       <c r="H42" s="3">
         <v>0</v>
       </c>
       <c r="I42" s="3">
-        <v>39700</v>
+        <v>40800</v>
       </c>
       <c r="J42" s="3">
-        <v>47100</v>
+        <v>48500</v>
       </c>
       <c r="K42" s="3">
         <v>84900</v>
@@ -2619,25 +2619,25 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>375900</v>
+        <v>386400</v>
       </c>
       <c r="E43" s="3">
-        <v>446600</v>
+        <v>459000</v>
       </c>
       <c r="F43" s="3">
-        <v>512400</v>
+        <v>526600</v>
       </c>
       <c r="G43" s="3">
-        <v>348600</v>
+        <v>358300</v>
       </c>
       <c r="H43" s="3">
-        <v>325000</v>
+        <v>334100</v>
       </c>
       <c r="I43" s="3">
-        <v>426800</v>
+        <v>438600</v>
       </c>
       <c r="J43" s="3">
-        <v>395800</v>
+        <v>406800</v>
       </c>
       <c r="K43" s="3">
         <v>422000</v>
@@ -2681,25 +2681,25 @@
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>507400</v>
+        <v>521500</v>
       </c>
       <c r="E44" s="3">
-        <v>553300</v>
+        <v>568700</v>
       </c>
       <c r="F44" s="3">
-        <v>553300</v>
+        <v>568700</v>
       </c>
       <c r="G44" s="3">
-        <v>393300</v>
+        <v>404200</v>
       </c>
       <c r="H44" s="3">
-        <v>326300</v>
+        <v>335400</v>
       </c>
       <c r="I44" s="3">
-        <v>660000</v>
+        <v>678400</v>
       </c>
       <c r="J44" s="3">
-        <v>485100</v>
+        <v>498600</v>
       </c>
       <c r="K44" s="3">
         <v>577900</v>
@@ -2743,25 +2743,25 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>1200</v>
+        <v>1300</v>
       </c>
       <c r="E45" s="3">
-        <v>3700</v>
+        <v>3800</v>
       </c>
       <c r="F45" s="3">
-        <v>16100</v>
+        <v>16600</v>
       </c>
       <c r="G45" s="3">
-        <v>2171100</v>
+        <v>2231400</v>
       </c>
       <c r="H45" s="3">
-        <v>1705800</v>
+        <v>1753300</v>
       </c>
       <c r="I45" s="3">
-        <v>28500</v>
+        <v>29300</v>
       </c>
       <c r="J45" s="3">
-        <v>11200</v>
+        <v>11500</v>
       </c>
       <c r="K45" s="3">
         <v>6300</v>
@@ -2805,25 +2805,25 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>1369600</v>
+        <v>1407700</v>
       </c>
       <c r="E46" s="3">
-        <v>1592900</v>
+        <v>1637200</v>
       </c>
       <c r="F46" s="3">
-        <v>1722000</v>
+        <v>1769800</v>
       </c>
       <c r="G46" s="3">
-        <v>3051900</v>
+        <v>3136700</v>
       </c>
       <c r="H46" s="3">
-        <v>2834800</v>
+        <v>2913600</v>
       </c>
       <c r="I46" s="3">
-        <v>1615300</v>
+        <v>1660200</v>
       </c>
       <c r="J46" s="3">
-        <v>1539600</v>
+        <v>1582400</v>
       </c>
       <c r="K46" s="3">
         <v>1434600</v>
@@ -2867,25 +2867,25 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>310200</v>
+        <v>318800</v>
       </c>
       <c r="E47" s="3">
-        <v>312600</v>
+        <v>321300</v>
       </c>
       <c r="F47" s="3">
-        <v>368500</v>
+        <v>378700</v>
       </c>
       <c r="G47" s="3">
-        <v>58300</v>
+        <v>59900</v>
       </c>
       <c r="H47" s="3">
-        <v>63300</v>
+        <v>65000</v>
       </c>
       <c r="I47" s="3">
-        <v>203500</v>
+        <v>209100</v>
       </c>
       <c r="J47" s="3">
-        <v>203500</v>
+        <v>209100</v>
       </c>
       <c r="K47" s="3">
         <v>195200</v>
@@ -2929,25 +2929,25 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>626500</v>
+        <v>643900</v>
       </c>
       <c r="E48" s="3">
-        <v>605400</v>
+        <v>622200</v>
       </c>
       <c r="F48" s="3">
-        <v>622800</v>
+        <v>640100</v>
       </c>
       <c r="G48" s="3">
-        <v>534700</v>
+        <v>549600</v>
       </c>
       <c r="H48" s="3">
-        <v>528500</v>
+        <v>543200</v>
       </c>
       <c r="I48" s="3">
-        <v>1370900</v>
+        <v>1409000</v>
       </c>
       <c r="J48" s="3">
-        <v>2858300</v>
+        <v>2937800</v>
       </c>
       <c r="K48" s="3">
         <v>1508100</v>
@@ -2991,25 +2991,25 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>533500</v>
+        <v>548300</v>
       </c>
       <c r="E49" s="3">
-        <v>560800</v>
+        <v>576300</v>
       </c>
       <c r="F49" s="3">
-        <v>617800</v>
+        <v>635000</v>
       </c>
       <c r="G49" s="3">
-        <v>344900</v>
+        <v>354500</v>
       </c>
       <c r="H49" s="3">
-        <v>359800</v>
+        <v>369800</v>
       </c>
       <c r="I49" s="3">
-        <v>428000</v>
+        <v>439900</v>
       </c>
       <c r="J49" s="3">
-        <v>395800</v>
+        <v>406800</v>
       </c>
       <c r="K49" s="3">
         <v>430900</v>
@@ -3177,25 +3177,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>50900</v>
+        <v>52300</v>
       </c>
       <c r="E52" s="3">
-        <v>38500</v>
+        <v>39500</v>
       </c>
       <c r="F52" s="3">
-        <v>34700</v>
+        <v>35700</v>
       </c>
       <c r="G52" s="3">
-        <v>43400</v>
+        <v>44600</v>
       </c>
       <c r="H52" s="3">
-        <v>81900</v>
+        <v>84200</v>
       </c>
       <c r="I52" s="3">
-        <v>63300</v>
+        <v>65000</v>
       </c>
       <c r="J52" s="3">
-        <v>52100</v>
+        <v>53600</v>
       </c>
       <c r="K52" s="3">
         <v>44400</v>
@@ -3301,25 +3301,25 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>2890600</v>
+        <v>2971000</v>
       </c>
       <c r="E54" s="3">
-        <v>3110200</v>
+        <v>3196700</v>
       </c>
       <c r="F54" s="3">
-        <v>3365700</v>
+        <v>3459300</v>
       </c>
       <c r="G54" s="3">
-        <v>4033200</v>
+        <v>4145400</v>
       </c>
       <c r="H54" s="3">
-        <v>3868200</v>
+        <v>3975800</v>
       </c>
       <c r="I54" s="3">
-        <v>3680900</v>
+        <v>3783200</v>
       </c>
       <c r="J54" s="3">
-        <v>3620100</v>
+        <v>3720700</v>
       </c>
       <c r="K54" s="3">
         <v>3613100</v>
@@ -3411,25 +3411,25 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>335000</v>
+        <v>344300</v>
       </c>
       <c r="E57" s="3">
-        <v>461500</v>
+        <v>474300</v>
       </c>
       <c r="F57" s="3">
-        <v>516100</v>
+        <v>530400</v>
       </c>
       <c r="G57" s="3">
-        <v>364700</v>
+        <v>374900</v>
       </c>
       <c r="H57" s="3">
-        <v>261800</v>
+        <v>269000</v>
       </c>
       <c r="I57" s="3">
-        <v>534700</v>
+        <v>549600</v>
       </c>
       <c r="J57" s="3">
-        <v>413100</v>
+        <v>424600</v>
       </c>
       <c r="K57" s="3">
         <v>468900</v>
@@ -3473,25 +3473,25 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>53300</v>
+        <v>54800</v>
       </c>
       <c r="E58" s="3">
-        <v>150100</v>
+        <v>154300</v>
       </c>
       <c r="F58" s="3">
-        <v>33500</v>
+        <v>34400</v>
       </c>
       <c r="G58" s="3">
-        <v>26100</v>
+        <v>26800</v>
       </c>
       <c r="H58" s="3">
-        <v>31000</v>
+        <v>31900</v>
       </c>
       <c r="I58" s="3">
-        <v>104200</v>
+        <v>107100</v>
       </c>
       <c r="J58" s="3">
-        <v>104200</v>
+        <v>107100</v>
       </c>
       <c r="K58" s="3">
         <v>50700</v>
@@ -3535,25 +3535,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>86800</v>
+        <v>89300</v>
       </c>
       <c r="E59" s="3">
-        <v>98000</v>
+        <v>100700</v>
       </c>
       <c r="F59" s="3">
-        <v>103000</v>
+        <v>105800</v>
       </c>
       <c r="G59" s="3">
-        <v>576900</v>
+        <v>592900</v>
       </c>
       <c r="H59" s="3">
-        <v>642600</v>
+        <v>660500</v>
       </c>
       <c r="I59" s="3">
-        <v>104200</v>
+        <v>107100</v>
       </c>
       <c r="J59" s="3">
-        <v>101700</v>
+        <v>104600</v>
       </c>
       <c r="K59" s="3">
         <v>124200</v>
@@ -3597,25 +3597,25 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>475100</v>
+        <v>488400</v>
       </c>
       <c r="E60" s="3">
-        <v>709600</v>
+        <v>729400</v>
       </c>
       <c r="F60" s="3">
-        <v>652600</v>
+        <v>670700</v>
       </c>
       <c r="G60" s="3">
-        <v>967700</v>
+        <v>994600</v>
       </c>
       <c r="H60" s="3">
-        <v>935400</v>
+        <v>961400</v>
       </c>
       <c r="I60" s="3">
-        <v>691000</v>
+        <v>710200</v>
       </c>
       <c r="J60" s="3">
-        <v>567000</v>
+        <v>582700</v>
       </c>
       <c r="K60" s="3">
         <v>643800</v>
@@ -3659,25 +3659,25 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>740600</v>
+        <v>761200</v>
       </c>
       <c r="E61" s="3">
-        <v>734400</v>
+        <v>754900</v>
       </c>
       <c r="F61" s="3">
-        <v>955300</v>
+        <v>981800</v>
       </c>
       <c r="G61" s="3">
-        <v>816300</v>
+        <v>839000</v>
       </c>
       <c r="H61" s="3">
-        <v>867200</v>
+        <v>891300</v>
       </c>
       <c r="I61" s="3">
-        <v>925500</v>
+        <v>951200</v>
       </c>
       <c r="J61" s="3">
-        <v>992500</v>
+        <v>1020100</v>
       </c>
       <c r="K61" s="3">
         <v>864300</v>
@@ -3721,25 +3721,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>173700</v>
+        <v>178500</v>
       </c>
       <c r="E62" s="3">
-        <v>189800</v>
+        <v>195100</v>
       </c>
       <c r="F62" s="3">
-        <v>241900</v>
+        <v>248600</v>
       </c>
       <c r="G62" s="3">
-        <v>239400</v>
+        <v>246100</v>
       </c>
       <c r="H62" s="3">
-        <v>194800</v>
+        <v>200200</v>
       </c>
       <c r="I62" s="3">
-        <v>260500</v>
+        <v>267800</v>
       </c>
       <c r="J62" s="3">
-        <v>295300</v>
+        <v>303500</v>
       </c>
       <c r="K62" s="3">
         <v>332000</v>
@@ -3969,25 +3969,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>1390700</v>
+        <v>1429400</v>
       </c>
       <c r="E66" s="3">
-        <v>1635100</v>
+        <v>1680600</v>
       </c>
       <c r="F66" s="3">
-        <v>1851000</v>
+        <v>1902400</v>
       </c>
       <c r="G66" s="3">
-        <v>2024700</v>
+        <v>2081000</v>
       </c>
       <c r="H66" s="3">
-        <v>1998600</v>
+        <v>2054200</v>
       </c>
       <c r="I66" s="3">
-        <v>1878300</v>
+        <v>1930500</v>
       </c>
       <c r="J66" s="3">
-        <v>1854700</v>
+        <v>1906300</v>
       </c>
       <c r="K66" s="3">
         <v>1840100</v>
@@ -4303,25 +4303,25 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>848600</v>
+        <v>872200</v>
       </c>
       <c r="E72" s="3">
-        <v>823800</v>
+        <v>846700</v>
       </c>
       <c r="F72" s="3">
-        <v>864700</v>
+        <v>888700</v>
       </c>
       <c r="G72" s="3">
-        <v>1358500</v>
+        <v>1396200</v>
       </c>
       <c r="H72" s="3">
-        <v>1219500</v>
+        <v>1253400</v>
       </c>
       <c r="I72" s="3">
-        <v>1152500</v>
+        <v>1184600</v>
       </c>
       <c r="J72" s="3">
-        <v>1115300</v>
+        <v>1146300</v>
       </c>
       <c r="K72" s="3">
         <v>1110200</v>
@@ -4551,25 +4551,25 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>1499900</v>
+        <v>1541600</v>
       </c>
       <c r="E76" s="3">
-        <v>1475100</v>
+        <v>1516100</v>
       </c>
       <c r="F76" s="3">
-        <v>1514800</v>
+        <v>1556900</v>
       </c>
       <c r="G76" s="3">
-        <v>2008500</v>
+        <v>2064400</v>
       </c>
       <c r="H76" s="3">
-        <v>1869600</v>
+        <v>1921600</v>
       </c>
       <c r="I76" s="3">
-        <v>1802600</v>
+        <v>1852700</v>
       </c>
       <c r="J76" s="3">
-        <v>1765400</v>
+        <v>1814500</v>
       </c>
       <c r="K76" s="3">
         <v>1773000</v>
@@ -4742,25 +4742,25 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>126500</v>
+        <v>130100</v>
       </c>
       <c r="E81" s="3">
-        <v>85600</v>
+        <v>88000</v>
       </c>
       <c r="F81" s="3">
-        <v>150100</v>
+        <v>154300</v>
       </c>
       <c r="G81" s="3">
-        <v>166200</v>
+        <v>170900</v>
       </c>
       <c r="H81" s="3">
-        <v>126500</v>
+        <v>130100</v>
       </c>
       <c r="I81" s="3">
-        <v>148900</v>
+        <v>153000</v>
       </c>
       <c r="J81" s="3">
-        <v>165000</v>
+        <v>169600</v>
       </c>
       <c r="K81" s="3">
         <v>144500</v>
@@ -4828,25 +4828,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>58300</v>
+        <v>59900</v>
       </c>
       <c r="E83" s="3">
-        <v>59500</v>
+        <v>61200</v>
       </c>
       <c r="F83" s="3">
-        <v>58300</v>
+        <v>59900</v>
       </c>
       <c r="G83" s="3">
-        <v>48400</v>
+        <v>49700</v>
       </c>
       <c r="H83" s="3">
-        <v>75700</v>
+        <v>77800</v>
       </c>
       <c r="I83" s="3">
-        <v>107900</v>
+        <v>110900</v>
       </c>
       <c r="J83" s="3">
-        <v>109200</v>
+        <v>112200</v>
       </c>
       <c r="K83" s="3">
         <v>95000</v>
@@ -5200,25 +5200,25 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>106700</v>
+        <v>109700</v>
       </c>
       <c r="E89" s="3">
-        <v>34700</v>
+        <v>35700</v>
       </c>
       <c r="F89" s="3">
-        <v>47100</v>
+        <v>48500</v>
       </c>
       <c r="G89" s="3">
-        <v>-94300</v>
+        <v>-96900</v>
       </c>
       <c r="H89" s="3">
-        <v>222100</v>
+        <v>228200</v>
       </c>
       <c r="I89" s="3">
-        <v>153800</v>
+        <v>158100</v>
       </c>
       <c r="J89" s="3">
-        <v>303900</v>
+        <v>312400</v>
       </c>
       <c r="K89" s="3">
         <v>196400</v>
@@ -5472,25 +5472,25 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-14900</v>
+        <v>-15300</v>
       </c>
       <c r="E94" s="3">
-        <v>19800</v>
+        <v>20400</v>
       </c>
       <c r="F94" s="3">
-        <v>1016100</v>
+        <v>1044300</v>
       </c>
       <c r="G94" s="3">
-        <v>-89300</v>
+        <v>-91800</v>
       </c>
       <c r="H94" s="3">
-        <v>-50900</v>
+        <v>-52300</v>
       </c>
       <c r="I94" s="3">
-        <v>-179900</v>
+        <v>-184900</v>
       </c>
       <c r="J94" s="3">
-        <v>-74400</v>
+        <v>-76500</v>
       </c>
       <c r="K94" s="3">
         <v>-106500</v>
@@ -5558,25 +5558,25 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-64500</v>
+        <v>-66300</v>
       </c>
       <c r="E96" s="3">
-        <v>-27300</v>
+        <v>-28100</v>
       </c>
       <c r="F96" s="3">
-        <v>-679800</v>
+        <v>-698800</v>
       </c>
       <c r="G96" s="3">
-        <v>-52100</v>
+        <v>-53600</v>
       </c>
       <c r="H96" s="3">
-        <v>-126500</v>
+        <v>-130100</v>
       </c>
       <c r="I96" s="3">
-        <v>-49600</v>
+        <v>-51000</v>
       </c>
       <c r="J96" s="3">
-        <v>-120300</v>
+        <v>-123700</v>
       </c>
       <c r="K96" s="3">
         <v>-50700</v>
@@ -5806,25 +5806,25 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-197300</v>
+        <v>-202700</v>
       </c>
       <c r="E100" s="3">
-        <v>-47100</v>
+        <v>-48500</v>
       </c>
       <c r="F100" s="3">
-        <v>-694700</v>
+        <v>-714100</v>
       </c>
       <c r="G100" s="3">
-        <v>-156300</v>
+        <v>-160700</v>
       </c>
       <c r="H100" s="3">
-        <v>-150100</v>
+        <v>-154300</v>
       </c>
       <c r="I100" s="3">
-        <v>-78200</v>
+        <v>-80300</v>
       </c>
       <c r="J100" s="3">
-        <v>42200</v>
+        <v>43400</v>
       </c>
       <c r="K100" s="3">
         <v>-188800</v>
@@ -5868,25 +5868,25 @@
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>1200</v>
+        <v>1300</v>
       </c>
       <c r="E101" s="3">
-        <v>-58300</v>
+        <v>-59900</v>
       </c>
       <c r="F101" s="3">
-        <v>114100</v>
+        <v>117300</v>
       </c>
       <c r="G101" s="3">
-        <v>6200</v>
+        <v>6400</v>
       </c>
       <c r="H101" s="3">
-        <v>9900</v>
+        <v>10200</v>
       </c>
       <c r="I101" s="3">
-        <v>-36000</v>
+        <v>-37000</v>
       </c>
       <c r="J101" s="3">
-        <v>-7400</v>
+        <v>-7700</v>
       </c>
       <c r="K101" s="3">
         <v>-15200</v>
@@ -5930,25 +5930,25 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-104200</v>
+        <v>-107100</v>
       </c>
       <c r="E102" s="3">
-        <v>-50900</v>
+        <v>-52300</v>
       </c>
       <c r="F102" s="3">
-        <v>482600</v>
+        <v>496000</v>
       </c>
       <c r="G102" s="3">
-        <v>-333700</v>
+        <v>-343000</v>
       </c>
       <c r="H102" s="3">
-        <v>31000</v>
+        <v>31900</v>
       </c>
       <c r="I102" s="3">
-        <v>-140200</v>
+        <v>-144100</v>
       </c>
       <c r="J102" s="3">
-        <v>264200</v>
+        <v>271600</v>
       </c>
       <c r="K102" s="3">
         <v>-114100</v>

--- a/AAII_Financials/Quarterly/TATYY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/TATYY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="92">
   <si>
     <t>TATYY</t>
   </si>
@@ -656,169 +656,176 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:V102"/>
+  <dimension ref="A5:W102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45016</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44834</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44651</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44469</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44286</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44104</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>43921</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>43738</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>43555</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>43373</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>43190</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>43008</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>42825</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>42643</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>42460</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>42277</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>42094</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>41912</v>
       </c>
     </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>1092800</v>
+        <v>1010900</v>
       </c>
       <c r="E8" s="3">
-        <v>1150100</v>
+        <v>1096600</v>
       </c>
       <c r="F8" s="3">
-        <v>1082600</v>
+        <v>1154200</v>
       </c>
       <c r="G8" s="3">
-        <v>916800</v>
+        <v>1086400</v>
       </c>
       <c r="H8" s="3">
-        <v>836500</v>
+        <v>920000</v>
       </c>
       <c r="I8" s="3">
-        <v>789300</v>
+        <v>839400</v>
       </c>
       <c r="J8" s="3">
+        <v>792100</v>
+      </c>
+      <c r="K8" s="3">
         <v>754900</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1781800</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1831400</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1622900</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1687100</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1789300</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1978300</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>1891400</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>1626900</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>1545600</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>1526000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>1502500</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>1580100</v>
       </c>
     </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -879,8 +886,11 @@
       <c r="V9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -941,8 +951,11 @@
       <c r="V10" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -965,8 +978,9 @@
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
-    </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W11" s="3"/>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1027,8 +1041,11 @@
       <c r="V12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1089,35 +1106,38 @@
       <c r="V13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>23000</v>
+      </c>
+      <c r="E14" s="3">
         <v>10200</v>
       </c>
-      <c r="E14" s="3">
-        <v>21700</v>
-      </c>
       <c r="F14" s="3">
-        <v>14000</v>
+        <v>21800</v>
       </c>
       <c r="G14" s="3">
-        <v>30600</v>
+        <v>14100</v>
       </c>
       <c r="H14" s="3">
-        <v>75200</v>
+        <v>30700</v>
       </c>
       <c r="I14" s="3">
-        <v>24200</v>
+        <v>75500</v>
       </c>
       <c r="J14" s="3">
+        <v>24300</v>
+      </c>
+      <c r="K14" s="3">
         <v>19100</v>
       </c>
-      <c r="K14" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="L14" s="3" t="s">
         <v>5</v>
       </c>
@@ -1130,8 +1150,8 @@
       <c r="O14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
+      <c r="P14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Q14" s="3">
         <v>0</v>
@@ -1139,8 +1159,8 @@
       <c r="R14" s="3">
         <v>0</v>
       </c>
-      <c r="S14" s="3" t="s">
-        <v>5</v>
+      <c r="S14" s="3">
+        <v>0</v>
       </c>
       <c r="T14" s="3" t="s">
         <v>5</v>
@@ -1151,35 +1171,38 @@
       <c r="V14" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W14" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E15" s="3">
-        <v>30600</v>
+      <c r="E15" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="F15" s="3">
-        <v>15300</v>
+        <v>30700</v>
       </c>
       <c r="G15" s="3">
-        <v>24200</v>
+        <v>15400</v>
       </c>
       <c r="H15" s="3">
+        <v>24300</v>
+      </c>
+      <c r="I15" s="3">
         <v>6400</v>
       </c>
-      <c r="I15" s="3">
-        <v>26800</v>
-      </c>
       <c r="J15" s="3">
+        <v>26900</v>
+      </c>
+      <c r="K15" s="3">
         <v>6400</v>
       </c>
-      <c r="K15" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="L15" s="3" t="s">
         <v>5</v>
       </c>
@@ -1192,8 +1215,8 @@
       <c r="O15" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P15" s="3">
-        <v>0</v>
+      <c r="P15" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Q15" s="3">
         <v>0</v>
@@ -1201,8 +1224,8 @@
       <c r="R15" s="3">
         <v>0</v>
       </c>
-      <c r="S15" s="3" t="s">
-        <v>5</v>
+      <c r="S15" s="3">
+        <v>0</v>
       </c>
       <c r="T15" s="3" t="s">
         <v>5</v>
@@ -1213,8 +1236,11 @@
       <c r="V15" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W15" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1234,132 +1260,139 @@
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
-    </row>
-    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W16" s="3"/>
+    </row>
+    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>935900</v>
+        <v>903400</v>
       </c>
       <c r="E17" s="3">
-        <v>1045600</v>
+        <v>939200</v>
       </c>
       <c r="F17" s="3">
-        <v>937200</v>
+        <v>1049300</v>
       </c>
       <c r="G17" s="3">
-        <v>873400</v>
+        <v>940500</v>
       </c>
       <c r="H17" s="3">
-        <v>794400</v>
+        <v>876500</v>
       </c>
       <c r="I17" s="3">
-        <v>731900</v>
+        <v>797200</v>
       </c>
       <c r="J17" s="3">
+        <v>734500</v>
+      </c>
+      <c r="K17" s="3">
         <v>664300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1617100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1625400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1477400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1549300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1618800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1744800</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1747400</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1474200</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1472600</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1433400</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1548500</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>1490600</v>
       </c>
     </row>
-    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>156800</v>
+        <v>107500</v>
       </c>
       <c r="E18" s="3">
-        <v>104600</v>
+        <v>157400</v>
       </c>
       <c r="F18" s="3">
-        <v>145400</v>
+        <v>104900</v>
       </c>
       <c r="G18" s="3">
-        <v>43400</v>
+        <v>145900</v>
       </c>
       <c r="H18" s="3">
-        <v>42100</v>
+        <v>43500</v>
       </c>
       <c r="I18" s="3">
-        <v>57400</v>
+        <v>42200</v>
       </c>
       <c r="J18" s="3">
+        <v>57600</v>
+      </c>
+      <c r="K18" s="3">
         <v>90500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>164700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>206000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>145500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>137800</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>170500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>233500</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>144000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>152700</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>73000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>92600</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-46100</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>89500</v>
       </c>
     </row>
-    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1382,132 +1415,139 @@
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
-    </row>
-    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W19" s="3"/>
+    </row>
+    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>8900</v>
+        <v>15400</v>
       </c>
       <c r="E20" s="3">
+        <v>9000</v>
+      </c>
+      <c r="F20" s="3">
         <v>2600</v>
       </c>
-      <c r="F20" s="3">
-        <v>-58700</v>
-      </c>
       <c r="G20" s="3">
+        <v>-58900</v>
+      </c>
+      <c r="H20" s="3">
         <v>-16600</v>
       </c>
-      <c r="H20" s="3">
-        <v>-15300</v>
-      </c>
       <c r="I20" s="3">
-        <v>-16600</v>
+        <v>-15400</v>
       </c>
       <c r="J20" s="3">
         <v>-16600</v>
       </c>
       <c r="K20" s="3">
+        <v>-16600</v>
+      </c>
+      <c r="L20" s="3">
         <v>2500</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-2500</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>4700</v>
       </c>
-      <c r="N20" s="3">
-        <v>0</v>
-      </c>
       <c r="O20" s="3">
         <v>0</v>
       </c>
       <c r="P20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="3">
         <v>-5700</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-5300</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>4900</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>17000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>11700</v>
-      </c>
-      <c r="U20" s="3">
-        <v>10500</v>
       </c>
       <c r="V20" s="3">
         <v>10500</v>
       </c>
-    </row>
-    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W20" s="3">
+        <v>10500</v>
+      </c>
+    </row>
+    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>225700</v>
+        <v>183000</v>
       </c>
       <c r="E21" s="3">
+        <v>226500</v>
+      </c>
+      <c r="F21" s="3">
+        <v>168900</v>
+      </c>
+      <c r="G21" s="3">
+        <v>147200</v>
+      </c>
+      <c r="H21" s="3">
+        <v>76800</v>
+      </c>
+      <c r="I21" s="3">
+        <v>104900</v>
+      </c>
+      <c r="J21" s="3">
+        <v>152300</v>
+      </c>
+      <c r="K21" s="3">
+        <v>186200</v>
+      </c>
+      <c r="L21" s="3">
+        <v>262300</v>
+      </c>
+      <c r="M21" s="3">
+        <v>323800</v>
+      </c>
+      <c r="N21" s="3">
+        <v>241300</v>
+      </c>
+      <c r="O21" s="3">
+        <v>229300</v>
+      </c>
+      <c r="P21" s="3">
+        <v>276800</v>
+      </c>
+      <c r="Q21" s="3">
+        <v>335400</v>
+      </c>
+      <c r="R21" s="3">
+        <v>244300</v>
+      </c>
+      <c r="S21" s="3">
+        <v>242600</v>
+      </c>
+      <c r="T21" s="3">
         <v>168300</v>
       </c>
-      <c r="F21" s="3">
-        <v>146600</v>
-      </c>
-      <c r="G21" s="3">
-        <v>76500</v>
-      </c>
-      <c r="H21" s="3">
-        <v>104600</v>
-      </c>
-      <c r="I21" s="3">
-        <v>151700</v>
-      </c>
-      <c r="J21" s="3">
-        <v>186200</v>
-      </c>
-      <c r="K21" s="3">
-        <v>262300</v>
-      </c>
-      <c r="L21" s="3">
-        <v>323800</v>
-      </c>
-      <c r="M21" s="3">
-        <v>241300</v>
-      </c>
-      <c r="N21" s="3">
-        <v>229300</v>
-      </c>
-      <c r="O21" s="3">
-        <v>276800</v>
-      </c>
-      <c r="P21" s="3">
-        <v>335400</v>
-      </c>
-      <c r="Q21" s="3">
-        <v>244300</v>
-      </c>
-      <c r="R21" s="3">
-        <v>242600</v>
-      </c>
-      <c r="S21" s="3">
-        <v>168300</v>
-      </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>176100</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>40800</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>167200</v>
       </c>
     </row>
-    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1538,8 +1578,8 @@
       <c r="L22" s="3">
         <v>0</v>
       </c>
-      <c r="M22" s="3" t="s">
-        <v>5</v>
+      <c r="M22" s="3">
+        <v>0</v>
       </c>
       <c r="N22" s="3" t="s">
         <v>5</v>
@@ -1556,144 +1596,153 @@
       <c r="R22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="S22" s="3">
+      <c r="S22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T22" s="3">
         <v>17000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>13000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>14500</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>17100</v>
       </c>
     </row>
-    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>165800</v>
+        <v>122800</v>
       </c>
       <c r="E23" s="3">
-        <v>107100</v>
+        <v>166300</v>
       </c>
       <c r="F23" s="3">
-        <v>86700</v>
+        <v>107500</v>
       </c>
       <c r="G23" s="3">
-        <v>26800</v>
+        <v>87000</v>
       </c>
       <c r="H23" s="3">
-        <v>26800</v>
+        <v>26900</v>
       </c>
       <c r="I23" s="3">
-        <v>40800</v>
+        <v>26900</v>
       </c>
       <c r="J23" s="3">
+        <v>40900</v>
+      </c>
+      <c r="K23" s="3">
         <v>74000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>167300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>203500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>150200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>137800</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>170500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>227800</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>138700</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>157600</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>73000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>91300</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-50000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>83000</v>
       </c>
     </row>
-    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>38300</v>
+        <v>30700</v>
       </c>
       <c r="E24" s="3">
-        <v>21700</v>
+        <v>38400</v>
       </c>
       <c r="F24" s="3">
+        <v>21800</v>
+      </c>
+      <c r="G24" s="3">
         <v>17900</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-5100</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>16600</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-3800</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>20400</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>22800</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>40900</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>31900</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>39000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-19100</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>52400</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-27700</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-1200</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>2600</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>3900</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>13200</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>14500</v>
       </c>
     </row>
-    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1754,132 +1803,141 @@
       <c r="V25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>127500</v>
+        <v>92100</v>
       </c>
       <c r="E26" s="3">
-        <v>85400</v>
+        <v>128000</v>
       </c>
       <c r="F26" s="3">
-        <v>68900</v>
+        <v>85700</v>
       </c>
       <c r="G26" s="3">
-        <v>31900</v>
+        <v>69100</v>
       </c>
       <c r="H26" s="3">
+        <v>32000</v>
+      </c>
+      <c r="I26" s="3">
         <v>10200</v>
       </c>
-      <c r="I26" s="3">
-        <v>44600</v>
-      </c>
       <c r="J26" s="3">
+        <v>44800</v>
+      </c>
+      <c r="K26" s="3">
         <v>53600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>144500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>162500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>118300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>98800</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>189600</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>175500</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>166400</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>158900</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>70400</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>87400</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-63200</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>68500</v>
       </c>
     </row>
-    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>127500</v>
+        <v>92100</v>
       </c>
       <c r="E27" s="3">
-        <v>85400</v>
+        <v>128000</v>
       </c>
       <c r="F27" s="3">
-        <v>68900</v>
+        <v>85700</v>
       </c>
       <c r="G27" s="3">
-        <v>31900</v>
+        <v>69100</v>
       </c>
       <c r="H27" s="3">
+        <v>32000</v>
+      </c>
+      <c r="I27" s="3">
         <v>10200</v>
       </c>
-      <c r="I27" s="3">
-        <v>44600</v>
-      </c>
       <c r="J27" s="3">
+        <v>44800</v>
+      </c>
+      <c r="K27" s="3">
         <v>53600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>144500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>162500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>118300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>98800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>189600</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>175500</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>166400</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>158900</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>70400</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>87400</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-63200</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>68500</v>
       </c>
     </row>
-    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1940,70 +1998,76 @@
       <c r="V28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="3">
-        <v>2600</v>
+        <v>17900</v>
       </c>
       <c r="E29" s="3">
         <v>2600</v>
       </c>
       <c r="F29" s="3">
-        <v>85400</v>
+        <v>2600</v>
       </c>
       <c r="G29" s="3">
-        <v>139000</v>
+        <v>85700</v>
       </c>
       <c r="H29" s="3">
-        <v>119900</v>
+        <v>139500</v>
       </c>
       <c r="I29" s="3">
-        <v>108400</v>
+        <v>120300</v>
       </c>
       <c r="J29" s="3">
+        <v>108800</v>
+      </c>
+      <c r="K29" s="3">
         <v>116000</v>
       </c>
-      <c r="K29" s="3">
-        <v>0</v>
-      </c>
-      <c r="L29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M29" s="3">
-        <v>0</v>
+      <c r="L29" s="3">
+        <v>0</v>
+      </c>
+      <c r="M29" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="N29" s="3">
         <v>0</v>
       </c>
       <c r="O29" s="3">
+        <v>0</v>
+      </c>
+      <c r="P29" s="3">
         <v>2700</v>
       </c>
-      <c r="P29" s="3">
-        <v>0</v>
-      </c>
       <c r="Q29" s="3">
         <v>0</v>
       </c>
       <c r="R29" s="3">
+        <v>0</v>
+      </c>
+      <c r="S29" s="3">
         <v>1200</v>
       </c>
-      <c r="S29" s="3">
+      <c r="T29" s="3">
         <v>78300</v>
       </c>
-      <c r="T29" s="3">
+      <c r="U29" s="3">
         <v>-23500</v>
       </c>
-      <c r="U29" s="3">
+      <c r="V29" s="3">
         <v>13200</v>
       </c>
-      <c r="V29" s="3">
+      <c r="W29" s="3">
         <v>21100</v>
       </c>
     </row>
-    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2064,8 +2128,11 @@
       <c r="V30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2126,132 +2193,141 @@
       <c r="V31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-8900</v>
+        <v>-15400</v>
       </c>
       <c r="E32" s="3">
+        <v>-9000</v>
+      </c>
+      <c r="F32" s="3">
         <v>-2600</v>
       </c>
-      <c r="F32" s="3">
-        <v>58700</v>
-      </c>
       <c r="G32" s="3">
+        <v>58900</v>
+      </c>
+      <c r="H32" s="3">
         <v>16600</v>
       </c>
-      <c r="H32" s="3">
-        <v>15300</v>
-      </c>
       <c r="I32" s="3">
-        <v>16600</v>
+        <v>15400</v>
       </c>
       <c r="J32" s="3">
         <v>16600</v>
       </c>
       <c r="K32" s="3">
+        <v>16600</v>
+      </c>
+      <c r="L32" s="3">
         <v>-2500</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>2500</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-4700</v>
       </c>
-      <c r="N32" s="3">
-        <v>0</v>
-      </c>
       <c r="O32" s="3">
         <v>0</v>
       </c>
       <c r="P32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="3">
         <v>5700</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>5300</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-4900</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-17000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-11700</v>
-      </c>
-      <c r="U32" s="3">
-        <v>-10500</v>
       </c>
       <c r="V32" s="3">
         <v>-10500</v>
       </c>
-    </row>
-    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W32" s="3">
+        <v>-10500</v>
+      </c>
+    </row>
+    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>130100</v>
+        <v>110000</v>
       </c>
       <c r="E33" s="3">
-        <v>88000</v>
+        <v>130500</v>
       </c>
       <c r="F33" s="3">
-        <v>154300</v>
+        <v>88300</v>
       </c>
       <c r="G33" s="3">
-        <v>170900</v>
+        <v>154800</v>
       </c>
       <c r="H33" s="3">
-        <v>130100</v>
+        <v>171500</v>
       </c>
       <c r="I33" s="3">
-        <v>153000</v>
+        <v>130500</v>
       </c>
       <c r="J33" s="3">
+        <v>153600</v>
+      </c>
+      <c r="K33" s="3">
         <v>169600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>144500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>162500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>118300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>98800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>192300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>175500</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>166400</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>160100</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>148700</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>63900</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-50000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>89500</v>
       </c>
     </row>
-    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2312,137 +2388,146 @@
       <c r="V34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>130100</v>
+        <v>110000</v>
       </c>
       <c r="E35" s="3">
-        <v>88000</v>
+        <v>130500</v>
       </c>
       <c r="F35" s="3">
-        <v>154300</v>
+        <v>88300</v>
       </c>
       <c r="G35" s="3">
-        <v>170900</v>
+        <v>154800</v>
       </c>
       <c r="H35" s="3">
-        <v>130100</v>
+        <v>171500</v>
       </c>
       <c r="I35" s="3">
-        <v>153000</v>
+        <v>130500</v>
       </c>
       <c r="J35" s="3">
+        <v>153600</v>
+      </c>
+      <c r="K35" s="3">
         <v>169600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>144500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>162500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>118300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>98800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>192300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>175500</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>166400</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>160100</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>148700</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>63900</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-50000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>89500</v>
       </c>
     </row>
-    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45016</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44834</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44651</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44469</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44286</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44104</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>43921</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>43738</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>43555</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>43373</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>43190</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>43008</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>42825</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>42643</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>42460</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>42277</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>42094</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>41912</v>
       </c>
     </row>
-    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2465,8 +2550,9 @@
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
-    </row>
-    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W39" s="3"/>
+    </row>
+    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2489,566 +2575,594 @@
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
-    </row>
-    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W40" s="3"/>
+    </row>
+    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>498600</v>
+        <v>559200</v>
       </c>
       <c r="E41" s="3">
-        <v>605700</v>
+        <v>500300</v>
       </c>
       <c r="F41" s="3">
-        <v>658000</v>
+        <v>607800</v>
       </c>
       <c r="G41" s="3">
-        <v>140300</v>
+        <v>660300</v>
       </c>
       <c r="H41" s="3">
-        <v>490900</v>
+        <v>140800</v>
       </c>
       <c r="I41" s="3">
-        <v>473100</v>
+        <v>492600</v>
       </c>
       <c r="J41" s="3">
+        <v>474700</v>
+      </c>
+      <c r="K41" s="3">
         <v>617100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>343400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>447900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>337100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>346500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>259100</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>342500</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>344700</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>355900</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>413500</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>305200</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>256800</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>425300</v>
       </c>
     </row>
-    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E42" s="3">
-        <v>0</v>
+      <c r="E42" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="F42" s="3">
         <v>0</v>
       </c>
       <c r="G42" s="3">
+        <v>0</v>
+      </c>
+      <c r="H42" s="3">
         <v>2600</v>
       </c>
-      <c r="H42" s="3">
-        <v>0</v>
-      </c>
       <c r="I42" s="3">
-        <v>40800</v>
+        <v>0</v>
       </c>
       <c r="J42" s="3">
+        <v>40900</v>
+      </c>
+      <c r="K42" s="3">
         <v>48500</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>84900</v>
       </c>
-      <c r="L42" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M42" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="N42" s="3">
-        <v>0</v>
-      </c>
-      <c r="O42" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P42" s="3">
+      <c r="N42" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O42" s="3">
+        <v>0</v>
+      </c>
+      <c r="P42" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q42" s="3">
         <v>1400</v>
       </c>
-      <c r="Q42" s="3">
-        <v>0</v>
-      </c>
       <c r="R42" s="3">
+        <v>0</v>
+      </c>
+      <c r="S42" s="3">
         <v>4900</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>5200</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>7800</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>23700</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>2600</v>
       </c>
     </row>
-    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>386400</v>
+        <v>380000</v>
       </c>
       <c r="E43" s="3">
-        <v>459000</v>
+        <v>387700</v>
       </c>
       <c r="F43" s="3">
-        <v>526600</v>
+        <v>460700</v>
       </c>
       <c r="G43" s="3">
-        <v>358300</v>
+        <v>528500</v>
       </c>
       <c r="H43" s="3">
-        <v>334100</v>
+        <v>359600</v>
       </c>
       <c r="I43" s="3">
-        <v>438600</v>
+        <v>335300</v>
       </c>
       <c r="J43" s="3">
+        <v>440200</v>
+      </c>
+      <c r="K43" s="3">
         <v>406800</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>422000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>397100</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>389200</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>425700</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>402300</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>450000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>385700</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>374400</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>396500</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>363900</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>384500</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>495100</v>
       </c>
     </row>
-    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>521500</v>
+        <v>451700</v>
       </c>
       <c r="E44" s="3">
-        <v>568700</v>
+        <v>523400</v>
       </c>
       <c r="F44" s="3">
-        <v>568700</v>
+        <v>570700</v>
       </c>
       <c r="G44" s="3">
-        <v>404200</v>
+        <v>570700</v>
       </c>
       <c r="H44" s="3">
-        <v>335400</v>
+        <v>405600</v>
       </c>
       <c r="I44" s="3">
-        <v>678400</v>
+        <v>336500</v>
       </c>
       <c r="J44" s="3">
+        <v>680800</v>
+      </c>
+      <c r="K44" s="3">
         <v>498600</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>577900</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>512500</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>513400</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>508700</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>571400</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>537700</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>582500</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>449500</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>507400</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>443500</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>478000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>331800</v>
       </c>
     </row>
-    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>0</v>
+      </c>
+      <c r="E45" s="3">
         <v>1300</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>3800</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>16600</v>
       </c>
-      <c r="G45" s="3">
-        <v>2231400</v>
-      </c>
       <c r="H45" s="3">
-        <v>1753300</v>
+        <v>2239300</v>
       </c>
       <c r="I45" s="3">
-        <v>29300</v>
+        <v>1759500</v>
       </c>
       <c r="J45" s="3">
+        <v>29400</v>
+      </c>
+      <c r="K45" s="3">
         <v>11500</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>6300</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>44700</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>56800</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>46400</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>32700</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>55200</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>40900</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>71400</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>65200</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>348300</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>81600</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>143500</v>
       </c>
     </row>
-    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>1407700</v>
+        <v>1390900</v>
       </c>
       <c r="E46" s="3">
-        <v>1637200</v>
+        <v>1412700</v>
       </c>
       <c r="F46" s="3">
-        <v>1769800</v>
+        <v>1643000</v>
       </c>
       <c r="G46" s="3">
-        <v>3136700</v>
+        <v>1776100</v>
       </c>
       <c r="H46" s="3">
-        <v>2913600</v>
+        <v>3147800</v>
       </c>
       <c r="I46" s="3">
-        <v>1660200</v>
+        <v>2923900</v>
       </c>
       <c r="J46" s="3">
+        <v>1666100</v>
+      </c>
+      <c r="K46" s="3">
         <v>1582400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1434600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1402100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1296500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1327300</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>1265600</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>1386800</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>1353800</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>1256200</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>1387800</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>1468700</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>1224600</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>1398400</v>
       </c>
     </row>
-    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>318800</v>
+        <v>261000</v>
       </c>
       <c r="E47" s="3">
-        <v>321300</v>
+        <v>319900</v>
       </c>
       <c r="F47" s="3">
-        <v>378700</v>
+        <v>322500</v>
       </c>
       <c r="G47" s="3">
-        <v>59900</v>
+        <v>380000</v>
       </c>
       <c r="H47" s="3">
-        <v>65000</v>
+        <v>60100</v>
       </c>
       <c r="I47" s="3">
+        <v>65300</v>
+      </c>
+      <c r="J47" s="3">
+        <v>209900</v>
+      </c>
+      <c r="K47" s="3">
         <v>209100</v>
       </c>
-      <c r="J47" s="3">
-        <v>209100</v>
-      </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>195200</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>198500</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>192800</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>158600</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>170500</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>154200</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>167700</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>136700</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>137000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>180000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>453000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>476700</v>
       </c>
     </row>
-    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>643900</v>
+        <v>675600</v>
       </c>
       <c r="E48" s="3">
-        <v>622200</v>
+        <v>646200</v>
       </c>
       <c r="F48" s="3">
-        <v>640100</v>
+        <v>624400</v>
       </c>
       <c r="G48" s="3">
-        <v>549600</v>
+        <v>642400</v>
       </c>
       <c r="H48" s="3">
-        <v>543200</v>
+        <v>551500</v>
       </c>
       <c r="I48" s="3">
-        <v>1409000</v>
+        <v>545100</v>
       </c>
       <c r="J48" s="3">
+        <v>1414000</v>
+      </c>
+      <c r="K48" s="3">
         <v>2937800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1508100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>1475300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>1161600</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>1206500</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>1316100</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>1416500</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>1401400</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>1272200</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>1207800</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>1006900</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>987600</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>995500</v>
       </c>
     </row>
-    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>548300</v>
+        <v>519500</v>
       </c>
       <c r="E49" s="3">
-        <v>576300</v>
+        <v>550200</v>
       </c>
       <c r="F49" s="3">
-        <v>635000</v>
+        <v>578400</v>
       </c>
       <c r="G49" s="3">
-        <v>354500</v>
+        <v>637200</v>
       </c>
       <c r="H49" s="3">
-        <v>369800</v>
+        <v>355700</v>
       </c>
       <c r="I49" s="3">
-        <v>439900</v>
+        <v>371100</v>
       </c>
       <c r="J49" s="3">
+        <v>441500</v>
+      </c>
+      <c r="K49" s="3">
         <v>406800</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>430900</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>431800</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>404600</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>431800</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>491000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>539200</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>529600</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>511100</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>508700</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>403000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>447700</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>418700</v>
       </c>
     </row>
-    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3109,8 +3223,11 @@
       <c r="V50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3171,70 +3288,76 @@
       <c r="V51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>52300</v>
+        <v>72900</v>
       </c>
       <c r="E52" s="3">
+        <v>52500</v>
+      </c>
+      <c r="F52" s="3">
+        <v>39700</v>
+      </c>
+      <c r="G52" s="3">
+        <v>35800</v>
+      </c>
+      <c r="H52" s="3">
+        <v>44800</v>
+      </c>
+      <c r="I52" s="3">
+        <v>84500</v>
+      </c>
+      <c r="J52" s="3">
+        <v>65300</v>
+      </c>
+      <c r="K52" s="3">
+        <v>53600</v>
+      </c>
+      <c r="L52" s="3">
+        <v>44400</v>
+      </c>
+      <c r="M52" s="3">
+        <v>42200</v>
+      </c>
+      <c r="N52" s="3">
+        <v>248400</v>
+      </c>
+      <c r="O52" s="3">
+        <v>241500</v>
+      </c>
+      <c r="P52" s="3">
+        <v>263200</v>
+      </c>
+      <c r="Q52" s="3">
+        <v>206600</v>
+      </c>
+      <c r="R52" s="3">
+        <v>207400</v>
+      </c>
+      <c r="S52" s="3">
+        <v>67700</v>
+      </c>
+      <c r="T52" s="3">
+        <v>90000</v>
+      </c>
+      <c r="U52" s="3">
+        <v>114800</v>
+      </c>
+      <c r="V52" s="3">
+        <v>77700</v>
+      </c>
+      <c r="W52" s="3">
         <v>39500</v>
       </c>
-      <c r="F52" s="3">
-        <v>35700</v>
-      </c>
-      <c r="G52" s="3">
-        <v>44600</v>
-      </c>
-      <c r="H52" s="3">
-        <v>84200</v>
-      </c>
-      <c r="I52" s="3">
-        <v>65000</v>
-      </c>
-      <c r="J52" s="3">
-        <v>53600</v>
-      </c>
-      <c r="K52" s="3">
-        <v>44400</v>
-      </c>
-      <c r="L52" s="3">
-        <v>42200</v>
-      </c>
-      <c r="M52" s="3">
-        <v>248400</v>
-      </c>
-      <c r="N52" s="3">
-        <v>241500</v>
-      </c>
-      <c r="O52" s="3">
-        <v>263200</v>
-      </c>
-      <c r="P52" s="3">
-        <v>206600</v>
-      </c>
-      <c r="Q52" s="3">
-        <v>207400</v>
-      </c>
-      <c r="R52" s="3">
-        <v>67700</v>
-      </c>
-      <c r="S52" s="3">
-        <v>90000</v>
-      </c>
-      <c r="T52" s="3">
-        <v>114800</v>
-      </c>
-      <c r="U52" s="3">
-        <v>77700</v>
-      </c>
-      <c r="V52" s="3">
-        <v>39500</v>
-      </c>
-    </row>
-    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3295,70 +3418,76 @@
       <c r="V53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>2971000</v>
+        <v>2920100</v>
       </c>
       <c r="E54" s="3">
-        <v>3196700</v>
+        <v>2981500</v>
       </c>
       <c r="F54" s="3">
-        <v>3459300</v>
+        <v>3208000</v>
       </c>
       <c r="G54" s="3">
-        <v>4145400</v>
+        <v>3471600</v>
       </c>
       <c r="H54" s="3">
-        <v>3975800</v>
+        <v>4160000</v>
       </c>
       <c r="I54" s="3">
-        <v>3783200</v>
+        <v>3989800</v>
       </c>
       <c r="J54" s="3">
+        <v>3796600</v>
+      </c>
+      <c r="K54" s="3">
         <v>3720700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>3613100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>3549900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>3303800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>3365700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>3506300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>3703300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>3659900</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>3244000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>3331200</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>3173400</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>3190600</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>3328800</v>
       </c>
     </row>
-    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3381,8 +3510,9 @@
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
-    </row>
-    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W55" s="3"/>
+    </row>
+    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3405,380 +3535,399 @@
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
-    </row>
-    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W56" s="3"/>
+    </row>
+    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>344300</v>
+        <v>331400</v>
       </c>
       <c r="E57" s="3">
-        <v>474300</v>
+        <v>345500</v>
       </c>
       <c r="F57" s="3">
-        <v>530400</v>
+        <v>476000</v>
       </c>
       <c r="G57" s="3">
-        <v>374900</v>
+        <v>532300</v>
       </c>
       <c r="H57" s="3">
-        <v>269000</v>
+        <v>376200</v>
       </c>
       <c r="I57" s="3">
-        <v>549600</v>
+        <v>270000</v>
       </c>
       <c r="J57" s="3">
+        <v>551500</v>
+      </c>
+      <c r="K57" s="3">
         <v>424600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>468900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>378400</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>404600</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>431800</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>425500</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>447200</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>416000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>397800</v>
-      </c>
-      <c r="S57" s="3">
-        <v>439600</v>
       </c>
       <c r="T57" s="3">
         <v>439600</v>
       </c>
       <c r="U57" s="3">
+        <v>439600</v>
+      </c>
+      <c r="V57" s="3">
         <v>416100</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>425300</v>
       </c>
     </row>
-    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>54800</v>
+        <v>21800</v>
       </c>
       <c r="E58" s="3">
-        <v>154300</v>
+        <v>55000</v>
       </c>
       <c r="F58" s="3">
-        <v>34400</v>
+        <v>154800</v>
       </c>
       <c r="G58" s="3">
-        <v>26800</v>
+        <v>34500</v>
       </c>
       <c r="H58" s="3">
-        <v>31900</v>
+        <v>26900</v>
       </c>
       <c r="I58" s="3">
+        <v>32000</v>
+      </c>
+      <c r="J58" s="3">
+        <v>107500</v>
+      </c>
+      <c r="K58" s="3">
         <v>107100</v>
       </c>
-      <c r="J58" s="3">
-        <v>107100</v>
-      </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>50700</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>317600</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>265000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>29300</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>21800</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>39600</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>116200</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>129300</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>260900</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>644300</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>401600</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>468800</v>
       </c>
     </row>
-    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>89300</v>
+        <v>79300</v>
       </c>
       <c r="E59" s="3">
-        <v>100700</v>
+        <v>89600</v>
       </c>
       <c r="F59" s="3">
-        <v>105800</v>
+        <v>101100</v>
       </c>
       <c r="G59" s="3">
-        <v>592900</v>
+        <v>106200</v>
       </c>
       <c r="H59" s="3">
-        <v>660500</v>
+        <v>595000</v>
       </c>
       <c r="I59" s="3">
-        <v>107100</v>
+        <v>662800</v>
       </c>
       <c r="J59" s="3">
+        <v>107500</v>
+      </c>
+      <c r="K59" s="3">
         <v>104600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>124200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>143900</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>136000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>135400</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>100900</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>113200</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>110900</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>150300</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>147400</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>159100</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>109300</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>142200</v>
       </c>
     </row>
-    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>488400</v>
+        <v>432500</v>
       </c>
       <c r="E60" s="3">
-        <v>729400</v>
+        <v>490100</v>
       </c>
       <c r="F60" s="3">
-        <v>670700</v>
+        <v>731900</v>
       </c>
       <c r="G60" s="3">
-        <v>994600</v>
+        <v>673100</v>
       </c>
       <c r="H60" s="3">
-        <v>961400</v>
+        <v>998100</v>
       </c>
       <c r="I60" s="3">
-        <v>710200</v>
+        <v>964800</v>
       </c>
       <c r="J60" s="3">
+        <v>712700</v>
+      </c>
+      <c r="K60" s="3">
         <v>582700</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>643800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>840000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>805600</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>596500</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>548200</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>600000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>643200</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>677400</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>847800</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>1243000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>927000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>1036300</v>
       </c>
     </row>
-    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>761200</v>
+        <v>733200</v>
       </c>
       <c r="E61" s="3">
-        <v>754900</v>
+        <v>763900</v>
       </c>
       <c r="F61" s="3">
-        <v>981800</v>
+        <v>757500</v>
       </c>
       <c r="G61" s="3">
-        <v>839000</v>
+        <v>985300</v>
       </c>
       <c r="H61" s="3">
-        <v>891300</v>
+        <v>842000</v>
       </c>
       <c r="I61" s="3">
-        <v>951200</v>
+        <v>894400</v>
       </c>
       <c r="J61" s="3">
+        <v>954600</v>
+      </c>
+      <c r="K61" s="3">
         <v>1020100</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>864300</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>667600</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>441200</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>703900</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>755500</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>812300</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>797800</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>731600</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>725200</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>371700</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>609700</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>579400</v>
       </c>
     </row>
-    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>178500</v>
+        <v>168900</v>
       </c>
       <c r="E62" s="3">
-        <v>195100</v>
+        <v>179100</v>
       </c>
       <c r="F62" s="3">
-        <v>248600</v>
+        <v>195800</v>
       </c>
       <c r="G62" s="3">
-        <v>246100</v>
+        <v>249500</v>
       </c>
       <c r="H62" s="3">
-        <v>200200</v>
+        <v>247000</v>
       </c>
       <c r="I62" s="3">
-        <v>267800</v>
+        <v>200900</v>
       </c>
       <c r="J62" s="3">
+        <v>268700</v>
+      </c>
+      <c r="K62" s="3">
         <v>303500</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>332000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>332500</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>295700</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>342800</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>338200</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>459900</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>459600</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>456900</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>416100</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>400400</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>421400</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>337100</v>
       </c>
     </row>
-    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3839,8 +3988,11 @@
       <c r="V63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3901,8 +4053,11 @@
       <c r="V64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3963,70 +4118,76 @@
       <c r="V65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>1429400</v>
+        <v>1335900</v>
       </c>
       <c r="E66" s="3">
-        <v>1680600</v>
+        <v>1434400</v>
       </c>
       <c r="F66" s="3">
-        <v>1902400</v>
+        <v>1686500</v>
       </c>
       <c r="G66" s="3">
-        <v>2081000</v>
+        <v>1909200</v>
       </c>
       <c r="H66" s="3">
-        <v>2054200</v>
+        <v>2088300</v>
       </c>
       <c r="I66" s="3">
-        <v>1930500</v>
+        <v>2061500</v>
       </c>
       <c r="J66" s="3">
+        <v>1937300</v>
+      </c>
+      <c r="K66" s="3">
         <v>1906300</v>
-      </c>
-      <c r="K66" s="3">
-        <v>1840100</v>
       </c>
       <c r="L66" s="3">
         <v>1840100</v>
       </c>
       <c r="M66" s="3">
+        <v>1840100</v>
+      </c>
+      <c r="N66" s="3">
         <v>1542500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1643200</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1642000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1872200</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1900600</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>1865900</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>1990400</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>2016500</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>1959400</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>1954100</v>
       </c>
     </row>
-    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4049,8 +4210,9 @@
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
-    </row>
-    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W67" s="3"/>
+    </row>
+    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4111,8 +4273,11 @@
       <c r="V68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4173,8 +4338,11 @@
       <c r="V69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4235,8 +4403,11 @@
       <c r="V70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4297,70 +4468,76 @@
       <c r="V71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>872200</v>
+        <v>912400</v>
       </c>
       <c r="E72" s="3">
-        <v>846700</v>
+        <v>875300</v>
       </c>
       <c r="F72" s="3">
-        <v>888700</v>
+        <v>849700</v>
       </c>
       <c r="G72" s="3">
-        <v>1396200</v>
+        <v>891900</v>
       </c>
       <c r="H72" s="3">
-        <v>1253400</v>
+        <v>1401200</v>
       </c>
       <c r="I72" s="3">
-        <v>1184600</v>
+        <v>1257900</v>
       </c>
       <c r="J72" s="3">
+        <v>1188800</v>
+      </c>
+      <c r="K72" s="3">
         <v>1146300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>1110200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>1060900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>1142700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>1084500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>1151000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>1091000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>1068500</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>734000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>658700</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>474800</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>542500</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>686000</v>
       </c>
     </row>
-    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4421,8 +4598,11 @@
       <c r="V73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4483,8 +4663,11 @@
       <c r="V74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4545,70 +4728,76 @@
       <c r="V75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>1541600</v>
+        <v>1584200</v>
       </c>
       <c r="E76" s="3">
-        <v>1516100</v>
+        <v>1547000</v>
       </c>
       <c r="F76" s="3">
-        <v>1556900</v>
+        <v>1521500</v>
       </c>
       <c r="G76" s="3">
-        <v>2064400</v>
+        <v>1562400</v>
       </c>
       <c r="H76" s="3">
-        <v>1921600</v>
+        <v>2071700</v>
       </c>
       <c r="I76" s="3">
-        <v>1852700</v>
+        <v>1928400</v>
       </c>
       <c r="J76" s="3">
+        <v>1859300</v>
+      </c>
+      <c r="K76" s="3">
         <v>1814500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1773000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1709800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>1761300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>1722500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>1864300</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>1831200</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>1759300</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>1378200</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>1340800</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>1156900</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>1231200</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>1374700</v>
       </c>
     </row>
-    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4669,137 +4858,146 @@
       <c r="V77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45016</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44834</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44651</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44469</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44286</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44104</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>43921</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>43738</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>43555</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>43373</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>43190</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>43008</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>42825</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>42643</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>42460</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>42277</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>42094</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>41912</v>
       </c>
     </row>
-    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>130100</v>
+        <v>110000</v>
       </c>
       <c r="E81" s="3">
-        <v>88000</v>
+        <v>130500</v>
       </c>
       <c r="F81" s="3">
-        <v>154300</v>
+        <v>88300</v>
       </c>
       <c r="G81" s="3">
-        <v>170900</v>
+        <v>154800</v>
       </c>
       <c r="H81" s="3">
-        <v>130100</v>
+        <v>171500</v>
       </c>
       <c r="I81" s="3">
-        <v>153000</v>
+        <v>130500</v>
       </c>
       <c r="J81" s="3">
+        <v>153600</v>
+      </c>
+      <c r="K81" s="3">
         <v>169600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>144500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>162500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>118300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>98800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>192300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>175500</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>166400</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>160100</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>148700</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>63900</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-50000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>89500</v>
       </c>
     </row>
-    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4822,70 +5020,74 @@
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
-    </row>
-    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W82" s="3"/>
+    </row>
+    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>59900</v>
+        <v>60100</v>
       </c>
       <c r="E83" s="3">
-        <v>61200</v>
+        <v>60100</v>
       </c>
       <c r="F83" s="3">
-        <v>59900</v>
+        <v>61400</v>
       </c>
       <c r="G83" s="3">
-        <v>49700</v>
+        <v>60100</v>
       </c>
       <c r="H83" s="3">
-        <v>77800</v>
+        <v>49900</v>
       </c>
       <c r="I83" s="3">
-        <v>110900</v>
+        <v>78100</v>
       </c>
       <c r="J83" s="3">
+        <v>111300</v>
+      </c>
+      <c r="K83" s="3">
         <v>112200</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>95000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>120400</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>91100</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>91500</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>106400</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>107500</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>105700</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>85000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>78300</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>71700</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>76400</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>67200</v>
       </c>
     </row>
-    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4946,8 +5148,11 @@
       <c r="V84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5008,8 +5213,11 @@
       <c r="V85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5070,8 +5278,11 @@
       <c r="V86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5132,8 +5343,11 @@
       <c r="V87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5194,70 +5408,76 @@
       <c r="V88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>109700</v>
+        <v>156100</v>
       </c>
       <c r="E89" s="3">
-        <v>35700</v>
+        <v>110000</v>
       </c>
       <c r="F89" s="3">
-        <v>48500</v>
+        <v>35800</v>
       </c>
       <c r="G89" s="3">
-        <v>-96900</v>
+        <v>48600</v>
       </c>
       <c r="H89" s="3">
-        <v>228200</v>
+        <v>-97300</v>
       </c>
       <c r="I89" s="3">
-        <v>158100</v>
+        <v>229100</v>
       </c>
       <c r="J89" s="3">
+        <v>158700</v>
+      </c>
+      <c r="K89" s="3">
         <v>312400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>196400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>285400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>140800</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>257400</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>105000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>295800</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>130800</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>245100</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>19600</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>225600</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>72400</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>163300</v>
       </c>
     </row>
-    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5280,70 +5500,74 @@
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
-    </row>
-    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W90" s="3"/>
+    </row>
+    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-64000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-46000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-45000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-33000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-81000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-67000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-83000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-69000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-94000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-73000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-67400</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-56100</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-81800</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-72200</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-76600</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-85000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-133000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-100400</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-216000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-192300</v>
       </c>
     </row>
-    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5404,8 +5628,11 @@
       <c r="V92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5466,70 +5693,76 @@
       <c r="V93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-15300</v>
+        <v>-10200</v>
       </c>
       <c r="E94" s="3">
-        <v>20400</v>
+        <v>-15400</v>
       </c>
       <c r="F94" s="3">
-        <v>1044300</v>
+        <v>20500</v>
       </c>
       <c r="G94" s="3">
-        <v>-91800</v>
+        <v>1048000</v>
       </c>
       <c r="H94" s="3">
-        <v>-52300</v>
+        <v>-92100</v>
       </c>
       <c r="I94" s="3">
-        <v>-184900</v>
+        <v>-52500</v>
       </c>
       <c r="J94" s="3">
+        <v>-185500</v>
+      </c>
+      <c r="K94" s="3">
         <v>-76500</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-106500</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-55800</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-95800</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-36600</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-83200</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-58000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-87200</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-59100</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>183900</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-71700</v>
-      </c>
-      <c r="U94" s="3">
-        <v>-108000</v>
       </c>
       <c r="V94" s="3">
         <v>-108000</v>
       </c>
-    </row>
-    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W94" s="3">
+        <v>-108000</v>
+      </c>
+    </row>
+    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5552,70 +5785,74 @@
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
-    </row>
-    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W95" s="3"/>
+    </row>
+    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-66300</v>
+        <v>-30700</v>
       </c>
       <c r="E96" s="3">
-        <v>-28100</v>
+        <v>-66500</v>
       </c>
       <c r="F96" s="3">
-        <v>-698800</v>
+        <v>-28200</v>
       </c>
       <c r="G96" s="3">
-        <v>-53600</v>
+        <v>-701200</v>
       </c>
       <c r="H96" s="3">
-        <v>-130100</v>
+        <v>-53700</v>
       </c>
       <c r="I96" s="3">
-        <v>-51000</v>
+        <v>-130500</v>
       </c>
       <c r="J96" s="3">
+        <v>-51200</v>
+      </c>
+      <c r="K96" s="3">
         <v>-123700</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-50700</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-120400</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-47300</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-114700</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-53200</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-130200</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-50200</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-113300</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-49600</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-120000</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-50000</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-121100</v>
       </c>
     </row>
-    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5676,8 +5913,11 @@
       <c r="V97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5738,8 +5978,11 @@
       <c r="V98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5800,190 +6043,202 @@
       <c r="V99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-202700</v>
+        <v>-71700</v>
       </c>
       <c r="E100" s="3">
-        <v>-48500</v>
+        <v>-203500</v>
       </c>
       <c r="F100" s="3">
-        <v>-714100</v>
+        <v>-48600</v>
       </c>
       <c r="G100" s="3">
-        <v>-160700</v>
+        <v>-716600</v>
       </c>
       <c r="H100" s="3">
-        <v>-154300</v>
+        <v>-161200</v>
       </c>
       <c r="I100" s="3">
-        <v>-80300</v>
+        <v>-154800</v>
       </c>
       <c r="J100" s="3">
+        <v>-80600</v>
+      </c>
+      <c r="K100" s="3">
         <v>43400</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-188800</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-153900</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-46100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-123200</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-80500</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-244800</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-93800</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-247600</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-116100</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-100400</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-151400</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-92200</v>
       </c>
     </row>
-    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-15400</v>
+      </c>
+      <c r="E101" s="3">
         <v>1300</v>
       </c>
-      <c r="E101" s="3">
-        <v>-59900</v>
-      </c>
       <c r="F101" s="3">
-        <v>117300</v>
+        <v>-60100</v>
       </c>
       <c r="G101" s="3">
+        <v>117700</v>
+      </c>
+      <c r="H101" s="3">
         <v>6400</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>10200</v>
       </c>
-      <c r="I101" s="3">
-        <v>-37000</v>
-      </c>
       <c r="J101" s="3">
+        <v>-37100</v>
+      </c>
+      <c r="K101" s="3">
         <v>-7700</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-15200</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>18600</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>2400</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>17100</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-12300</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-19800</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>13200</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>27100</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>20900</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-2600</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>18400</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>6600</v>
       </c>
     </row>
-    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-107100</v>
+        <v>58900</v>
       </c>
       <c r="E102" s="3">
-        <v>-52300</v>
+        <v>-107500</v>
       </c>
       <c r="F102" s="3">
-        <v>496000</v>
+        <v>-52500</v>
       </c>
       <c r="G102" s="3">
-        <v>-343000</v>
+        <v>497800</v>
       </c>
       <c r="H102" s="3">
-        <v>31900</v>
+        <v>-344200</v>
       </c>
       <c r="I102" s="3">
-        <v>-144100</v>
+        <v>32000</v>
       </c>
       <c r="J102" s="3">
+        <v>-144600</v>
+      </c>
+      <c r="K102" s="3">
         <v>271600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-114100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>94300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>1200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>114700</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-70900</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-26900</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-37000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-34500</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>108300</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>50900</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-168500</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-30300</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/TATYY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/TATYY_QTR_FIN.xlsx
@@ -765,25 +765,25 @@
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>1010900</v>
+        <v>1036600</v>
       </c>
       <c r="E8" s="3">
-        <v>1096600</v>
+        <v>1124600</v>
       </c>
       <c r="F8" s="3">
-        <v>1154200</v>
+        <v>1183600</v>
       </c>
       <c r="G8" s="3">
-        <v>1086400</v>
+        <v>1114100</v>
       </c>
       <c r="H8" s="3">
-        <v>920000</v>
+        <v>943500</v>
       </c>
       <c r="I8" s="3">
-        <v>839400</v>
+        <v>860800</v>
       </c>
       <c r="J8" s="3">
-        <v>792100</v>
+        <v>812300</v>
       </c>
       <c r="K8" s="3">
         <v>754900</v>
@@ -1115,25 +1115,25 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>23000</v>
+        <v>23600</v>
       </c>
       <c r="E14" s="3">
-        <v>10200</v>
+        <v>10500</v>
       </c>
       <c r="F14" s="3">
-        <v>21800</v>
+        <v>22300</v>
       </c>
       <c r="G14" s="3">
-        <v>14100</v>
+        <v>14400</v>
       </c>
       <c r="H14" s="3">
-        <v>30700</v>
+        <v>31500</v>
       </c>
       <c r="I14" s="3">
-        <v>75500</v>
+        <v>77400</v>
       </c>
       <c r="J14" s="3">
-        <v>24300</v>
+        <v>24900</v>
       </c>
       <c r="K14" s="3">
         <v>19100</v>
@@ -1186,19 +1186,19 @@
         <v>5</v>
       </c>
       <c r="F15" s="3">
-        <v>30700</v>
+        <v>31500</v>
       </c>
       <c r="G15" s="3">
-        <v>15400</v>
+        <v>15700</v>
       </c>
       <c r="H15" s="3">
-        <v>24300</v>
+        <v>24900</v>
       </c>
       <c r="I15" s="3">
-        <v>6400</v>
+        <v>6600</v>
       </c>
       <c r="J15" s="3">
-        <v>26900</v>
+        <v>27600</v>
       </c>
       <c r="K15" s="3">
         <v>6400</v>
@@ -1267,25 +1267,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>903400</v>
+        <v>926400</v>
       </c>
       <c r="E17" s="3">
-        <v>939200</v>
+        <v>963200</v>
       </c>
       <c r="F17" s="3">
-        <v>1049300</v>
+        <v>1076000</v>
       </c>
       <c r="G17" s="3">
-        <v>940500</v>
+        <v>964500</v>
       </c>
       <c r="H17" s="3">
-        <v>876500</v>
+        <v>898900</v>
       </c>
       <c r="I17" s="3">
-        <v>797200</v>
+        <v>817500</v>
       </c>
       <c r="J17" s="3">
-        <v>734500</v>
+        <v>753200</v>
       </c>
       <c r="K17" s="3">
         <v>664300</v>
@@ -1332,25 +1332,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>107500</v>
+        <v>110200</v>
       </c>
       <c r="E18" s="3">
-        <v>157400</v>
+        <v>161400</v>
       </c>
       <c r="F18" s="3">
-        <v>104900</v>
+        <v>107600</v>
       </c>
       <c r="G18" s="3">
-        <v>145900</v>
+        <v>149600</v>
       </c>
       <c r="H18" s="3">
-        <v>43500</v>
+        <v>44600</v>
       </c>
       <c r="I18" s="3">
-        <v>42200</v>
+        <v>43300</v>
       </c>
       <c r="J18" s="3">
-        <v>57600</v>
+        <v>59000</v>
       </c>
       <c r="K18" s="3">
         <v>90500</v>
@@ -1422,25 +1422,25 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>15400</v>
+        <v>15700</v>
       </c>
       <c r="E20" s="3">
-        <v>9000</v>
+        <v>9200</v>
       </c>
       <c r="F20" s="3">
         <v>2600</v>
       </c>
       <c r="G20" s="3">
-        <v>-58900</v>
+        <v>-60400</v>
       </c>
       <c r="H20" s="3">
-        <v>-16600</v>
+        <v>-17100</v>
       </c>
       <c r="I20" s="3">
-        <v>-15400</v>
+        <v>-15700</v>
       </c>
       <c r="J20" s="3">
-        <v>-16600</v>
+        <v>-17100</v>
       </c>
       <c r="K20" s="3">
         <v>-16600</v>
@@ -1487,25 +1487,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>183000</v>
+        <v>187600</v>
       </c>
       <c r="E21" s="3">
-        <v>226500</v>
+        <v>232300</v>
       </c>
       <c r="F21" s="3">
-        <v>168900</v>
+        <v>173200</v>
       </c>
       <c r="G21" s="3">
-        <v>147200</v>
+        <v>150900</v>
       </c>
       <c r="H21" s="3">
-        <v>76800</v>
+        <v>78700</v>
       </c>
       <c r="I21" s="3">
-        <v>104900</v>
+        <v>107600</v>
       </c>
       <c r="J21" s="3">
-        <v>152300</v>
+        <v>156200</v>
       </c>
       <c r="K21" s="3">
         <v>186200</v>
@@ -1617,25 +1617,25 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>122800</v>
+        <v>126000</v>
       </c>
       <c r="E23" s="3">
-        <v>166300</v>
+        <v>170600</v>
       </c>
       <c r="F23" s="3">
-        <v>107500</v>
+        <v>110200</v>
       </c>
       <c r="G23" s="3">
-        <v>87000</v>
+        <v>89200</v>
       </c>
       <c r="H23" s="3">
-        <v>26900</v>
+        <v>27600</v>
       </c>
       <c r="I23" s="3">
-        <v>26900</v>
+        <v>27600</v>
       </c>
       <c r="J23" s="3">
-        <v>40900</v>
+        <v>42000</v>
       </c>
       <c r="K23" s="3">
         <v>74000</v>
@@ -1682,25 +1682,25 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>30700</v>
+        <v>31500</v>
       </c>
       <c r="E24" s="3">
-        <v>38400</v>
+        <v>39400</v>
       </c>
       <c r="F24" s="3">
-        <v>21800</v>
+        <v>22300</v>
       </c>
       <c r="G24" s="3">
-        <v>17900</v>
+        <v>18400</v>
       </c>
       <c r="H24" s="3">
-        <v>-5100</v>
+        <v>-5200</v>
       </c>
       <c r="I24" s="3">
-        <v>16600</v>
+        <v>17100</v>
       </c>
       <c r="J24" s="3">
-        <v>-3800</v>
+        <v>-3900</v>
       </c>
       <c r="K24" s="3">
         <v>20400</v>
@@ -1812,25 +1812,25 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>92100</v>
+        <v>94500</v>
       </c>
       <c r="E26" s="3">
-        <v>128000</v>
+        <v>131200</v>
       </c>
       <c r="F26" s="3">
-        <v>85700</v>
+        <v>87900</v>
       </c>
       <c r="G26" s="3">
-        <v>69100</v>
+        <v>70900</v>
       </c>
       <c r="H26" s="3">
-        <v>32000</v>
+        <v>32800</v>
       </c>
       <c r="I26" s="3">
-        <v>10200</v>
+        <v>10500</v>
       </c>
       <c r="J26" s="3">
-        <v>44800</v>
+        <v>45900</v>
       </c>
       <c r="K26" s="3">
         <v>53600</v>
@@ -1877,25 +1877,25 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>92100</v>
+        <v>94500</v>
       </c>
       <c r="E27" s="3">
-        <v>128000</v>
+        <v>131200</v>
       </c>
       <c r="F27" s="3">
-        <v>85700</v>
+        <v>87900</v>
       </c>
       <c r="G27" s="3">
-        <v>69100</v>
+        <v>70900</v>
       </c>
       <c r="H27" s="3">
-        <v>32000</v>
+        <v>32800</v>
       </c>
       <c r="I27" s="3">
-        <v>10200</v>
+        <v>10500</v>
       </c>
       <c r="J27" s="3">
-        <v>44800</v>
+        <v>45900</v>
       </c>
       <c r="K27" s="3">
         <v>53600</v>
@@ -2007,7 +2007,7 @@
         <v>24</v>
       </c>
       <c r="D29" s="3">
-        <v>17900</v>
+        <v>18400</v>
       </c>
       <c r="E29" s="3">
         <v>2600</v>
@@ -2016,16 +2016,16 @@
         <v>2600</v>
       </c>
       <c r="G29" s="3">
-        <v>85700</v>
+        <v>87900</v>
       </c>
       <c r="H29" s="3">
-        <v>139500</v>
+        <v>143000</v>
       </c>
       <c r="I29" s="3">
-        <v>120300</v>
+        <v>123300</v>
       </c>
       <c r="J29" s="3">
-        <v>108800</v>
+        <v>111500</v>
       </c>
       <c r="K29" s="3">
         <v>116000</v>
@@ -2202,25 +2202,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-15400</v>
+        <v>-15700</v>
       </c>
       <c r="E32" s="3">
-        <v>-9000</v>
+        <v>-9200</v>
       </c>
       <c r="F32" s="3">
         <v>-2600</v>
       </c>
       <c r="G32" s="3">
-        <v>58900</v>
+        <v>60400</v>
       </c>
       <c r="H32" s="3">
-        <v>16600</v>
+        <v>17100</v>
       </c>
       <c r="I32" s="3">
-        <v>15400</v>
+        <v>15700</v>
       </c>
       <c r="J32" s="3">
-        <v>16600</v>
+        <v>17100</v>
       </c>
       <c r="K32" s="3">
         <v>16600</v>
@@ -2267,25 +2267,25 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>110000</v>
+        <v>112800</v>
       </c>
       <c r="E33" s="3">
-        <v>130500</v>
+        <v>133800</v>
       </c>
       <c r="F33" s="3">
-        <v>88300</v>
+        <v>90500</v>
       </c>
       <c r="G33" s="3">
-        <v>154800</v>
+        <v>158800</v>
       </c>
       <c r="H33" s="3">
-        <v>171500</v>
+        <v>175800</v>
       </c>
       <c r="I33" s="3">
-        <v>130500</v>
+        <v>133800</v>
       </c>
       <c r="J33" s="3">
-        <v>153600</v>
+        <v>157500</v>
       </c>
       <c r="K33" s="3">
         <v>169600</v>
@@ -2397,25 +2397,25 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>110000</v>
+        <v>112800</v>
       </c>
       <c r="E35" s="3">
-        <v>130500</v>
+        <v>133800</v>
       </c>
       <c r="F35" s="3">
-        <v>88300</v>
+        <v>90500</v>
       </c>
       <c r="G35" s="3">
-        <v>154800</v>
+        <v>158800</v>
       </c>
       <c r="H35" s="3">
-        <v>171500</v>
+        <v>175800</v>
       </c>
       <c r="I35" s="3">
-        <v>130500</v>
+        <v>133800</v>
       </c>
       <c r="J35" s="3">
-        <v>153600</v>
+        <v>157500</v>
       </c>
       <c r="K35" s="3">
         <v>169600</v>
@@ -2582,25 +2582,25 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>559200</v>
+        <v>573400</v>
       </c>
       <c r="E41" s="3">
-        <v>500300</v>
+        <v>513100</v>
       </c>
       <c r="F41" s="3">
-        <v>607800</v>
+        <v>623300</v>
       </c>
       <c r="G41" s="3">
-        <v>660300</v>
+        <v>677100</v>
       </c>
       <c r="H41" s="3">
-        <v>140800</v>
+        <v>166600</v>
       </c>
       <c r="I41" s="3">
-        <v>492600</v>
+        <v>505200</v>
       </c>
       <c r="J41" s="3">
-        <v>474700</v>
+        <v>486800</v>
       </c>
       <c r="K41" s="3">
         <v>617100</v>
@@ -2665,7 +2665,7 @@
         <v>0</v>
       </c>
       <c r="J42" s="3">
-        <v>40900</v>
+        <v>42000</v>
       </c>
       <c r="K42" s="3">
         <v>48500</v>
@@ -2712,25 +2712,25 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>380000</v>
+        <v>368700</v>
       </c>
       <c r="E43" s="3">
-        <v>387700</v>
+        <v>397600</v>
       </c>
       <c r="F43" s="3">
-        <v>460700</v>
+        <v>451400</v>
       </c>
       <c r="G43" s="3">
-        <v>528500</v>
+        <v>541900</v>
       </c>
       <c r="H43" s="3">
-        <v>359600</v>
+        <v>347700</v>
       </c>
       <c r="I43" s="3">
-        <v>335300</v>
+        <v>343800</v>
       </c>
       <c r="J43" s="3">
-        <v>440200</v>
+        <v>433000</v>
       </c>
       <c r="K43" s="3">
         <v>406800</v>
@@ -2777,25 +2777,25 @@
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>451700</v>
+        <v>463200</v>
       </c>
       <c r="E44" s="3">
-        <v>523400</v>
+        <v>536700</v>
       </c>
       <c r="F44" s="3">
-        <v>570700</v>
+        <v>585200</v>
       </c>
       <c r="G44" s="3">
-        <v>570700</v>
+        <v>585200</v>
       </c>
       <c r="H44" s="3">
-        <v>405600</v>
+        <v>416000</v>
       </c>
       <c r="I44" s="3">
-        <v>336500</v>
+        <v>345100</v>
       </c>
       <c r="J44" s="3">
-        <v>680800</v>
+        <v>698100</v>
       </c>
       <c r="K44" s="3">
         <v>498600</v>
@@ -2842,25 +2842,25 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>0</v>
+        <v>21000</v>
       </c>
       <c r="E45" s="3">
         <v>1300</v>
       </c>
       <c r="F45" s="3">
-        <v>3800</v>
+        <v>24900</v>
       </c>
       <c r="G45" s="3">
-        <v>16600</v>
+        <v>17100</v>
       </c>
       <c r="H45" s="3">
-        <v>2239300</v>
+        <v>2295000</v>
       </c>
       <c r="I45" s="3">
-        <v>1759500</v>
+        <v>1804300</v>
       </c>
       <c r="J45" s="3">
-        <v>29400</v>
+        <v>48600</v>
       </c>
       <c r="K45" s="3">
         <v>11500</v>
@@ -2907,25 +2907,25 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>1390900</v>
+        <v>1426400</v>
       </c>
       <c r="E46" s="3">
-        <v>1412700</v>
+        <v>1448700</v>
       </c>
       <c r="F46" s="3">
-        <v>1643000</v>
+        <v>1684900</v>
       </c>
       <c r="G46" s="3">
-        <v>1776100</v>
+        <v>1821300</v>
       </c>
       <c r="H46" s="3">
-        <v>3147800</v>
+        <v>3228000</v>
       </c>
       <c r="I46" s="3">
-        <v>2923900</v>
+        <v>2998400</v>
       </c>
       <c r="J46" s="3">
-        <v>1666100</v>
+        <v>1708500</v>
       </c>
       <c r="K46" s="3">
         <v>1582400</v>
@@ -2972,25 +2972,25 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>261000</v>
+        <v>267700</v>
       </c>
       <c r="E47" s="3">
-        <v>319900</v>
+        <v>328100</v>
       </c>
       <c r="F47" s="3">
-        <v>322500</v>
+        <v>330700</v>
       </c>
       <c r="G47" s="3">
-        <v>380000</v>
+        <v>389700</v>
       </c>
       <c r="H47" s="3">
-        <v>60100</v>
+        <v>61700</v>
       </c>
       <c r="I47" s="3">
-        <v>65300</v>
+        <v>66900</v>
       </c>
       <c r="J47" s="3">
-        <v>209900</v>
+        <v>215200</v>
       </c>
       <c r="K47" s="3">
         <v>209100</v>
@@ -3037,25 +3037,25 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>675600</v>
+        <v>692800</v>
       </c>
       <c r="E48" s="3">
-        <v>646200</v>
+        <v>662700</v>
       </c>
       <c r="F48" s="3">
-        <v>624400</v>
+        <v>640400</v>
       </c>
       <c r="G48" s="3">
-        <v>642400</v>
+        <v>658700</v>
       </c>
       <c r="H48" s="3">
-        <v>551500</v>
+        <v>565600</v>
       </c>
       <c r="I48" s="3">
-        <v>545100</v>
+        <v>559000</v>
       </c>
       <c r="J48" s="3">
-        <v>1414000</v>
+        <v>1450000</v>
       </c>
       <c r="K48" s="3">
         <v>2937800</v>
@@ -3102,25 +3102,25 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>519500</v>
+        <v>532800</v>
       </c>
       <c r="E49" s="3">
-        <v>550200</v>
+        <v>564200</v>
       </c>
       <c r="F49" s="3">
-        <v>578400</v>
+        <v>593100</v>
       </c>
       <c r="G49" s="3">
-        <v>637200</v>
+        <v>653500</v>
       </c>
       <c r="H49" s="3">
-        <v>355700</v>
+        <v>364800</v>
       </c>
       <c r="I49" s="3">
-        <v>371100</v>
+        <v>380500</v>
       </c>
       <c r="J49" s="3">
-        <v>441500</v>
+        <v>452700</v>
       </c>
       <c r="K49" s="3">
         <v>406800</v>
@@ -3297,25 +3297,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>72900</v>
+        <v>74800</v>
       </c>
       <c r="E52" s="3">
-        <v>52500</v>
+        <v>53800</v>
       </c>
       <c r="F52" s="3">
-        <v>39700</v>
+        <v>40700</v>
       </c>
       <c r="G52" s="3">
-        <v>35800</v>
+        <v>36700</v>
       </c>
       <c r="H52" s="3">
-        <v>44800</v>
+        <v>45900</v>
       </c>
       <c r="I52" s="3">
-        <v>84500</v>
+        <v>86600</v>
       </c>
       <c r="J52" s="3">
-        <v>65300</v>
+        <v>66900</v>
       </c>
       <c r="K52" s="3">
         <v>53600</v>
@@ -3427,25 +3427,25 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>2920100</v>
+        <v>2994400</v>
       </c>
       <c r="E54" s="3">
-        <v>2981500</v>
+        <v>3057400</v>
       </c>
       <c r="F54" s="3">
-        <v>3208000</v>
+        <v>3289700</v>
       </c>
       <c r="G54" s="3">
-        <v>3471600</v>
+        <v>3560000</v>
       </c>
       <c r="H54" s="3">
-        <v>4160000</v>
+        <v>4266000</v>
       </c>
       <c r="I54" s="3">
-        <v>3989800</v>
+        <v>4091400</v>
       </c>
       <c r="J54" s="3">
-        <v>3796600</v>
+        <v>3893300</v>
       </c>
       <c r="K54" s="3">
         <v>3720700</v>
@@ -3542,25 +3542,25 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>331400</v>
+        <v>228300</v>
       </c>
       <c r="E57" s="3">
-        <v>345500</v>
+        <v>354300</v>
       </c>
       <c r="F57" s="3">
-        <v>476000</v>
+        <v>328100</v>
       </c>
       <c r="G57" s="3">
-        <v>532300</v>
+        <v>545900</v>
       </c>
       <c r="H57" s="3">
-        <v>376200</v>
+        <v>198100</v>
       </c>
       <c r="I57" s="3">
-        <v>270000</v>
+        <v>276900</v>
       </c>
       <c r="J57" s="3">
-        <v>551500</v>
+        <v>350400</v>
       </c>
       <c r="K57" s="3">
         <v>424600</v>
@@ -3607,25 +3607,25 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>21800</v>
+        <v>22300</v>
       </c>
       <c r="E58" s="3">
-        <v>55000</v>
+        <v>56400</v>
       </c>
       <c r="F58" s="3">
-        <v>154800</v>
+        <v>158800</v>
       </c>
       <c r="G58" s="3">
-        <v>34500</v>
+        <v>35400</v>
       </c>
       <c r="H58" s="3">
-        <v>26900</v>
+        <v>42000</v>
       </c>
       <c r="I58" s="3">
-        <v>32000</v>
+        <v>32800</v>
       </c>
       <c r="J58" s="3">
-        <v>107500</v>
+        <v>74800</v>
       </c>
       <c r="K58" s="3">
         <v>107100</v>
@@ -3672,25 +3672,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>79300</v>
+        <v>192900</v>
       </c>
       <c r="E59" s="3">
-        <v>89600</v>
+        <v>91900</v>
       </c>
       <c r="F59" s="3">
-        <v>101100</v>
+        <v>263800</v>
       </c>
       <c r="G59" s="3">
-        <v>106200</v>
+        <v>108900</v>
       </c>
       <c r="H59" s="3">
-        <v>595000</v>
+        <v>797800</v>
       </c>
       <c r="I59" s="3">
-        <v>662800</v>
+        <v>679700</v>
       </c>
       <c r="J59" s="3">
-        <v>107500</v>
+        <v>325400</v>
       </c>
       <c r="K59" s="3">
         <v>104600</v>
@@ -3737,25 +3737,25 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>432500</v>
+        <v>443500</v>
       </c>
       <c r="E60" s="3">
-        <v>490100</v>
+        <v>502600</v>
       </c>
       <c r="F60" s="3">
-        <v>731900</v>
+        <v>750600</v>
       </c>
       <c r="G60" s="3">
-        <v>673100</v>
+        <v>690200</v>
       </c>
       <c r="H60" s="3">
-        <v>998100</v>
+        <v>1023500</v>
       </c>
       <c r="I60" s="3">
-        <v>964800</v>
+        <v>989400</v>
       </c>
       <c r="J60" s="3">
-        <v>712700</v>
+        <v>730900</v>
       </c>
       <c r="K60" s="3">
         <v>582700</v>
@@ -3802,25 +3802,25 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>733200</v>
+        <v>751900</v>
       </c>
       <c r="E61" s="3">
-        <v>763900</v>
+        <v>783400</v>
       </c>
       <c r="F61" s="3">
-        <v>757500</v>
+        <v>776800</v>
       </c>
       <c r="G61" s="3">
-        <v>985300</v>
+        <v>1010400</v>
       </c>
       <c r="H61" s="3">
-        <v>842000</v>
+        <v>863400</v>
       </c>
       <c r="I61" s="3">
-        <v>894400</v>
+        <v>917200</v>
       </c>
       <c r="J61" s="3">
-        <v>954600</v>
+        <v>978900</v>
       </c>
       <c r="K61" s="3">
         <v>1020100</v>
@@ -3867,25 +3867,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>168900</v>
+        <v>173200</v>
       </c>
       <c r="E62" s="3">
-        <v>179100</v>
+        <v>183700</v>
       </c>
       <c r="F62" s="3">
-        <v>195800</v>
+        <v>200800</v>
       </c>
       <c r="G62" s="3">
-        <v>249500</v>
+        <v>255900</v>
       </c>
       <c r="H62" s="3">
-        <v>247000</v>
+        <v>253300</v>
       </c>
       <c r="I62" s="3">
-        <v>200900</v>
+        <v>206000</v>
       </c>
       <c r="J62" s="3">
-        <v>268700</v>
+        <v>275600</v>
       </c>
       <c r="K62" s="3">
         <v>303500</v>
@@ -4127,25 +4127,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>1335900</v>
+        <v>1369900</v>
       </c>
       <c r="E66" s="3">
-        <v>1434400</v>
+        <v>1471000</v>
       </c>
       <c r="F66" s="3">
-        <v>1686500</v>
+        <v>1729500</v>
       </c>
       <c r="G66" s="3">
-        <v>1909200</v>
+        <v>1957800</v>
       </c>
       <c r="H66" s="3">
-        <v>2088300</v>
+        <v>2141500</v>
       </c>
       <c r="I66" s="3">
-        <v>2061500</v>
+        <v>2114000</v>
       </c>
       <c r="J66" s="3">
-        <v>1937300</v>
+        <v>1986700</v>
       </c>
       <c r="K66" s="3">
         <v>1906300</v>
@@ -4477,25 +4477,25 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>912400</v>
+        <v>964500</v>
       </c>
       <c r="E72" s="3">
-        <v>875300</v>
+        <v>897500</v>
       </c>
       <c r="F72" s="3">
-        <v>849700</v>
+        <v>871300</v>
       </c>
       <c r="G72" s="3">
-        <v>891900</v>
+        <v>914600</v>
       </c>
       <c r="H72" s="3">
-        <v>1401200</v>
+        <v>1436900</v>
       </c>
       <c r="I72" s="3">
-        <v>1257900</v>
+        <v>1289900</v>
       </c>
       <c r="J72" s="3">
-        <v>1188800</v>
+        <v>1219000</v>
       </c>
       <c r="K72" s="3">
         <v>1146300</v>
@@ -4737,25 +4737,25 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>1584200</v>
+        <v>1624500</v>
       </c>
       <c r="E76" s="3">
-        <v>1547000</v>
+        <v>1586400</v>
       </c>
       <c r="F76" s="3">
-        <v>1521500</v>
+        <v>1560200</v>
       </c>
       <c r="G76" s="3">
-        <v>1562400</v>
+        <v>1602200</v>
       </c>
       <c r="H76" s="3">
-        <v>2071700</v>
+        <v>2124500</v>
       </c>
       <c r="I76" s="3">
-        <v>1928400</v>
+        <v>1977500</v>
       </c>
       <c r="J76" s="3">
-        <v>1859300</v>
+        <v>1906600</v>
       </c>
       <c r="K76" s="3">
         <v>1814500</v>
@@ -4937,25 +4937,25 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>110000</v>
+        <v>112800</v>
       </c>
       <c r="E81" s="3">
-        <v>130500</v>
+        <v>133800</v>
       </c>
       <c r="F81" s="3">
-        <v>88300</v>
+        <v>90500</v>
       </c>
       <c r="G81" s="3">
-        <v>154800</v>
+        <v>158800</v>
       </c>
       <c r="H81" s="3">
-        <v>171500</v>
+        <v>175800</v>
       </c>
       <c r="I81" s="3">
-        <v>130500</v>
+        <v>133800</v>
       </c>
       <c r="J81" s="3">
-        <v>153600</v>
+        <v>157500</v>
       </c>
       <c r="K81" s="3">
         <v>169600</v>
@@ -5027,25 +5027,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>60100</v>
+        <v>61700</v>
       </c>
       <c r="E83" s="3">
-        <v>60100</v>
+        <v>61700</v>
       </c>
       <c r="F83" s="3">
-        <v>61400</v>
+        <v>63000</v>
       </c>
       <c r="G83" s="3">
-        <v>60100</v>
+        <v>61700</v>
       </c>
       <c r="H83" s="3">
-        <v>49900</v>
+        <v>51200</v>
       </c>
       <c r="I83" s="3">
-        <v>78100</v>
+        <v>80000</v>
       </c>
       <c r="J83" s="3">
-        <v>111300</v>
+        <v>114200</v>
       </c>
       <c r="K83" s="3">
         <v>112200</v>
@@ -5417,25 +5417,25 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>156100</v>
+        <v>160100</v>
       </c>
       <c r="E89" s="3">
-        <v>110000</v>
+        <v>112800</v>
       </c>
       <c r="F89" s="3">
-        <v>35800</v>
+        <v>36700</v>
       </c>
       <c r="G89" s="3">
-        <v>48600</v>
+        <v>49900</v>
       </c>
       <c r="H89" s="3">
-        <v>-97300</v>
+        <v>-99700</v>
       </c>
       <c r="I89" s="3">
-        <v>229100</v>
+        <v>234900</v>
       </c>
       <c r="J89" s="3">
-        <v>158700</v>
+        <v>162700</v>
       </c>
       <c r="K89" s="3">
         <v>312400</v>
@@ -5702,25 +5702,25 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-10200</v>
+        <v>-10500</v>
       </c>
       <c r="E94" s="3">
-        <v>-15400</v>
+        <v>-15700</v>
       </c>
       <c r="F94" s="3">
-        <v>20500</v>
+        <v>21000</v>
       </c>
       <c r="G94" s="3">
-        <v>1048000</v>
+        <v>1074700</v>
       </c>
       <c r="H94" s="3">
-        <v>-92100</v>
+        <v>-94500</v>
       </c>
       <c r="I94" s="3">
-        <v>-52500</v>
+        <v>-53800</v>
       </c>
       <c r="J94" s="3">
-        <v>-185500</v>
+        <v>-190300</v>
       </c>
       <c r="K94" s="3">
         <v>-76500</v>
@@ -5792,25 +5792,25 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-30700</v>
+        <v>-31500</v>
       </c>
       <c r="E96" s="3">
-        <v>-66500</v>
+        <v>-68200</v>
       </c>
       <c r="F96" s="3">
-        <v>-28200</v>
+        <v>-28900</v>
       </c>
       <c r="G96" s="3">
-        <v>-701200</v>
+        <v>-719100</v>
       </c>
       <c r="H96" s="3">
-        <v>-53700</v>
+        <v>-55100</v>
       </c>
       <c r="I96" s="3">
-        <v>-130500</v>
+        <v>-133800</v>
       </c>
       <c r="J96" s="3">
-        <v>-51200</v>
+        <v>-52500</v>
       </c>
       <c r="K96" s="3">
         <v>-123700</v>
@@ -6052,25 +6052,25 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-71700</v>
+        <v>-73500</v>
       </c>
       <c r="E100" s="3">
-        <v>-203500</v>
+        <v>-208600</v>
       </c>
       <c r="F100" s="3">
-        <v>-48600</v>
+        <v>-49900</v>
       </c>
       <c r="G100" s="3">
-        <v>-716600</v>
+        <v>-734800</v>
       </c>
       <c r="H100" s="3">
-        <v>-161200</v>
+        <v>-165300</v>
       </c>
       <c r="I100" s="3">
-        <v>-154800</v>
+        <v>-158800</v>
       </c>
       <c r="J100" s="3">
-        <v>-80600</v>
+        <v>-82700</v>
       </c>
       <c r="K100" s="3">
         <v>43400</v>
@@ -6117,25 +6117,25 @@
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>-15400</v>
+        <v>-15700</v>
       </c>
       <c r="E101" s="3">
         <v>1300</v>
       </c>
       <c r="F101" s="3">
-        <v>-60100</v>
+        <v>-61700</v>
       </c>
       <c r="G101" s="3">
-        <v>117700</v>
+        <v>120700</v>
       </c>
       <c r="H101" s="3">
-        <v>6400</v>
+        <v>6600</v>
       </c>
       <c r="I101" s="3">
-        <v>10200</v>
+        <v>10500</v>
       </c>
       <c r="J101" s="3">
-        <v>-37100</v>
+        <v>-38100</v>
       </c>
       <c r="K101" s="3">
         <v>-7700</v>
@@ -6182,25 +6182,25 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>58900</v>
+        <v>60400</v>
       </c>
       <c r="E102" s="3">
-        <v>-107500</v>
+        <v>-110200</v>
       </c>
       <c r="F102" s="3">
-        <v>-52500</v>
+        <v>-53800</v>
       </c>
       <c r="G102" s="3">
-        <v>497800</v>
+        <v>510400</v>
       </c>
       <c r="H102" s="3">
-        <v>-344200</v>
+        <v>-353000</v>
       </c>
       <c r="I102" s="3">
-        <v>32000</v>
+        <v>32800</v>
       </c>
       <c r="J102" s="3">
-        <v>-144600</v>
+        <v>-148300</v>
       </c>
       <c r="K102" s="3">
         <v>271600</v>

--- a/AAII_Financials/Quarterly/TATYY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/TATYY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="333" uniqueCount="92">
   <si>
     <t>TATYY</t>
   </si>
@@ -656,18 +656,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:W102"/>
+  <dimension ref="A5:Y102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
@@ -682,150 +681,164 @@
     <col min="21" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="16384" width="9.140625" style="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="F7" s="2">
+      <c r="I7" s="2">
+        <v>45107</v>
+      </c>
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
-        <v>44834</v>
-      </c>
-      <c r="H7" s="2">
-        <v>44651</v>
-      </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44469</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44286</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44104</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>43921</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>43738</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>43555</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>43373</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>43190</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>43008</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>42825</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>42643</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>42460</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>42277</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>42094</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>41912</v>
       </c>
     </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D8" s="3">
-        <v>1036600</v>
-      </c>
-      <c r="E8" s="3">
-        <v>1124600</v>
-      </c>
-      <c r="F8" s="3">
-        <v>1183600</v>
-      </c>
-      <c r="G8" s="3">
-        <v>1114100</v>
-      </c>
-      <c r="H8" s="3">
-        <v>943500</v>
-      </c>
-      <c r="I8" s="3">
+      <c r="D8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K8" s="3">
         <v>860800</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>812300</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>754900</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>1781800</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>1831400</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>1622900</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>1687100</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>1789300</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>1978300</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>1891400</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>1626900</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>1545600</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>1526000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>1502500</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>1580100</v>
       </c>
     </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -889,8 +902,14 @@
       <c r="W9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -954,8 +973,14 @@
       <c r="W10" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -979,8 +1004,10 @@
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
-    </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X11" s="3"/>
+      <c r="Y11" s="3"/>
+    </row>
+    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1044,8 +1071,14 @@
       <c r="W12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1109,41 +1142,47 @@
       <c r="W13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>23600</v>
-      </c>
-      <c r="E14" s="3">
-        <v>10500</v>
-      </c>
-      <c r="F14" s="3">
-        <v>22300</v>
-      </c>
-      <c r="G14" s="3">
-        <v>14400</v>
-      </c>
-      <c r="H14" s="3">
-        <v>31500</v>
-      </c>
-      <c r="I14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K14" s="3">
         <v>77400</v>
       </c>
-      <c r="J14" s="3">
+      <c r="L14" s="3">
         <v>24900</v>
       </c>
-      <c r="K14" s="3">
+      <c r="M14" s="3">
         <v>19100</v>
       </c>
-      <c r="L14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M14" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="N14" s="3" t="s">
         <v>5</v>
       </c>
@@ -1153,20 +1192,20 @@
       <c r="P14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
-      </c>
-      <c r="R14" s="3">
-        <v>0</v>
+      <c r="Q14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="S14" s="3">
         <v>0</v>
       </c>
-      <c r="T14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U14" s="3" t="s">
-        <v>5</v>
+      <c r="T14" s="3">
+        <v>0</v>
+      </c>
+      <c r="U14" s="3">
+        <v>0</v>
       </c>
       <c r="V14" s="3" t="s">
         <v>5</v>
@@ -1174,8 +1213,14 @@
       <c r="W14" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y14" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1185,30 +1230,30 @@
       <c r="E15" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F15" s="3">
-        <v>31500</v>
-      </c>
-      <c r="G15" s="3">
-        <v>15700</v>
-      </c>
-      <c r="H15" s="3">
-        <v>24900</v>
-      </c>
-      <c r="I15" s="3">
+      <c r="F15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K15" s="3">
         <v>6600</v>
       </c>
-      <c r="J15" s="3">
+      <c r="L15" s="3">
         <v>27600</v>
       </c>
-      <c r="K15" s="3">
+      <c r="M15" s="3">
         <v>6400</v>
       </c>
-      <c r="L15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M15" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="N15" s="3" t="s">
         <v>5</v>
       </c>
@@ -1218,20 +1263,20 @@
       <c r="P15" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q15" s="3">
-        <v>0</v>
-      </c>
-      <c r="R15" s="3">
-        <v>0</v>
+      <c r="Q15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R15" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="S15" s="3">
         <v>0</v>
       </c>
-      <c r="T15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U15" s="3" t="s">
-        <v>5</v>
+      <c r="T15" s="3">
+        <v>0</v>
+      </c>
+      <c r="U15" s="3">
+        <v>0</v>
       </c>
       <c r="V15" s="3" t="s">
         <v>5</v>
@@ -1239,8 +1284,14 @@
       <c r="W15" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y15" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1261,138 +1312,152 @@
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
-    </row>
-    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X16" s="3"/>
+      <c r="Y16" s="3"/>
+    </row>
+    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D17" s="3">
-        <v>926400</v>
-      </c>
-      <c r="E17" s="3">
-        <v>963200</v>
-      </c>
-      <c r="F17" s="3">
-        <v>1076000</v>
-      </c>
-      <c r="G17" s="3">
-        <v>964500</v>
-      </c>
-      <c r="H17" s="3">
-        <v>898900</v>
-      </c>
-      <c r="I17" s="3">
+      <c r="D17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K17" s="3">
         <v>817500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>753200</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>664300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>1617100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>1625400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>1477400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>1549300</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>1618800</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>1744800</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>1747400</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>1474200</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>1472600</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>1433400</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>1548500</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>1490600</v>
       </c>
     </row>
-    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3">
-        <v>110200</v>
-      </c>
-      <c r="E18" s="3">
-        <v>161400</v>
-      </c>
-      <c r="F18" s="3">
-        <v>107600</v>
-      </c>
-      <c r="G18" s="3">
-        <v>149600</v>
-      </c>
-      <c r="H18" s="3">
-        <v>44600</v>
-      </c>
-      <c r="I18" s="3">
+      <c r="D18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K18" s="3">
         <v>43300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>59000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>90500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>164700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>206000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>145500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>137800</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>170500</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>233500</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>144000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>152700</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>73000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>92600</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>-46100</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>89500</v>
       </c>
     </row>
-    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1416,161 +1481,175 @@
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
-    </row>
-    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X19" s="3"/>
+      <c r="Y19" s="3"/>
+    </row>
+    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
-        <v>15700</v>
-      </c>
-      <c r="E20" s="3">
-        <v>9200</v>
-      </c>
-      <c r="F20" s="3">
-        <v>2600</v>
-      </c>
-      <c r="G20" s="3">
-        <v>-60400</v>
-      </c>
-      <c r="H20" s="3">
+      <c r="D20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K20" s="3">
+        <v>-15700</v>
+      </c>
+      <c r="L20" s="3">
         <v>-17100</v>
       </c>
-      <c r="I20" s="3">
-        <v>-15700</v>
-      </c>
-      <c r="J20" s="3">
-        <v>-17100</v>
-      </c>
-      <c r="K20" s="3">
+      <c r="M20" s="3">
         <v>-16600</v>
       </c>
-      <c r="L20" s="3">
+      <c r="N20" s="3">
         <v>2500</v>
       </c>
-      <c r="M20" s="3">
+      <c r="O20" s="3">
         <v>-2500</v>
       </c>
-      <c r="N20" s="3">
+      <c r="P20" s="3">
         <v>4700</v>
       </c>
-      <c r="O20" s="3">
-        <v>0</v>
-      </c>
-      <c r="P20" s="3">
-        <v>0</v>
-      </c>
       <c r="Q20" s="3">
+        <v>0</v>
+      </c>
+      <c r="R20" s="3">
+        <v>0</v>
+      </c>
+      <c r="S20" s="3">
         <v>-5700</v>
       </c>
-      <c r="R20" s="3">
+      <c r="T20" s="3">
         <v>-5300</v>
       </c>
-      <c r="S20" s="3">
+      <c r="U20" s="3">
         <v>4900</v>
       </c>
-      <c r="T20" s="3">
+      <c r="V20" s="3">
         <v>17000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="W20" s="3">
         <v>11700</v>
       </c>
-      <c r="V20" s="3">
+      <c r="X20" s="3">
         <v>10500</v>
       </c>
-      <c r="W20" s="3">
+      <c r="Y20" s="3">
         <v>10500</v>
       </c>
     </row>
-    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3">
-        <v>187600</v>
-      </c>
-      <c r="E21" s="3">
-        <v>232300</v>
-      </c>
-      <c r="F21" s="3">
-        <v>173200</v>
-      </c>
-      <c r="G21" s="3">
-        <v>150900</v>
-      </c>
-      <c r="H21" s="3">
-        <v>78700</v>
-      </c>
-      <c r="I21" s="3">
+      <c r="D21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K21" s="3">
         <v>107600</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>156200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>186200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>262300</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>323800</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>241300</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>229300</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>276800</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>335400</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>244300</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>242600</v>
       </c>
-      <c r="T21" s="3">
+      <c r="V21" s="3">
         <v>168300</v>
       </c>
-      <c r="U21" s="3">
+      <c r="W21" s="3">
         <v>176100</v>
       </c>
-      <c r="V21" s="3">
+      <c r="X21" s="3">
         <v>40800</v>
       </c>
-      <c r="W21" s="3">
+      <c r="Y21" s="3">
         <v>167200</v>
       </c>
     </row>
-    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
-        <v>0</v>
-      </c>
-      <c r="E22" s="3">
-        <v>0</v>
-      </c>
-      <c r="F22" s="3">
-        <v>0</v>
-      </c>
-      <c r="G22" s="3">
-        <v>0</v>
-      </c>
-      <c r="H22" s="3">
-        <v>0</v>
-      </c>
-      <c r="I22" s="3">
-        <v>0</v>
-      </c>
-      <c r="J22" s="3">
-        <v>0</v>
+      <c r="D22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
@@ -1581,11 +1660,11 @@
       <c r="M22" s="3">
         <v>0</v>
       </c>
-      <c r="N22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O22" s="3" t="s">
-        <v>5</v>
+      <c r="N22" s="3">
+        <v>0</v>
+      </c>
+      <c r="O22" s="3">
+        <v>0</v>
       </c>
       <c r="P22" s="3" t="s">
         <v>5</v>
@@ -1599,150 +1678,168 @@
       <c r="S22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="T22" s="3">
+      <c r="T22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V22" s="3">
         <v>17000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="W22" s="3">
         <v>13000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="X22" s="3">
         <v>14500</v>
       </c>
-      <c r="W22" s="3">
+      <c r="Y22" s="3">
         <v>17100</v>
       </c>
     </row>
-    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D23" s="3">
-        <v>126000</v>
-      </c>
-      <c r="E23" s="3">
-        <v>170600</v>
-      </c>
-      <c r="F23" s="3">
-        <v>110200</v>
-      </c>
-      <c r="G23" s="3">
-        <v>89200</v>
-      </c>
-      <c r="H23" s="3">
+      <c r="D23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K23" s="3">
         <v>27600</v>
       </c>
-      <c r="I23" s="3">
-        <v>27600</v>
-      </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>42000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>74000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>167300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>203500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>150200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>137800</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>170500</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>227800</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>138700</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>157600</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>73000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>91300</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>-50000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>83000</v>
       </c>
     </row>
-    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3">
-        <v>31500</v>
-      </c>
-      <c r="E24" s="3">
-        <v>39400</v>
-      </c>
-      <c r="F24" s="3">
-        <v>22300</v>
-      </c>
-      <c r="G24" s="3">
-        <v>18400</v>
-      </c>
-      <c r="H24" s="3">
-        <v>-5200</v>
-      </c>
-      <c r="I24" s="3">
+      <c r="D24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K24" s="3">
         <v>17100</v>
       </c>
-      <c r="J24" s="3">
+      <c r="L24" s="3">
         <v>-3900</v>
       </c>
-      <c r="K24" s="3">
+      <c r="M24" s="3">
         <v>20400</v>
       </c>
-      <c r="L24" s="3">
+      <c r="N24" s="3">
         <v>22800</v>
       </c>
-      <c r="M24" s="3">
+      <c r="O24" s="3">
         <v>40900</v>
       </c>
-      <c r="N24" s="3">
+      <c r="P24" s="3">
         <v>31900</v>
       </c>
-      <c r="O24" s="3">
+      <c r="Q24" s="3">
         <v>39000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="R24" s="3">
         <v>-19100</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="S24" s="3">
         <v>52400</v>
       </c>
-      <c r="R24" s="3">
+      <c r="T24" s="3">
         <v>-27700</v>
       </c>
-      <c r="S24" s="3">
+      <c r="U24" s="3">
         <v>-1200</v>
       </c>
-      <c r="T24" s="3">
+      <c r="V24" s="3">
         <v>2600</v>
       </c>
-      <c r="U24" s="3">
+      <c r="W24" s="3">
         <v>3900</v>
       </c>
-      <c r="V24" s="3">
+      <c r="X24" s="3">
         <v>13200</v>
       </c>
-      <c r="W24" s="3">
+      <c r="Y24" s="3">
         <v>14500</v>
       </c>
     </row>
-    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1806,138 +1903,156 @@
       <c r="W25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X25" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D26" s="3">
-        <v>94500</v>
-      </c>
-      <c r="E26" s="3">
-        <v>131200</v>
-      </c>
-      <c r="F26" s="3">
-        <v>87900</v>
-      </c>
-      <c r="G26" s="3">
-        <v>70900</v>
-      </c>
-      <c r="H26" s="3">
-        <v>32800</v>
-      </c>
-      <c r="I26" s="3">
+      <c r="D26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K26" s="3">
         <v>10500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>45900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>53600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>144500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>162500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>118300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>98800</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>189600</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>175500</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>166400</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>158900</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>70400</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>87400</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>-63200</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>68500</v>
       </c>
     </row>
-    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D27" s="3">
-        <v>94500</v>
-      </c>
-      <c r="E27" s="3">
-        <v>131200</v>
-      </c>
-      <c r="F27" s="3">
-        <v>87900</v>
-      </c>
-      <c r="G27" s="3">
-        <v>70900</v>
-      </c>
-      <c r="H27" s="3">
-        <v>32800</v>
-      </c>
-      <c r="I27" s="3">
+      <c r="D27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K27" s="3">
         <v>10500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>45900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>53600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>144500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>162500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>118300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>98800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>189600</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>175500</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>166400</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>158900</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>70400</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>87400</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>-63200</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>68500</v>
       </c>
     </row>
-    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2001,73 +2116,85 @@
       <c r="W28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D29" s="3">
-        <v>18400</v>
-      </c>
-      <c r="E29" s="3">
-        <v>2600</v>
-      </c>
-      <c r="F29" s="3">
-        <v>2600</v>
-      </c>
-      <c r="G29" s="3">
-        <v>87900</v>
-      </c>
-      <c r="H29" s="3">
-        <v>143000</v>
-      </c>
-      <c r="I29" s="3">
+      <c r="D29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K29" s="3">
         <v>123300</v>
       </c>
-      <c r="J29" s="3">
+      <c r="L29" s="3">
         <v>111500</v>
       </c>
-      <c r="K29" s="3">
+      <c r="M29" s="3">
         <v>116000</v>
       </c>
-      <c r="L29" s="3">
-        <v>0</v>
-      </c>
-      <c r="M29" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="N29" s="3">
         <v>0</v>
       </c>
-      <c r="O29" s="3">
-        <v>0</v>
+      <c r="O29" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="P29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="3">
+        <v>0</v>
+      </c>
+      <c r="R29" s="3">
         <v>2700</v>
       </c>
-      <c r="Q29" s="3">
-        <v>0</v>
-      </c>
-      <c r="R29" s="3">
-        <v>0</v>
-      </c>
       <c r="S29" s="3">
+        <v>0</v>
+      </c>
+      <c r="T29" s="3">
+        <v>0</v>
+      </c>
+      <c r="U29" s="3">
         <v>1200</v>
       </c>
-      <c r="T29" s="3">
+      <c r="V29" s="3">
         <v>78300</v>
       </c>
-      <c r="U29" s="3">
+      <c r="W29" s="3">
         <v>-23500</v>
       </c>
-      <c r="V29" s="3">
+      <c r="X29" s="3">
         <v>13200</v>
       </c>
-      <c r="W29" s="3">
+      <c r="Y29" s="3">
         <v>21100</v>
       </c>
     </row>
-    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2131,8 +2258,14 @@
       <c r="W30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2196,138 +2329,156 @@
       <c r="W31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X31" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
-        <v>-15700</v>
-      </c>
-      <c r="E32" s="3">
-        <v>-9200</v>
-      </c>
-      <c r="F32" s="3">
-        <v>-2600</v>
-      </c>
-      <c r="G32" s="3">
-        <v>60400</v>
-      </c>
-      <c r="H32" s="3">
+      <c r="D32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K32" s="3">
+        <v>15700</v>
+      </c>
+      <c r="L32" s="3">
         <v>17100</v>
       </c>
-      <c r="I32" s="3">
-        <v>15700</v>
-      </c>
-      <c r="J32" s="3">
-        <v>17100</v>
-      </c>
-      <c r="K32" s="3">
+      <c r="M32" s="3">
         <v>16600</v>
       </c>
-      <c r="L32" s="3">
+      <c r="N32" s="3">
         <v>-2500</v>
       </c>
-      <c r="M32" s="3">
+      <c r="O32" s="3">
         <v>2500</v>
       </c>
-      <c r="N32" s="3">
+      <c r="P32" s="3">
         <v>-4700</v>
       </c>
-      <c r="O32" s="3">
-        <v>0</v>
-      </c>
-      <c r="P32" s="3">
-        <v>0</v>
-      </c>
       <c r="Q32" s="3">
+        <v>0</v>
+      </c>
+      <c r="R32" s="3">
+        <v>0</v>
+      </c>
+      <c r="S32" s="3">
         <v>5700</v>
       </c>
-      <c r="R32" s="3">
+      <c r="T32" s="3">
         <v>5300</v>
       </c>
-      <c r="S32" s="3">
+      <c r="U32" s="3">
         <v>-4900</v>
       </c>
-      <c r="T32" s="3">
+      <c r="V32" s="3">
         <v>-17000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="W32" s="3">
         <v>-11700</v>
       </c>
-      <c r="V32" s="3">
+      <c r="X32" s="3">
         <v>-10500</v>
       </c>
-      <c r="W32" s="3">
+      <c r="Y32" s="3">
         <v>-10500</v>
       </c>
     </row>
-    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D33" s="3">
-        <v>112800</v>
-      </c>
-      <c r="E33" s="3">
+      <c r="D33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K33" s="3">
         <v>133800</v>
       </c>
-      <c r="F33" s="3">
-        <v>90500</v>
-      </c>
-      <c r="G33" s="3">
-        <v>158800</v>
-      </c>
-      <c r="H33" s="3">
-        <v>175800</v>
-      </c>
-      <c r="I33" s="3">
-        <v>133800</v>
-      </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>157500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>169600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>144500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>162500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>118300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>98800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>192300</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>175500</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>166400</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>160100</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>148700</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>63900</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>-50000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>89500</v>
       </c>
     </row>
-    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2391,143 +2542,161 @@
       <c r="W34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X34" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D35" s="3">
-        <v>112800</v>
-      </c>
-      <c r="E35" s="3">
+      <c r="D35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K35" s="3">
         <v>133800</v>
       </c>
-      <c r="F35" s="3">
-        <v>90500</v>
-      </c>
-      <c r="G35" s="3">
-        <v>158800</v>
-      </c>
-      <c r="H35" s="3">
-        <v>175800</v>
-      </c>
-      <c r="I35" s="3">
-        <v>133800</v>
-      </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>157500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>169600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>144500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>162500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>118300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>98800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>192300</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>175500</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>166400</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>160100</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>148700</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>63900</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>-50000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>89500</v>
       </c>
     </row>
-    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="F38" s="2">
+      <c r="I38" s="2">
+        <v>45107</v>
+      </c>
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
-        <v>44834</v>
-      </c>
-      <c r="H38" s="2">
-        <v>44651</v>
-      </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44469</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44286</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44104</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>43921</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>43738</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>43555</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>43373</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>43190</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>43008</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>42825</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>42643</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>42460</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>42277</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>42094</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>41912</v>
       </c>
     </row>
-    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2551,8 +2720,10 @@
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
-    </row>
-    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X39" s="3"/>
+      <c r="Y39" s="3"/>
+    </row>
+    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2576,81 +2747,89 @@
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
-    </row>
-    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X40" s="3"/>
+      <c r="Y40" s="3"/>
+    </row>
+    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>573400</v>
+        <v>796100</v>
       </c>
       <c r="E41" s="3">
-        <v>513100</v>
+        <v>750700</v>
       </c>
       <c r="F41" s="3">
-        <v>623300</v>
+        <v>551900</v>
       </c>
       <c r="G41" s="3">
-        <v>677100</v>
+        <v>556600</v>
       </c>
       <c r="H41" s="3">
-        <v>166600</v>
+        <v>477100</v>
       </c>
       <c r="I41" s="3">
+        <v>496900</v>
+      </c>
+      <c r="J41" s="3">
+        <v>587600</v>
+      </c>
+      <c r="K41" s="3">
         <v>505200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>486800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>617100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>343400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>447900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>337100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>346500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>259100</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>342500</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>344700</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>355900</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>413500</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>305200</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>256800</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>425300</v>
       </c>
     </row>
-    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="D42" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E42" s="3" t="s">
-        <v>5</v>
+      <c r="D42" s="3">
+        <v>0</v>
+      </c>
+      <c r="E42" s="3">
+        <v>0</v>
       </c>
       <c r="F42" s="3">
         <v>0</v>
@@ -2659,510 +2838,558 @@
         <v>0</v>
       </c>
       <c r="H42" s="3">
+        <v>0</v>
+      </c>
+      <c r="I42" s="3">
+        <v>0</v>
+      </c>
+      <c r="J42" s="3">
+        <v>0</v>
+      </c>
+      <c r="K42" s="3">
+        <v>0</v>
+      </c>
+      <c r="L42" s="3">
+        <v>42000</v>
+      </c>
+      <c r="M42" s="3">
+        <v>48500</v>
+      </c>
+      <c r="N42" s="3">
+        <v>84900</v>
+      </c>
+      <c r="O42" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P42" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q42" s="3">
+        <v>0</v>
+      </c>
+      <c r="R42" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S42" s="3">
+        <v>1400</v>
+      </c>
+      <c r="T42" s="3">
+        <v>0</v>
+      </c>
+      <c r="U42" s="3">
+        <v>4900</v>
+      </c>
+      <c r="V42" s="3">
+        <v>5200</v>
+      </c>
+      <c r="W42" s="3">
+        <v>7800</v>
+      </c>
+      <c r="X42" s="3">
+        <v>23700</v>
+      </c>
+      <c r="Y42" s="3">
         <v>2600</v>
       </c>
-      <c r="I42" s="3">
-        <v>0</v>
-      </c>
-      <c r="J42" s="3">
-        <v>42000</v>
-      </c>
-      <c r="K42" s="3">
-        <v>48500</v>
-      </c>
-      <c r="L42" s="3">
-        <v>84900</v>
-      </c>
-      <c r="M42" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N42" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O42" s="3">
-        <v>0</v>
-      </c>
-      <c r="P42" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q42" s="3">
-        <v>1400</v>
-      </c>
-      <c r="R42" s="3">
-        <v>0</v>
-      </c>
-      <c r="S42" s="3">
-        <v>4900</v>
-      </c>
-      <c r="T42" s="3">
-        <v>5200</v>
-      </c>
-      <c r="U42" s="3">
-        <v>7800</v>
-      </c>
-      <c r="V42" s="3">
-        <v>23700</v>
-      </c>
-      <c r="W42" s="3">
-        <v>2600</v>
-      </c>
-    </row>
-    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
+    </row>
+    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>368700</v>
+        <v>372600</v>
       </c>
       <c r="E43" s="3">
-        <v>397600</v>
+        <v>351300</v>
       </c>
       <c r="F43" s="3">
-        <v>451400</v>
+        <v>354900</v>
       </c>
       <c r="G43" s="3">
-        <v>541900</v>
+        <v>357900</v>
       </c>
       <c r="H43" s="3">
-        <v>347700</v>
+        <v>369800</v>
       </c>
       <c r="I43" s="3">
+        <v>385100</v>
+      </c>
+      <c r="J43" s="3">
+        <v>425600</v>
+      </c>
+      <c r="K43" s="3">
         <v>343800</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>433000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>406800</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>422000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>397100</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>389200</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>425700</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>402300</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>450000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="T43" s="3">
         <v>385700</v>
       </c>
-      <c r="S43" s="3">
+      <c r="U43" s="3">
         <v>374400</v>
       </c>
-      <c r="T43" s="3">
+      <c r="V43" s="3">
         <v>396500</v>
       </c>
-      <c r="U43" s="3">
+      <c r="W43" s="3">
         <v>363900</v>
       </c>
-      <c r="V43" s="3">
+      <c r="X43" s="3">
         <v>384500</v>
       </c>
-      <c r="W43" s="3">
+      <c r="Y43" s="3">
         <v>495100</v>
       </c>
     </row>
-    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>463200</v>
+        <v>434300</v>
       </c>
       <c r="E44" s="3">
-        <v>536700</v>
+        <v>409500</v>
       </c>
       <c r="F44" s="3">
-        <v>585200</v>
+        <v>445800</v>
       </c>
       <c r="G44" s="3">
-        <v>585200</v>
+        <v>449600</v>
       </c>
       <c r="H44" s="3">
-        <v>416000</v>
+        <v>499100</v>
       </c>
       <c r="I44" s="3">
+        <v>519800</v>
+      </c>
+      <c r="J44" s="3">
+        <v>551800</v>
+      </c>
+      <c r="K44" s="3">
         <v>345100</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>698100</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>498600</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>577900</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>512500</v>
       </c>
-      <c r="N44" s="3">
+      <c r="P44" s="3">
         <v>513400</v>
       </c>
-      <c r="O44" s="3">
+      <c r="Q44" s="3">
         <v>508700</v>
       </c>
-      <c r="P44" s="3">
+      <c r="R44" s="3">
         <v>571400</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="S44" s="3">
         <v>537700</v>
       </c>
-      <c r="R44" s="3">
+      <c r="T44" s="3">
         <v>582500</v>
       </c>
-      <c r="S44" s="3">
+      <c r="U44" s="3">
         <v>449500</v>
       </c>
-      <c r="T44" s="3">
+      <c r="V44" s="3">
         <v>507400</v>
       </c>
-      <c r="U44" s="3">
+      <c r="W44" s="3">
         <v>443500</v>
       </c>
-      <c r="V44" s="3">
+      <c r="X44" s="3">
         <v>478000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="Y44" s="3">
         <v>331800</v>
       </c>
     </row>
-    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
-        <v>21000</v>
-      </c>
-      <c r="E45" s="3">
+      <c r="D45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H45" s="3">
+        <v>1200</v>
+      </c>
+      <c r="I45" s="3">
         <v>1300</v>
       </c>
-      <c r="F45" s="3">
-        <v>24900</v>
-      </c>
-      <c r="G45" s="3">
-        <v>17100</v>
-      </c>
-      <c r="H45" s="3">
-        <v>2295000</v>
-      </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
+        <v>3700</v>
+      </c>
+      <c r="K45" s="3">
         <v>1804300</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>48600</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>11500</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>6300</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>44700</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>56800</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>46400</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>32700</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>55200</v>
       </c>
-      <c r="R45" s="3">
+      <c r="T45" s="3">
         <v>40900</v>
       </c>
-      <c r="S45" s="3">
+      <c r="U45" s="3">
         <v>71400</v>
       </c>
-      <c r="T45" s="3">
+      <c r="V45" s="3">
         <v>65200</v>
       </c>
-      <c r="U45" s="3">
+      <c r="W45" s="3">
         <v>348300</v>
       </c>
-      <c r="V45" s="3">
+      <c r="X45" s="3">
         <v>81600</v>
       </c>
-      <c r="W45" s="3">
+      <c r="Y45" s="3">
         <v>143500</v>
       </c>
     </row>
-    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>1426400</v>
+        <v>1603000</v>
       </c>
       <c r="E46" s="3">
-        <v>1448700</v>
+        <v>1511500</v>
       </c>
       <c r="F46" s="3">
-        <v>1684900</v>
+        <v>1372900</v>
       </c>
       <c r="G46" s="3">
-        <v>1821300</v>
+        <v>1384600</v>
       </c>
       <c r="H46" s="3">
-        <v>3228000</v>
+        <v>1347200</v>
       </c>
       <c r="I46" s="3">
+        <v>1403000</v>
+      </c>
+      <c r="J46" s="3">
+        <v>1588500</v>
+      </c>
+      <c r="K46" s="3">
         <v>2998400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>1708500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>1582400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>1434600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>1402100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>1296500</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>1327300</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>1265600</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>1386800</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>1353800</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>1256200</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>1387800</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>1468700</v>
       </c>
-      <c r="V46" s="3">
+      <c r="X46" s="3">
         <v>1224600</v>
       </c>
-      <c r="W46" s="3">
+      <c r="Y46" s="3">
         <v>1398400</v>
       </c>
     </row>
-    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>267700</v>
+        <v>36200</v>
       </c>
       <c r="E47" s="3">
-        <v>328100</v>
+        <v>34100</v>
       </c>
       <c r="F47" s="3">
-        <v>330700</v>
+        <v>243800</v>
       </c>
       <c r="G47" s="3">
-        <v>389700</v>
+        <v>245800</v>
       </c>
       <c r="H47" s="3">
-        <v>61700</v>
+        <v>290400</v>
       </c>
       <c r="I47" s="3">
+        <v>302400</v>
+      </c>
+      <c r="J47" s="3">
+        <v>298100</v>
+      </c>
+      <c r="K47" s="3">
         <v>66900</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>215200</v>
       </c>
-      <c r="K47" s="3">
+      <c r="M47" s="3">
         <v>209100</v>
       </c>
-      <c r="L47" s="3">
+      <c r="N47" s="3">
         <v>195200</v>
       </c>
-      <c r="M47" s="3">
+      <c r="O47" s="3">
         <v>198500</v>
       </c>
-      <c r="N47" s="3">
+      <c r="P47" s="3">
         <v>192800</v>
       </c>
-      <c r="O47" s="3">
+      <c r="Q47" s="3">
         <v>158600</v>
       </c>
-      <c r="P47" s="3">
+      <c r="R47" s="3">
         <v>170500</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="S47" s="3">
         <v>154200</v>
       </c>
-      <c r="R47" s="3">
+      <c r="T47" s="3">
         <v>167700</v>
       </c>
-      <c r="S47" s="3">
+      <c r="U47" s="3">
         <v>136700</v>
       </c>
-      <c r="T47" s="3">
+      <c r="V47" s="3">
         <v>137000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="W47" s="3">
         <v>180000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="X47" s="3">
         <v>453000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="Y47" s="3">
         <v>476700</v>
       </c>
     </row>
-    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>692800</v>
+        <v>705000</v>
       </c>
       <c r="E48" s="3">
-        <v>662700</v>
+        <v>664800</v>
       </c>
       <c r="F48" s="3">
-        <v>640400</v>
+        <v>666900</v>
       </c>
       <c r="G48" s="3">
-        <v>658700</v>
+        <v>672500</v>
       </c>
       <c r="H48" s="3">
-        <v>565600</v>
+        <v>616300</v>
       </c>
       <c r="I48" s="3">
+        <v>641800</v>
+      </c>
+      <c r="J48" s="3">
+        <v>603700</v>
+      </c>
+      <c r="K48" s="3">
         <v>559000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>1450000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>2937800</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>1508100</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>1475300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>1161600</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>1206500</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>1316100</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>1416500</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>1401400</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>1272200</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>1207800</v>
       </c>
-      <c r="U48" s="3">
+      <c r="W48" s="3">
         <v>1006900</v>
       </c>
-      <c r="V48" s="3">
+      <c r="X48" s="3">
         <v>987600</v>
       </c>
-      <c r="W48" s="3">
+      <c r="Y48" s="3">
         <v>995500</v>
       </c>
     </row>
-    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>532800</v>
+        <v>504000</v>
       </c>
       <c r="E49" s="3">
-        <v>564200</v>
+        <v>475200</v>
       </c>
       <c r="F49" s="3">
-        <v>593100</v>
+        <v>488800</v>
       </c>
       <c r="G49" s="3">
-        <v>653500</v>
+        <v>492900</v>
       </c>
       <c r="H49" s="3">
-        <v>364800</v>
+        <v>524700</v>
       </c>
       <c r="I49" s="3">
+        <v>546400</v>
+      </c>
+      <c r="J49" s="3">
+        <v>533200</v>
+      </c>
+      <c r="K49" s="3">
         <v>380500</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>452700</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>406800</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>430900</v>
-      </c>
-      <c r="M49" s="3">
-        <v>431800</v>
-      </c>
-      <c r="N49" s="3">
-        <v>404600</v>
       </c>
       <c r="O49" s="3">
         <v>431800</v>
       </c>
       <c r="P49" s="3">
+        <v>404600</v>
+      </c>
+      <c r="Q49" s="3">
+        <v>431800</v>
+      </c>
+      <c r="R49" s="3">
         <v>491000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="S49" s="3">
         <v>539200</v>
       </c>
-      <c r="R49" s="3">
+      <c r="T49" s="3">
         <v>529600</v>
       </c>
-      <c r="S49" s="3">
+      <c r="U49" s="3">
         <v>511100</v>
       </c>
-      <c r="T49" s="3">
+      <c r="V49" s="3">
         <v>508700</v>
       </c>
-      <c r="U49" s="3">
+      <c r="W49" s="3">
         <v>403000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="X49" s="3">
         <v>447700</v>
       </c>
-      <c r="W49" s="3">
+      <c r="Y49" s="3">
         <v>418700</v>
       </c>
     </row>
-    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3226,8 +3453,14 @@
       <c r="W50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X50" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3291,73 +3524,85 @@
       <c r="W51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X51" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>74800</v>
+        <v>53600</v>
       </c>
       <c r="E52" s="3">
-        <v>53800</v>
+        <v>50600</v>
       </c>
       <c r="F52" s="3">
-        <v>40700</v>
+        <v>50500</v>
       </c>
       <c r="G52" s="3">
-        <v>36700</v>
+        <v>51000</v>
       </c>
       <c r="H52" s="3">
-        <v>45900</v>
+        <v>45200</v>
       </c>
       <c r="I52" s="3">
+        <v>47000</v>
+      </c>
+      <c r="J52" s="3">
+        <v>35900</v>
+      </c>
+      <c r="K52" s="3">
         <v>86600</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>66900</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>53600</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>44400</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>42200</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>248400</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>241500</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>263200</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="S52" s="3">
         <v>206600</v>
       </c>
-      <c r="R52" s="3">
+      <c r="T52" s="3">
         <v>207400</v>
       </c>
-      <c r="S52" s="3">
+      <c r="U52" s="3">
         <v>67700</v>
       </c>
-      <c r="T52" s="3">
+      <c r="V52" s="3">
         <v>90000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="W52" s="3">
         <v>114800</v>
       </c>
-      <c r="V52" s="3">
+      <c r="X52" s="3">
         <v>77700</v>
       </c>
-      <c r="W52" s="3">
+      <c r="Y52" s="3">
         <v>39500</v>
       </c>
     </row>
-    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3421,73 +3666,85 @@
       <c r="W53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X53" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>2994400</v>
+        <v>2963400</v>
       </c>
       <c r="E54" s="3">
-        <v>3057400</v>
+        <v>2794200</v>
       </c>
       <c r="F54" s="3">
-        <v>3289700</v>
+        <v>2882100</v>
       </c>
       <c r="G54" s="3">
-        <v>3560000</v>
+        <v>2906700</v>
       </c>
       <c r="H54" s="3">
-        <v>4266000</v>
+        <v>2843300</v>
       </c>
       <c r="I54" s="3">
+        <v>2960900</v>
+      </c>
+      <c r="J54" s="3">
+        <v>3101500</v>
+      </c>
+      <c r="K54" s="3">
         <v>4091400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>3893300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>3720700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>3613100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>3549900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>3303800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>3365700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>3506300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>3703300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>3659900</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>3244000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>3331200</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>3173400</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>3190600</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>3328800</v>
       </c>
     </row>
-    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3511,8 +3768,10 @@
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
-    </row>
-    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X55" s="3"/>
+      <c r="Y55" s="3"/>
+    </row>
+    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3536,398 +3795,436 @@
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
-    </row>
-    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X56" s="3"/>
+      <c r="Y56" s="3"/>
+    </row>
+    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>228300</v>
+        <v>345800</v>
       </c>
       <c r="E57" s="3">
-        <v>354300</v>
+        <v>326100</v>
       </c>
       <c r="F57" s="3">
-        <v>328100</v>
+        <v>219800</v>
       </c>
       <c r="G57" s="3">
-        <v>545900</v>
+        <v>221600</v>
       </c>
       <c r="H57" s="3">
-        <v>198100</v>
+        <v>329500</v>
       </c>
       <c r="I57" s="3">
+        <v>343100</v>
+      </c>
+      <c r="J57" s="3">
+        <v>309300</v>
+      </c>
+      <c r="K57" s="3">
         <v>276900</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>350400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>424600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>468900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>378400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>404600</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>431800</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>425500</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>447200</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>416000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>397800</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>439600</v>
       </c>
-      <c r="U57" s="3">
+      <c r="W57" s="3">
         <v>439600</v>
       </c>
-      <c r="V57" s="3">
+      <c r="X57" s="3">
         <v>416100</v>
       </c>
-      <c r="W57" s="3">
+      <c r="Y57" s="3">
         <v>425300</v>
       </c>
     </row>
-    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>22300</v>
+        <v>22800</v>
       </c>
       <c r="E58" s="3">
-        <v>56400</v>
+        <v>21500</v>
       </c>
       <c r="F58" s="3">
-        <v>158800</v>
+        <v>21500</v>
       </c>
       <c r="G58" s="3">
-        <v>35400</v>
+        <v>21700</v>
       </c>
       <c r="H58" s="3">
-        <v>42000</v>
+        <v>52500</v>
       </c>
       <c r="I58" s="3">
+        <v>54600</v>
+      </c>
+      <c r="J58" s="3">
+        <v>149700</v>
+      </c>
+      <c r="K58" s="3">
         <v>32800</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>74800</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>107100</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>50700</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>317600</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>265000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="Q58" s="3">
         <v>29300</v>
       </c>
-      <c r="P58" s="3">
+      <c r="R58" s="3">
         <v>21800</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="S58" s="3">
         <v>39600</v>
       </c>
-      <c r="R58" s="3">
+      <c r="T58" s="3">
         <v>116200</v>
       </c>
-      <c r="S58" s="3">
+      <c r="U58" s="3">
         <v>129300</v>
       </c>
-      <c r="T58" s="3">
+      <c r="V58" s="3">
         <v>260900</v>
       </c>
-      <c r="U58" s="3">
+      <c r="W58" s="3">
         <v>644300</v>
       </c>
-      <c r="V58" s="3">
+      <c r="X58" s="3">
         <v>401600</v>
       </c>
-      <c r="W58" s="3">
+      <c r="Y58" s="3">
         <v>468800</v>
       </c>
     </row>
-    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>192900</v>
+        <v>105900</v>
       </c>
       <c r="E59" s="3">
-        <v>91900</v>
+        <v>99800</v>
       </c>
       <c r="F59" s="3">
-        <v>263800</v>
+        <v>101000</v>
       </c>
       <c r="G59" s="3">
-        <v>108900</v>
+        <v>101900</v>
       </c>
       <c r="H59" s="3">
-        <v>797800</v>
+        <v>85400</v>
       </c>
       <c r="I59" s="3">
+        <v>89000</v>
+      </c>
+      <c r="J59" s="3">
+        <v>117500</v>
+      </c>
+      <c r="K59" s="3">
         <v>679700</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>325400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>104600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>124200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>143900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>136000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>135400</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>100900</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>113200</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>110900</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>150300</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>147400</v>
       </c>
-      <c r="U59" s="3">
+      <c r="W59" s="3">
         <v>159100</v>
       </c>
-      <c r="V59" s="3">
+      <c r="X59" s="3">
         <v>109300</v>
       </c>
-      <c r="W59" s="3">
+      <c r="Y59" s="3">
         <v>142200</v>
       </c>
     </row>
-    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>443500</v>
+        <v>474500</v>
       </c>
       <c r="E60" s="3">
-        <v>502600</v>
+        <v>447400</v>
       </c>
       <c r="F60" s="3">
-        <v>750600</v>
+        <v>426900</v>
       </c>
       <c r="G60" s="3">
-        <v>690200</v>
+        <v>430500</v>
       </c>
       <c r="H60" s="3">
-        <v>1023500</v>
+        <v>467400</v>
       </c>
       <c r="I60" s="3">
+        <v>486700</v>
+      </c>
+      <c r="J60" s="3">
+        <v>707600</v>
+      </c>
+      <c r="K60" s="3">
         <v>989400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>730900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>582700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>643800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>840000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>805600</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>596500</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>548200</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>600000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>643200</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>677400</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>847800</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>1243000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="X60" s="3">
         <v>927000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="Y60" s="3">
         <v>1036300</v>
       </c>
     </row>
-    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>751900</v>
+        <v>721100</v>
       </c>
       <c r="E61" s="3">
-        <v>783400</v>
+        <v>679900</v>
       </c>
       <c r="F61" s="3">
-        <v>776800</v>
+        <v>723700</v>
       </c>
       <c r="G61" s="3">
-        <v>1010400</v>
+        <v>729900</v>
       </c>
       <c r="H61" s="3">
-        <v>863400</v>
+        <v>728500</v>
       </c>
       <c r="I61" s="3">
+        <v>758700</v>
+      </c>
+      <c r="J61" s="3">
+        <v>732400</v>
+      </c>
+      <c r="K61" s="3">
         <v>917200</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>978900</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>1020100</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>864300</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>667600</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>441200</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>703900</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>755500</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="S61" s="3">
         <v>812300</v>
       </c>
-      <c r="R61" s="3">
+      <c r="T61" s="3">
         <v>797800</v>
       </c>
-      <c r="S61" s="3">
+      <c r="U61" s="3">
         <v>731600</v>
       </c>
-      <c r="T61" s="3">
+      <c r="V61" s="3">
         <v>725200</v>
       </c>
-      <c r="U61" s="3">
+      <c r="W61" s="3">
         <v>371700</v>
       </c>
-      <c r="V61" s="3">
+      <c r="X61" s="3">
         <v>609700</v>
       </c>
-      <c r="W61" s="3">
+      <c r="Y61" s="3">
         <v>579400</v>
       </c>
     </row>
-    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>173200</v>
+        <v>4000</v>
       </c>
       <c r="E62" s="3">
-        <v>183700</v>
+        <v>3800</v>
       </c>
       <c r="F62" s="3">
-        <v>200800</v>
+        <v>2500</v>
       </c>
       <c r="G62" s="3">
-        <v>255900</v>
+        <v>2500</v>
       </c>
       <c r="H62" s="3">
-        <v>253300</v>
+        <v>4900</v>
       </c>
       <c r="I62" s="3">
+        <v>5100</v>
+      </c>
+      <c r="J62" s="3">
+        <v>6200</v>
+      </c>
+      <c r="K62" s="3">
         <v>206000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>275600</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>303500</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>332000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>332500</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>295700</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>342800</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>338200</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>459900</v>
       </c>
-      <c r="R62" s="3">
+      <c r="T62" s="3">
         <v>459600</v>
       </c>
-      <c r="S62" s="3">
+      <c r="U62" s="3">
         <v>456900</v>
       </c>
-      <c r="T62" s="3">
+      <c r="V62" s="3">
         <v>416100</v>
       </c>
-      <c r="U62" s="3">
+      <c r="W62" s="3">
         <v>400400</v>
       </c>
-      <c r="V62" s="3">
+      <c r="X62" s="3">
         <v>421400</v>
       </c>
-      <c r="W62" s="3">
+      <c r="Y62" s="3">
         <v>337100</v>
       </c>
     </row>
-    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3991,8 +4288,14 @@
       <c r="W63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X63" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4056,8 +4359,14 @@
       <c r="W64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X64" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4121,73 +4430,85 @@
       <c r="W65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X65" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>1369900</v>
+        <v>1361700</v>
       </c>
       <c r="E66" s="3">
-        <v>1471000</v>
+        <v>1284000</v>
       </c>
       <c r="F66" s="3">
-        <v>1729500</v>
+        <v>1317300</v>
       </c>
       <c r="G66" s="3">
-        <v>1957800</v>
+        <v>1328500</v>
       </c>
       <c r="H66" s="3">
-        <v>2141500</v>
+        <v>1366800</v>
       </c>
       <c r="I66" s="3">
+        <v>1423300</v>
+      </c>
+      <c r="J66" s="3">
+        <v>1629300</v>
+      </c>
+      <c r="K66" s="3">
         <v>2114000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>1986700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>1906300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>1840100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>1840100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>1542500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>1643200</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>1642000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>1872200</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>1900600</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>1865900</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>1990400</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>2016500</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>1959400</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>1954100</v>
       </c>
     </row>
-    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4211,8 +4532,10 @@
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
-    </row>
-    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X67" s="3"/>
+      <c r="Y67" s="3"/>
+    </row>
+    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4276,8 +4599,14 @@
       <c r="W68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X68" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4341,8 +4670,14 @@
       <c r="W69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X69" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4406,8 +4741,14 @@
       <c r="W70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4471,73 +4812,85 @@
       <c r="W71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X71" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>964500</v>
+        <v>851100</v>
       </c>
       <c r="E72" s="3">
-        <v>897500</v>
+        <v>802500</v>
       </c>
       <c r="F72" s="3">
-        <v>871300</v>
+        <v>786800</v>
       </c>
       <c r="G72" s="3">
-        <v>914600</v>
+        <v>793500</v>
       </c>
       <c r="H72" s="3">
-        <v>1436900</v>
+        <v>678500</v>
       </c>
       <c r="I72" s="3">
+        <v>706600</v>
+      </c>
+      <c r="J72" s="3">
+        <v>634600</v>
+      </c>
+      <c r="K72" s="3">
         <v>1289900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>1219000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>1146300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>1110200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>1060900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>1142700</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>1084500</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>1151000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>1091000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>1068500</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>734000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>658700</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>474800</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>542500</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>686000</v>
       </c>
     </row>
-    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4601,8 +4954,14 @@
       <c r="W73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X73" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4666,8 +5025,14 @@
       <c r="W74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X74" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4731,73 +5096,85 @@
       <c r="W75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X75" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>1624500</v>
+        <v>1600300</v>
       </c>
       <c r="E76" s="3">
-        <v>1586400</v>
+        <v>1509000</v>
       </c>
       <c r="F76" s="3">
-        <v>1560200</v>
+        <v>1563600</v>
       </c>
       <c r="G76" s="3">
-        <v>1602200</v>
+        <v>1576900</v>
       </c>
       <c r="H76" s="3">
-        <v>2124500</v>
+        <v>1475400</v>
       </c>
       <c r="I76" s="3">
+        <v>1536400</v>
+      </c>
+      <c r="J76" s="3">
+        <v>1471000</v>
+      </c>
+      <c r="K76" s="3">
         <v>1977500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>1906600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>1814500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>1773000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>1709800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>1761300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>1722500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>1864300</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>1831200</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>1759300</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>1378200</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>1340800</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>1156900</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>1231200</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>1374700</v>
       </c>
     </row>
-    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4861,143 +5238,161 @@
       <c r="W77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X77" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="F80" s="2">
+      <c r="I80" s="2">
+        <v>45107</v>
+      </c>
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
-        <v>44834</v>
-      </c>
-      <c r="H80" s="2">
-        <v>44651</v>
-      </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44469</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44286</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44104</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>43921</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>43738</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>43555</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>43373</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>43190</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>43008</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>42825</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>42643</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>42460</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>42277</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>42094</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>41912</v>
       </c>
     </row>
-    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D81" s="3">
-        <v>112800</v>
-      </c>
-      <c r="E81" s="3">
+      <c r="D81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K81" s="3">
         <v>133800</v>
       </c>
-      <c r="F81" s="3">
-        <v>90500</v>
-      </c>
-      <c r="G81" s="3">
-        <v>158800</v>
-      </c>
-      <c r="H81" s="3">
-        <v>175800</v>
-      </c>
-      <c r="I81" s="3">
-        <v>133800</v>
-      </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>157500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>169600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>144500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>162500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>118300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>98800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>192300</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>175500</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>166400</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>160100</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>148700</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>63900</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>-50000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>89500</v>
       </c>
     </row>
-    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5021,73 +5416,81 @@
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
       <c r="W82" s="3"/>
-    </row>
-    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X82" s="3"/>
+      <c r="Y82" s="3"/>
+    </row>
+    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>61700</v>
+        <v>17700</v>
       </c>
       <c r="E83" s="3">
-        <v>61700</v>
-      </c>
-      <c r="F83" s="3">
-        <v>63000</v>
-      </c>
-      <c r="G83" s="3">
-        <v>61700</v>
+        <v>18400</v>
+      </c>
+      <c r="F83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G83" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="H83" s="3">
-        <v>51200</v>
+        <v>16200</v>
       </c>
       <c r="I83" s="3">
+        <v>17600</v>
+      </c>
+      <c r="J83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K83" s="3">
         <v>80000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="L83" s="3">
         <v>114200</v>
       </c>
-      <c r="K83" s="3">
+      <c r="M83" s="3">
         <v>112200</v>
       </c>
-      <c r="L83" s="3">
+      <c r="N83" s="3">
         <v>95000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="O83" s="3">
         <v>120400</v>
       </c>
-      <c r="N83" s="3">
+      <c r="P83" s="3">
         <v>91100</v>
       </c>
-      <c r="O83" s="3">
+      <c r="Q83" s="3">
         <v>91500</v>
       </c>
-      <c r="P83" s="3">
+      <c r="R83" s="3">
         <v>106400</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="S83" s="3">
         <v>107500</v>
       </c>
-      <c r="R83" s="3">
+      <c r="T83" s="3">
         <v>105700</v>
       </c>
-      <c r="S83" s="3">
+      <c r="U83" s="3">
         <v>85000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="V83" s="3">
         <v>78300</v>
       </c>
-      <c r="U83" s="3">
+      <c r="W83" s="3">
         <v>71700</v>
       </c>
-      <c r="V83" s="3">
+      <c r="X83" s="3">
         <v>76400</v>
       </c>
-      <c r="W83" s="3">
+      <c r="Y83" s="3">
         <v>67200</v>
       </c>
     </row>
-    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5151,8 +5554,14 @@
       <c r="W84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X84" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5216,8 +5625,14 @@
       <c r="W85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X85" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5281,8 +5696,14 @@
       <c r="W86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X86" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5346,8 +5767,14 @@
       <c r="W87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X87" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5411,73 +5838,85 @@
       <c r="W88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X88" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>160100</v>
+        <v>70400</v>
       </c>
       <c r="E89" s="3">
-        <v>112800</v>
-      </c>
-      <c r="F89" s="3">
-        <v>36700</v>
-      </c>
-      <c r="G89" s="3">
-        <v>49900</v>
+        <v>66300</v>
+      </c>
+      <c r="F89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G89" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="H89" s="3">
-        <v>-99700</v>
+        <v>52500</v>
       </c>
       <c r="I89" s="3">
+        <v>54600</v>
+      </c>
+      <c r="J89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K89" s="3">
         <v>234900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>162700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>312400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>196400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>285400</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>140800</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>257400</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>105000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>295800</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>130800</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>245100</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>19600</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>225600</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>72400</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Y89" s="3">
         <v>163300</v>
       </c>
     </row>
-    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5501,73 +5940,81 @@
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
       <c r="W90" s="3"/>
-    </row>
-    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X90" s="3"/>
+      <c r="Y90" s="3"/>
+    </row>
+    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-64000</v>
+        <v>-31500</v>
       </c>
       <c r="E91" s="3">
-        <v>-46000</v>
-      </c>
-      <c r="F91" s="3">
-        <v>-45000</v>
-      </c>
-      <c r="G91" s="3">
-        <v>-33000</v>
+        <v>-29700</v>
+      </c>
+      <c r="F91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G91" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="H91" s="3">
-        <v>-81000</v>
+        <v>-25600</v>
       </c>
       <c r="I91" s="3">
+        <v>-26700</v>
+      </c>
+      <c r="J91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K91" s="3">
         <v>-67000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-83000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-69000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-94000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-73000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="P91" s="3">
         <v>-67400</v>
       </c>
-      <c r="O91" s="3">
+      <c r="Q91" s="3">
         <v>-56100</v>
       </c>
-      <c r="P91" s="3">
+      <c r="R91" s="3">
         <v>-81800</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="S91" s="3">
         <v>-72200</v>
       </c>
-      <c r="R91" s="3">
+      <c r="T91" s="3">
         <v>-76600</v>
       </c>
-      <c r="S91" s="3">
+      <c r="U91" s="3">
         <v>-85000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="V91" s="3">
         <v>-133000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="W91" s="3">
         <v>-100400</v>
       </c>
-      <c r="V91" s="3">
+      <c r="X91" s="3">
         <v>-216000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="Y91" s="3">
         <v>-192300</v>
       </c>
     </row>
-    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5631,8 +6078,14 @@
       <c r="W92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X92" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5696,73 +6149,85 @@
       <c r="W93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X93" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-10500</v>
+        <v>160200</v>
       </c>
       <c r="E94" s="3">
-        <v>-15700</v>
-      </c>
-      <c r="F94" s="3">
-        <v>21000</v>
-      </c>
-      <c r="G94" s="3">
-        <v>1074700</v>
+        <v>151000</v>
+      </c>
+      <c r="F94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G94" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="H94" s="3">
-        <v>-94500</v>
+        <v>-7300</v>
       </c>
       <c r="I94" s="3">
+        <v>-7600</v>
+      </c>
+      <c r="J94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K94" s="3">
         <v>-53800</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-190300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-76500</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-106500</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-55800</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>-95800</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>-36600</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>-83200</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>-58000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="T94" s="3">
         <v>-87200</v>
       </c>
-      <c r="S94" s="3">
+      <c r="U94" s="3">
         <v>-59100</v>
       </c>
-      <c r="T94" s="3">
+      <c r="V94" s="3">
         <v>183900</v>
       </c>
-      <c r="U94" s="3">
+      <c r="W94" s="3">
         <v>-71700</v>
       </c>
-      <c r="V94" s="3">
+      <c r="X94" s="3">
         <v>-108000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="Y94" s="3">
         <v>-108000</v>
       </c>
     </row>
-    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5786,73 +6251,81 @@
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
       <c r="W95" s="3"/>
-    </row>
-    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X95" s="3"/>
+      <c r="Y95" s="3"/>
+    </row>
+    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-31500</v>
+        <v>34200</v>
       </c>
       <c r="E96" s="3">
-        <v>-68200</v>
-      </c>
-      <c r="F96" s="3">
-        <v>-28900</v>
-      </c>
-      <c r="G96" s="3">
-        <v>-719100</v>
+        <v>32200</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="H96" s="3">
-        <v>-55100</v>
+        <v>31700</v>
       </c>
       <c r="I96" s="3">
+        <v>33000</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K96" s="3">
         <v>-133800</v>
       </c>
-      <c r="J96" s="3">
+      <c r="L96" s="3">
         <v>-52500</v>
       </c>
-      <c r="K96" s="3">
+      <c r="M96" s="3">
         <v>-123700</v>
       </c>
-      <c r="L96" s="3">
+      <c r="N96" s="3">
         <v>-50700</v>
       </c>
-      <c r="M96" s="3">
+      <c r="O96" s="3">
         <v>-120400</v>
       </c>
-      <c r="N96" s="3">
+      <c r="P96" s="3">
         <v>-47300</v>
       </c>
-      <c r="O96" s="3">
+      <c r="Q96" s="3">
         <v>-114700</v>
       </c>
-      <c r="P96" s="3">
+      <c r="R96" s="3">
         <v>-53200</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="S96" s="3">
         <v>-130200</v>
       </c>
-      <c r="R96" s="3">
+      <c r="T96" s="3">
         <v>-50200</v>
       </c>
-      <c r="S96" s="3">
+      <c r="U96" s="3">
         <v>-113300</v>
       </c>
-      <c r="T96" s="3">
+      <c r="V96" s="3">
         <v>-49600</v>
       </c>
-      <c r="U96" s="3">
+      <c r="W96" s="3">
         <v>-120000</v>
       </c>
-      <c r="V96" s="3">
+      <c r="X96" s="3">
         <v>-50000</v>
       </c>
-      <c r="W96" s="3">
+      <c r="Y96" s="3">
         <v>-121100</v>
       </c>
     </row>
-    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5916,8 +6389,14 @@
       <c r="W97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X97" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5981,8 +6460,14 @@
       <c r="W98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X98" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6046,199 +6531,223 @@
       <c r="W99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X99" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-73500</v>
+        <v>-103200</v>
       </c>
       <c r="E100" s="3">
-        <v>-208600</v>
-      </c>
-      <c r="F100" s="3">
-        <v>-49900</v>
-      </c>
-      <c r="G100" s="3">
-        <v>-734800</v>
+        <v>-97300</v>
+      </c>
+      <c r="F100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G100" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="H100" s="3">
-        <v>-165300</v>
+        <v>-97000</v>
       </c>
       <c r="I100" s="3">
+        <v>-101000</v>
+      </c>
+      <c r="J100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K100" s="3">
         <v>-158800</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>-82700</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>43400</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>-188800</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>-153900</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>-46100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>-123200</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>-80500</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>-244800</v>
       </c>
-      <c r="R100" s="3">
+      <c r="T100" s="3">
         <v>-93800</v>
       </c>
-      <c r="S100" s="3">
+      <c r="U100" s="3">
         <v>-247600</v>
       </c>
-      <c r="T100" s="3">
+      <c r="V100" s="3">
         <v>-116100</v>
       </c>
-      <c r="U100" s="3">
+      <c r="W100" s="3">
         <v>-100400</v>
       </c>
-      <c r="V100" s="3">
+      <c r="X100" s="3">
         <v>-151400</v>
       </c>
-      <c r="W100" s="3">
+      <c r="Y100" s="3">
         <v>-92200</v>
       </c>
     </row>
-    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>-15700</v>
+        <v>600</v>
       </c>
       <c r="E101" s="3">
-        <v>1300</v>
-      </c>
-      <c r="F101" s="3">
-        <v>-61700</v>
-      </c>
-      <c r="G101" s="3">
-        <v>120700</v>
+        <v>600</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="H101" s="3">
+        <v>51300</v>
+      </c>
+      <c r="I101" s="3">
+        <v>55900</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K101" s="3">
+        <v>10500</v>
+      </c>
+      <c r="L101" s="3">
+        <v>-38100</v>
+      </c>
+      <c r="M101" s="3">
+        <v>-7700</v>
+      </c>
+      <c r="N101" s="3">
+        <v>-15200</v>
+      </c>
+      <c r="O101" s="3">
+        <v>18600</v>
+      </c>
+      <c r="P101" s="3">
+        <v>2400</v>
+      </c>
+      <c r="Q101" s="3">
+        <v>17100</v>
+      </c>
+      <c r="R101" s="3">
+        <v>-12300</v>
+      </c>
+      <c r="S101" s="3">
+        <v>-19800</v>
+      </c>
+      <c r="T101" s="3">
+        <v>13200</v>
+      </c>
+      <c r="U101" s="3">
+        <v>27100</v>
+      </c>
+      <c r="V101" s="3">
+        <v>20900</v>
+      </c>
+      <c r="W101" s="3">
+        <v>-2600</v>
+      </c>
+      <c r="X101" s="3">
+        <v>18400</v>
+      </c>
+      <c r="Y101" s="3">
         <v>6600</v>
       </c>
-      <c r="I101" s="3">
-        <v>10500</v>
-      </c>
-      <c r="J101" s="3">
-        <v>-38100</v>
-      </c>
-      <c r="K101" s="3">
-        <v>-7700</v>
-      </c>
-      <c r="L101" s="3">
-        <v>-15200</v>
-      </c>
-      <c r="M101" s="3">
-        <v>18600</v>
-      </c>
-      <c r="N101" s="3">
-        <v>2400</v>
-      </c>
-      <c r="O101" s="3">
-        <v>17100</v>
-      </c>
-      <c r="P101" s="3">
-        <v>-12300</v>
-      </c>
-      <c r="Q101" s="3">
-        <v>-19800</v>
-      </c>
-      <c r="R101" s="3">
-        <v>13200</v>
-      </c>
-      <c r="S101" s="3">
-        <v>27100</v>
-      </c>
-      <c r="T101" s="3">
-        <v>20900</v>
-      </c>
-      <c r="U101" s="3">
-        <v>-2600</v>
-      </c>
-      <c r="V101" s="3">
-        <v>18400</v>
-      </c>
-      <c r="W101" s="3">
-        <v>6600</v>
-      </c>
-    </row>
-    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
+    </row>
+    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>60400</v>
+        <v>105200</v>
       </c>
       <c r="E102" s="3">
-        <v>-110200</v>
+        <v>99200</v>
       </c>
       <c r="F102" s="3">
-        <v>-53800</v>
+        <v>0</v>
       </c>
       <c r="G102" s="3">
-        <v>510400</v>
+        <v>0</v>
       </c>
       <c r="H102" s="3">
-        <v>-353000</v>
+        <v>-51300</v>
       </c>
       <c r="I102" s="3">
+        <v>-53400</v>
+      </c>
+      <c r="J102" s="3">
+        <v>0</v>
+      </c>
+      <c r="K102" s="3">
         <v>32800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-148300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>271600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>-114100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>94300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>1200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>114700</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>-70900</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>-26900</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>-37000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>-34500</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>108300</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>50900</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>-168500</v>
       </c>
-      <c r="W102" s="3">
+      <c r="Y102" s="3">
         <v>-30300</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/TATYY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/TATYY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="333" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="387" uniqueCount="92">
   <si>
     <t>TATYY</t>
   </si>
@@ -656,19 +656,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Y102"/>
+  <dimension ref="A5:AA102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
@@ -683,91 +682,99 @@
     <col min="23" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="25" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="16384" width="9.140625" style="1"/>
+    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44469</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44286</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44104</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>43921</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>43738</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>43555</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>43373</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>43190</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>43008</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>42825</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>42643</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>42460</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>42277</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>42094</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>41912</v>
       </c>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -792,53 +799,59 @@
       <c r="J8" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K8" s="3">
+      <c r="K8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M8" s="3">
         <v>860800</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>812300</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>754900</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>1781800</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>1831400</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>1622900</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>1687100</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>1789300</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>1978300</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>1891400</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>1626900</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>1545600</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>1526000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Z8" s="3">
         <v>1502500</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AA8" s="3">
         <v>1580100</v>
       </c>
     </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -908,8 +921,14 @@
       <c r="Y9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -979,8 +998,14 @@
       <c r="Y10" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1006,8 +1031,10 @@
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
-    </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z11" s="3"/>
+      <c r="AA11" s="3"/>
+    </row>
+    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1077,8 +1104,14 @@
       <c r="Y12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1148,8 +1181,14 @@
       <c r="Y13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1174,21 +1213,21 @@
       <c r="J14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K14" s="3">
+      <c r="K14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M14" s="3">
         <v>77400</v>
       </c>
-      <c r="L14" s="3">
+      <c r="N14" s="3">
         <v>24900</v>
       </c>
-      <c r="M14" s="3">
+      <c r="O14" s="3">
         <v>19100</v>
       </c>
-      <c r="N14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O14" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="P14" s="3" t="s">
         <v>5</v>
       </c>
@@ -1198,20 +1237,20 @@
       <c r="R14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="S14" s="3">
-        <v>0</v>
-      </c>
-      <c r="T14" s="3">
-        <v>0</v>
+      <c r="S14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="U14" s="3">
         <v>0</v>
       </c>
-      <c r="V14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W14" s="3" t="s">
-        <v>5</v>
+      <c r="V14" s="3">
+        <v>0</v>
+      </c>
+      <c r="W14" s="3">
+        <v>0</v>
       </c>
       <c r="X14" s="3" t="s">
         <v>5</v>
@@ -1219,8 +1258,14 @@
       <c r="Y14" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA14" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1245,21 +1290,21 @@
       <c r="J15" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K15" s="3">
+      <c r="K15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M15" s="3">
         <v>6600</v>
       </c>
-      <c r="L15" s="3">
+      <c r="N15" s="3">
         <v>27600</v>
       </c>
-      <c r="M15" s="3">
+      <c r="O15" s="3">
         <v>6400</v>
       </c>
-      <c r="N15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O15" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="P15" s="3" t="s">
         <v>5</v>
       </c>
@@ -1269,20 +1314,20 @@
       <c r="R15" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="S15" s="3">
-        <v>0</v>
-      </c>
-      <c r="T15" s="3">
-        <v>0</v>
+      <c r="S15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T15" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="U15" s="3">
         <v>0</v>
       </c>
-      <c r="V15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W15" s="3" t="s">
-        <v>5</v>
+      <c r="V15" s="3">
+        <v>0</v>
+      </c>
+      <c r="W15" s="3">
+        <v>0</v>
       </c>
       <c r="X15" s="3" t="s">
         <v>5</v>
@@ -1290,8 +1335,14 @@
       <c r="Y15" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA15" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1314,8 +1365,10 @@
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
-    </row>
-    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z16" s="3"/>
+      <c r="AA16" s="3"/>
+    </row>
+    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1340,53 +1393,59 @@
       <c r="J17" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K17" s="3">
+      <c r="K17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M17" s="3">
         <v>817500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>753200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>664300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>1617100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>1625400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>1477400</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>1549300</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>1618800</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>1744800</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>1747400</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>1474200</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>1472600</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>1433400</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>1548500</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>1490600</v>
       </c>
     </row>
-    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1411,53 +1470,59 @@
       <c r="J18" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K18" s="3">
+      <c r="K18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M18" s="3">
         <v>43300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>59000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>90500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>164700</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>206000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>145500</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>137800</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>170500</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>233500</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>144000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>152700</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>73000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>92600</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>-46100</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AA18" s="3">
         <v>89500</v>
       </c>
     </row>
-    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1483,8 +1548,10 @@
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
-    </row>
-    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z19" s="3"/>
+      <c r="AA19" s="3"/>
+    </row>
+    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1509,53 +1576,59 @@
       <c r="J20" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K20" s="3">
+      <c r="K20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M20" s="3">
         <v>-15700</v>
       </c>
-      <c r="L20" s="3">
+      <c r="N20" s="3">
         <v>-17100</v>
       </c>
-      <c r="M20" s="3">
+      <c r="O20" s="3">
         <v>-16600</v>
       </c>
-      <c r="N20" s="3">
+      <c r="P20" s="3">
         <v>2500</v>
       </c>
-      <c r="O20" s="3">
+      <c r="Q20" s="3">
         <v>-2500</v>
       </c>
-      <c r="P20" s="3">
+      <c r="R20" s="3">
         <v>4700</v>
       </c>
-      <c r="Q20" s="3">
-        <v>0</v>
-      </c>
-      <c r="R20" s="3">
-        <v>0</v>
-      </c>
       <c r="S20" s="3">
+        <v>0</v>
+      </c>
+      <c r="T20" s="3">
+        <v>0</v>
+      </c>
+      <c r="U20" s="3">
         <v>-5700</v>
       </c>
-      <c r="T20" s="3">
+      <c r="V20" s="3">
         <v>-5300</v>
       </c>
-      <c r="U20" s="3">
+      <c r="W20" s="3">
         <v>4900</v>
       </c>
-      <c r="V20" s="3">
+      <c r="X20" s="3">
         <v>17000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="Y20" s="3">
         <v>11700</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Z20" s="3">
         <v>10500</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="AA20" s="3">
         <v>10500</v>
       </c>
     </row>
-    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1580,53 +1653,59 @@
       <c r="J21" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K21" s="3">
+      <c r="K21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M21" s="3">
         <v>107600</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>156200</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>186200</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>262300</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>323800</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>241300</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>229300</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>276800</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>335400</v>
       </c>
-      <c r="T21" s="3">
+      <c r="V21" s="3">
         <v>244300</v>
       </c>
-      <c r="U21" s="3">
+      <c r="W21" s="3">
         <v>242600</v>
       </c>
-      <c r="V21" s="3">
+      <c r="X21" s="3">
         <v>168300</v>
       </c>
-      <c r="W21" s="3">
+      <c r="Y21" s="3">
         <v>176100</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Z21" s="3">
         <v>40800</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="AA21" s="3">
         <v>167200</v>
       </c>
     </row>
-    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1651,11 +1730,11 @@
       <c r="J22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K22" s="3">
-        <v>0</v>
-      </c>
-      <c r="L22" s="3">
-        <v>0</v>
+      <c r="K22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L22" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M22" s="3">
         <v>0</v>
@@ -1666,11 +1745,11 @@
       <c r="O22" s="3">
         <v>0</v>
       </c>
-      <c r="P22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q22" s="3" t="s">
-        <v>5</v>
+      <c r="P22" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="3">
+        <v>0</v>
       </c>
       <c r="R22" s="3" t="s">
         <v>5</v>
@@ -1684,20 +1763,26 @@
       <c r="U22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="V22" s="3">
+      <c r="V22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X22" s="3">
         <v>17000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="Y22" s="3">
         <v>13000</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Z22" s="3">
         <v>14500</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="AA22" s="3">
         <v>17100</v>
       </c>
     </row>
-    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1722,53 +1807,59 @@
       <c r="J23" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K23" s="3">
+      <c r="K23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M23" s="3">
         <v>27600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>42000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>74000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>167300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>203500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>150200</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>137800</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>170500</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>227800</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>138700</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>157600</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>73000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>91300</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>-50000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>83000</v>
       </c>
     </row>
-    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1793,53 +1884,59 @@
       <c r="J24" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K24" s="3">
+      <c r="K24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M24" s="3">
         <v>17100</v>
       </c>
-      <c r="L24" s="3">
+      <c r="N24" s="3">
         <v>-3900</v>
       </c>
-      <c r="M24" s="3">
+      <c r="O24" s="3">
         <v>20400</v>
       </c>
-      <c r="N24" s="3">
+      <c r="P24" s="3">
         <v>22800</v>
       </c>
-      <c r="O24" s="3">
+      <c r="Q24" s="3">
         <v>40900</v>
       </c>
-      <c r="P24" s="3">
+      <c r="R24" s="3">
         <v>31900</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="S24" s="3">
         <v>39000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="T24" s="3">
         <v>-19100</v>
       </c>
-      <c r="S24" s="3">
+      <c r="U24" s="3">
         <v>52400</v>
       </c>
-      <c r="T24" s="3">
+      <c r="V24" s="3">
         <v>-27700</v>
       </c>
-      <c r="U24" s="3">
+      <c r="W24" s="3">
         <v>-1200</v>
       </c>
-      <c r="V24" s="3">
+      <c r="X24" s="3">
         <v>2600</v>
       </c>
-      <c r="W24" s="3">
+      <c r="Y24" s="3">
         <v>3900</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Z24" s="3">
         <v>13200</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="AA24" s="3">
         <v>14500</v>
       </c>
     </row>
-    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1909,8 +2006,14 @@
       <c r="Y25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -1935,53 +2038,59 @@
       <c r="J26" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K26" s="3">
+      <c r="K26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M26" s="3">
         <v>10500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>45900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>53600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>144500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>162500</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>118300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>98800</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>189600</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>175500</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>166400</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>158900</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>70400</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>87400</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>-63200</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>68500</v>
       </c>
     </row>
-    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -2006,53 +2115,59 @@
       <c r="J27" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K27" s="3">
+      <c r="K27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M27" s="3">
         <v>10500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>45900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>53600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>144500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>162500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>118300</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>98800</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>189600</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>175500</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>166400</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>158900</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>70400</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>87400</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>-63200</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>68500</v>
       </c>
     </row>
-    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2122,8 +2237,14 @@
       <c r="Y28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2148,53 +2269,59 @@
       <c r="J29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K29" s="3">
+      <c r="K29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M29" s="3">
         <v>123300</v>
       </c>
-      <c r="L29" s="3">
+      <c r="N29" s="3">
         <v>111500</v>
       </c>
-      <c r="M29" s="3">
+      <c r="O29" s="3">
         <v>116000</v>
       </c>
-      <c r="N29" s="3">
-        <v>0</v>
-      </c>
-      <c r="O29" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="P29" s="3">
         <v>0</v>
       </c>
-      <c r="Q29" s="3">
-        <v>0</v>
+      <c r="Q29" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="R29" s="3">
+        <v>0</v>
+      </c>
+      <c r="S29" s="3">
+        <v>0</v>
+      </c>
+      <c r="T29" s="3">
         <v>2700</v>
       </c>
-      <c r="S29" s="3">
-        <v>0</v>
-      </c>
-      <c r="T29" s="3">
-        <v>0</v>
-      </c>
       <c r="U29" s="3">
+        <v>0</v>
+      </c>
+      <c r="V29" s="3">
+        <v>0</v>
+      </c>
+      <c r="W29" s="3">
         <v>1200</v>
       </c>
-      <c r="V29" s="3">
+      <c r="X29" s="3">
         <v>78300</v>
       </c>
-      <c r="W29" s="3">
+      <c r="Y29" s="3">
         <v>-23500</v>
       </c>
-      <c r="X29" s="3">
+      <c r="Z29" s="3">
         <v>13200</v>
       </c>
-      <c r="Y29" s="3">
+      <c r="AA29" s="3">
         <v>21100</v>
       </c>
     </row>
-    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2264,8 +2391,14 @@
       <c r="Y30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2335,8 +2468,14 @@
       <c r="Y31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2361,53 +2500,59 @@
       <c r="J32" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K32" s="3">
+      <c r="K32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M32" s="3">
         <v>15700</v>
       </c>
-      <c r="L32" s="3">
+      <c r="N32" s="3">
         <v>17100</v>
       </c>
-      <c r="M32" s="3">
+      <c r="O32" s="3">
         <v>16600</v>
       </c>
-      <c r="N32" s="3">
+      <c r="P32" s="3">
         <v>-2500</v>
       </c>
-      <c r="O32" s="3">
+      <c r="Q32" s="3">
         <v>2500</v>
       </c>
-      <c r="P32" s="3">
+      <c r="R32" s="3">
         <v>-4700</v>
       </c>
-      <c r="Q32" s="3">
-        <v>0</v>
-      </c>
-      <c r="R32" s="3">
-        <v>0</v>
-      </c>
       <c r="S32" s="3">
+        <v>0</v>
+      </c>
+      <c r="T32" s="3">
+        <v>0</v>
+      </c>
+      <c r="U32" s="3">
         <v>5700</v>
       </c>
-      <c r="T32" s="3">
+      <c r="V32" s="3">
         <v>5300</v>
       </c>
-      <c r="U32" s="3">
+      <c r="W32" s="3">
         <v>-4900</v>
       </c>
-      <c r="V32" s="3">
+      <c r="X32" s="3">
         <v>-17000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="Y32" s="3">
         <v>-11700</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Z32" s="3">
         <v>-10500</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="AA32" s="3">
         <v>-10500</v>
       </c>
     </row>
-    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -2432,53 +2577,59 @@
       <c r="J33" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K33" s="3">
+      <c r="K33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M33" s="3">
         <v>133800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>157500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>169600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>144500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>162500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>118300</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>98800</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>192300</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>175500</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>166400</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>160100</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>148700</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>63900</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>-50000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>89500</v>
       </c>
     </row>
-    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2548,8 +2699,14 @@
       <c r="Y34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -2574,129 +2731,141 @@
       <c r="J35" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K35" s="3">
+      <c r="K35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M35" s="3">
         <v>133800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>157500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>169600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>144500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>162500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>118300</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>98800</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>192300</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>175500</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>166400</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>160100</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>148700</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>63900</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>-50000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>89500</v>
       </c>
     </row>
-    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44469</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44286</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44104</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>43921</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>43738</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>43555</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>43373</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>43190</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>43008</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>42825</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>42643</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>42460</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>42277</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>42094</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>41912</v>
       </c>
     </row>
-    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2722,8 +2891,10 @@
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
-    </row>
-    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z39" s="3"/>
+      <c r="AA39" s="3"/>
+    </row>
+    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2749,79 +2920,87 @@
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
-    </row>
-    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z40" s="3"/>
+      <c r="AA40" s="3"/>
+    </row>
+    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>431500</v>
+      </c>
+      <c r="E41" s="3">
+        <v>418100</v>
+      </c>
+      <c r="F41" s="3">
         <v>796100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>750700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>551900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>556600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>477100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>496900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>587600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>505200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>486800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>617100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>343400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>447900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>337100</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>346500</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>259100</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>342500</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>344700</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>355900</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>413500</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>305200</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Z41" s="3">
         <v>256800</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="AA41" s="3">
         <v>425300</v>
       </c>
     </row>
-    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2850,199 +3029,217 @@
         <v>0</v>
       </c>
       <c r="L42" s="3">
+        <v>0</v>
+      </c>
+      <c r="M42" s="3">
+        <v>0</v>
+      </c>
+      <c r="N42" s="3">
         <v>42000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="O42" s="3">
         <v>48500</v>
       </c>
-      <c r="N42" s="3">
+      <c r="P42" s="3">
         <v>84900</v>
       </c>
-      <c r="O42" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P42" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q42" s="3">
-        <v>0</v>
+      <c r="Q42" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="R42" s="3" t="s">
         <v>5</v>
       </c>
       <c r="S42" s="3">
+        <v>0</v>
+      </c>
+      <c r="T42" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U42" s="3">
         <v>1400</v>
       </c>
-      <c r="T42" s="3">
-        <v>0</v>
-      </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
+        <v>0</v>
+      </c>
+      <c r="W42" s="3">
         <v>4900</v>
       </c>
-      <c r="V42" s="3">
+      <c r="X42" s="3">
         <v>5200</v>
       </c>
-      <c r="W42" s="3">
+      <c r="Y42" s="3">
         <v>7800</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Z42" s="3">
         <v>23700</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="AA42" s="3">
         <v>2600</v>
       </c>
     </row>
-    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>484500</v>
+      </c>
+      <c r="E43" s="3">
+        <v>469500</v>
+      </c>
+      <c r="F43" s="3">
         <v>372600</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>351300</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>354900</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>357900</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>369800</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>385100</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>425600</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>343800</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>433000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>406800</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>422000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>397100</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>389200</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>425700</v>
       </c>
-      <c r="R43" s="3">
+      <c r="T43" s="3">
         <v>402300</v>
       </c>
-      <c r="S43" s="3">
+      <c r="U43" s="3">
         <v>450000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="V43" s="3">
         <v>385700</v>
       </c>
-      <c r="U43" s="3">
+      <c r="W43" s="3">
         <v>374400</v>
       </c>
-      <c r="V43" s="3">
+      <c r="X43" s="3">
         <v>396500</v>
       </c>
-      <c r="W43" s="3">
+      <c r="Y43" s="3">
         <v>363900</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Z43" s="3">
         <v>384500</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="AA43" s="3">
         <v>495100</v>
       </c>
     </row>
-    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>750700</v>
+      </c>
+      <c r="E44" s="3">
+        <v>727400</v>
+      </c>
+      <c r="F44" s="3">
         <v>434300</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>409500</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>445800</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>449600</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>499100</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>519800</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>551800</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>345100</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>698100</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>498600</v>
       </c>
-      <c r="N44" s="3">
+      <c r="P44" s="3">
         <v>577900</v>
       </c>
-      <c r="O44" s="3">
+      <c r="Q44" s="3">
         <v>512500</v>
       </c>
-      <c r="P44" s="3">
+      <c r="R44" s="3">
         <v>513400</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="S44" s="3">
         <v>508700</v>
       </c>
-      <c r="R44" s="3">
+      <c r="T44" s="3">
         <v>571400</v>
       </c>
-      <c r="S44" s="3">
+      <c r="U44" s="3">
         <v>537700</v>
       </c>
-      <c r="T44" s="3">
+      <c r="V44" s="3">
         <v>582500</v>
       </c>
-      <c r="U44" s="3">
+      <c r="W44" s="3">
         <v>449500</v>
       </c>
-      <c r="V44" s="3">
+      <c r="X44" s="3">
         <v>507400</v>
       </c>
-      <c r="W44" s="3">
+      <c r="Y44" s="3">
         <v>443500</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Z44" s="3">
         <v>478000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="AA44" s="3">
         <v>331800</v>
       </c>
     </row>
-    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E45" s="3" t="s">
-        <v>5</v>
+      <c r="D45" s="3">
+        <v>5200</v>
+      </c>
+      <c r="E45" s="3">
+        <v>5000</v>
       </c>
       <c r="F45" s="3" t="s">
         <v>5</v>
@@ -3050,133 +3247,145 @@
       <c r="G45" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H45" s="3">
+      <c r="H45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J45" s="3">
         <v>1200</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>1300</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>3700</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>1804300</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>48600</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>11500</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>6300</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>44700</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>56800</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>46400</v>
       </c>
-      <c r="R45" s="3">
+      <c r="T45" s="3">
         <v>32700</v>
       </c>
-      <c r="S45" s="3">
+      <c r="U45" s="3">
         <v>55200</v>
       </c>
-      <c r="T45" s="3">
+      <c r="V45" s="3">
         <v>40900</v>
       </c>
-      <c r="U45" s="3">
+      <c r="W45" s="3">
         <v>71400</v>
       </c>
-      <c r="V45" s="3">
+      <c r="X45" s="3">
         <v>65200</v>
       </c>
-      <c r="W45" s="3">
+      <c r="Y45" s="3">
         <v>348300</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Z45" s="3">
         <v>81600</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="AA45" s="3">
         <v>143500</v>
       </c>
     </row>
-    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1701600</v>
+      </c>
+      <c r="E46" s="3">
+        <v>1648800</v>
+      </c>
+      <c r="F46" s="3">
         <v>1603000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>1511500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>1372900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>1384600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>1347200</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>1403000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>1588500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>2998400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>1708500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>1582400</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>1434600</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>1402100</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>1296500</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>1327300</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>1265600</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>1386800</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>1353800</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>1256200</v>
       </c>
-      <c r="V46" s="3">
+      <c r="X46" s="3">
         <v>1387800</v>
       </c>
-      <c r="W46" s="3">
+      <c r="Y46" s="3">
         <v>1468700</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Z46" s="3">
         <v>1224600</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="AA46" s="3">
         <v>1398400</v>
       </c>
     </row>
-    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3184,212 +3393,230 @@
         <v>36200</v>
       </c>
       <c r="E47" s="3">
+        <v>35100</v>
+      </c>
+      <c r="F47" s="3">
+        <v>36200</v>
+      </c>
+      <c r="G47" s="3">
         <v>34100</v>
       </c>
-      <c r="F47" s="3">
+      <c r="H47" s="3">
         <v>243800</v>
       </c>
-      <c r="G47" s="3">
+      <c r="I47" s="3">
         <v>245800</v>
       </c>
-      <c r="H47" s="3">
+      <c r="J47" s="3">
         <v>290400</v>
       </c>
-      <c r="I47" s="3">
+      <c r="K47" s="3">
         <v>302400</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>298100</v>
       </c>
-      <c r="K47" s="3">
+      <c r="M47" s="3">
         <v>66900</v>
       </c>
-      <c r="L47" s="3">
+      <c r="N47" s="3">
         <v>215200</v>
       </c>
-      <c r="M47" s="3">
+      <c r="O47" s="3">
         <v>209100</v>
       </c>
-      <c r="N47" s="3">
+      <c r="P47" s="3">
         <v>195200</v>
       </c>
-      <c r="O47" s="3">
+      <c r="Q47" s="3">
         <v>198500</v>
       </c>
-      <c r="P47" s="3">
+      <c r="R47" s="3">
         <v>192800</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="S47" s="3">
         <v>158600</v>
       </c>
-      <c r="R47" s="3">
+      <c r="T47" s="3">
         <v>170500</v>
       </c>
-      <c r="S47" s="3">
+      <c r="U47" s="3">
         <v>154200</v>
       </c>
-      <c r="T47" s="3">
+      <c r="V47" s="3">
         <v>167700</v>
       </c>
-      <c r="U47" s="3">
+      <c r="W47" s="3">
         <v>136700</v>
       </c>
-      <c r="V47" s="3">
+      <c r="X47" s="3">
         <v>137000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="Y47" s="3">
         <v>180000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Z47" s="3">
         <v>453000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="AA47" s="3">
         <v>476700</v>
       </c>
     </row>
-    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1839800</v>
+      </c>
+      <c r="E48" s="3">
+        <v>1782700</v>
+      </c>
+      <c r="F48" s="3">
         <v>705000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>664800</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>666900</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>672500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>616300</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>641800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>603700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>559000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>1450000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>2937800</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>1508100</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>1475300</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>1161600</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>1206500</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>1316100</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>1416500</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>1401400</v>
       </c>
-      <c r="U48" s="3">
+      <c r="W48" s="3">
         <v>1272200</v>
       </c>
-      <c r="V48" s="3">
+      <c r="X48" s="3">
         <v>1207800</v>
       </c>
-      <c r="W48" s="3">
+      <c r="Y48" s="3">
         <v>1006900</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Z48" s="3">
         <v>987600</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="AA48" s="3">
         <v>995500</v>
       </c>
     </row>
-    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1028400</v>
+      </c>
+      <c r="E49" s="3">
+        <v>996500</v>
+      </c>
+      <c r="F49" s="3">
         <v>504000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>475200</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>488800</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>492900</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>524700</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>546400</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>533200</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>380500</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>452700</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>406800</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>430900</v>
-      </c>
-      <c r="O49" s="3">
-        <v>431800</v>
-      </c>
-      <c r="P49" s="3">
-        <v>404600</v>
       </c>
       <c r="Q49" s="3">
         <v>431800</v>
       </c>
       <c r="R49" s="3">
+        <v>404600</v>
+      </c>
+      <c r="S49" s="3">
+        <v>431800</v>
+      </c>
+      <c r="T49" s="3">
         <v>491000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="U49" s="3">
         <v>539200</v>
       </c>
-      <c r="T49" s="3">
+      <c r="V49" s="3">
         <v>529600</v>
       </c>
-      <c r="U49" s="3">
+      <c r="W49" s="3">
         <v>511100</v>
       </c>
-      <c r="V49" s="3">
+      <c r="X49" s="3">
         <v>508700</v>
       </c>
-      <c r="W49" s="3">
+      <c r="Y49" s="3">
         <v>403000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Z49" s="3">
         <v>447700</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="AA49" s="3">
         <v>418700</v>
       </c>
     </row>
-    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3459,8 +3686,14 @@
       <c r="Y50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3530,79 +3763,91 @@
       <c r="Y51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>143400</v>
+      </c>
+      <c r="E52" s="3">
+        <v>139000</v>
+      </c>
+      <c r="F52" s="3">
         <v>53600</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>50600</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>50500</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>51000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>45200</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>47000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>35900</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>86600</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>66900</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>53600</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>44400</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>42200</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>248400</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="S52" s="3">
         <v>241500</v>
       </c>
-      <c r="R52" s="3">
+      <c r="T52" s="3">
         <v>263200</v>
       </c>
-      <c r="S52" s="3">
+      <c r="U52" s="3">
         <v>206600</v>
       </c>
-      <c r="T52" s="3">
+      <c r="V52" s="3">
         <v>207400</v>
       </c>
-      <c r="U52" s="3">
+      <c r="W52" s="3">
         <v>67700</v>
       </c>
-      <c r="V52" s="3">
+      <c r="X52" s="3">
         <v>90000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="Y52" s="3">
         <v>114800</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Z52" s="3">
         <v>77700</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="AA52" s="3">
         <v>39500</v>
       </c>
     </row>
-    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3672,79 +3917,91 @@
       <c r="Y53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>4820500</v>
+      </c>
+      <c r="E54" s="3">
+        <v>4670900</v>
+      </c>
+      <c r="F54" s="3">
         <v>2963400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>2794200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>2882100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>2906700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>2843300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>2960900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>3101500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>4091400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>3893300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>3720700</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>3613100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>3549900</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>3303800</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>3365700</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>3506300</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>3703300</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>3659900</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>3244000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>3331200</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>3173400</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>3190600</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AA54" s="3">
         <v>3328800</v>
       </c>
     </row>
-    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3770,8 +4027,10 @@
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
-    </row>
-    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z55" s="3"/>
+      <c r="AA55" s="3"/>
+    </row>
+    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3797,434 +4056,472 @@
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
-    </row>
-    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z56" s="3"/>
+      <c r="AA56" s="3"/>
+    </row>
+    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>301000</v>
+      </c>
+      <c r="E57" s="3">
+        <v>291700</v>
+      </c>
+      <c r="F57" s="3">
         <v>345800</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>326100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>219800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>221600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>329500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>343100</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>309300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>276900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>350400</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>424600</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>468900</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>378400</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>404600</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>431800</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>425500</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>447200</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>416000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="W57" s="3">
         <v>397800</v>
       </c>
-      <c r="V57" s="3">
+      <c r="X57" s="3">
         <v>439600</v>
       </c>
-      <c r="W57" s="3">
+      <c r="Y57" s="3">
         <v>439600</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Z57" s="3">
         <v>416100</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="AA57" s="3">
         <v>425300</v>
       </c>
     </row>
-    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>208000</v>
+      </c>
+      <c r="E58" s="3">
+        <v>201600</v>
+      </c>
+      <c r="F58" s="3">
         <v>22800</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>21500</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>21500</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>21700</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>52500</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>54600</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>149700</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>32800</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>74800</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>107100</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>50700</v>
       </c>
-      <c r="O58" s="3">
+      <c r="Q58" s="3">
         <v>317600</v>
       </c>
-      <c r="P58" s="3">
+      <c r="R58" s="3">
         <v>265000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="S58" s="3">
         <v>29300</v>
       </c>
-      <c r="R58" s="3">
+      <c r="T58" s="3">
         <v>21800</v>
       </c>
-      <c r="S58" s="3">
+      <c r="U58" s="3">
         <v>39600</v>
       </c>
-      <c r="T58" s="3">
+      <c r="V58" s="3">
         <v>116200</v>
       </c>
-      <c r="U58" s="3">
+      <c r="W58" s="3">
         <v>129300</v>
       </c>
-      <c r="V58" s="3">
+      <c r="X58" s="3">
         <v>260900</v>
       </c>
-      <c r="W58" s="3">
+      <c r="Y58" s="3">
         <v>644300</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Z58" s="3">
         <v>401600</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="AA58" s="3">
         <v>468800</v>
       </c>
     </row>
-    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>140800</v>
+      </c>
+      <c r="E59" s="3">
+        <v>136500</v>
+      </c>
+      <c r="F59" s="3">
         <v>105900</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>99800</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>101000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>101900</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>85400</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>89000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>117500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>679700</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>325400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>104600</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>124200</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>143900</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>136000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>135400</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>100900</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>113200</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>110900</v>
       </c>
-      <c r="U59" s="3">
+      <c r="W59" s="3">
         <v>150300</v>
       </c>
-      <c r="V59" s="3">
+      <c r="X59" s="3">
         <v>147400</v>
       </c>
-      <c r="W59" s="3">
+      <c r="Y59" s="3">
         <v>159100</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Z59" s="3">
         <v>109300</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="AA59" s="3">
         <v>142200</v>
       </c>
     </row>
-    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>786800</v>
+      </c>
+      <c r="E60" s="3">
+        <v>762400</v>
+      </c>
+      <c r="F60" s="3">
         <v>474500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>447400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>426900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>430500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>467400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>486700</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>707600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>989400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>730900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>582700</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>643800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>840000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>805600</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>596500</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>548200</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>600000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>643200</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>677400</v>
       </c>
-      <c r="V60" s="3">
+      <c r="X60" s="3">
         <v>847800</v>
       </c>
-      <c r="W60" s="3">
+      <c r="Y60" s="3">
         <v>1243000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Z60" s="3">
         <v>927000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="AA60" s="3">
         <v>1036300</v>
       </c>
     </row>
-    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1479300</v>
+      </c>
+      <c r="E61" s="3">
+        <v>1433500</v>
+      </c>
+      <c r="F61" s="3">
         <v>721100</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>679900</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>723700</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>729900</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>728500</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>758700</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>732400</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>917200</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>978900</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>1020100</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>864300</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>667600</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>441200</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="S61" s="3">
         <v>703900</v>
       </c>
-      <c r="R61" s="3">
+      <c r="T61" s="3">
         <v>755500</v>
       </c>
-      <c r="S61" s="3">
+      <c r="U61" s="3">
         <v>812300</v>
       </c>
-      <c r="T61" s="3">
+      <c r="V61" s="3">
         <v>797800</v>
       </c>
-      <c r="U61" s="3">
+      <c r="W61" s="3">
         <v>731600</v>
       </c>
-      <c r="V61" s="3">
+      <c r="X61" s="3">
         <v>725200</v>
       </c>
-      <c r="W61" s="3">
+      <c r="Y61" s="3">
         <v>371700</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Z61" s="3">
         <v>609700</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="AA61" s="3">
         <v>579400</v>
       </c>
     </row>
-    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>77500</v>
+      </c>
+      <c r="E62" s="3">
+        <v>75100</v>
+      </c>
+      <c r="F62" s="3">
         <v>4000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>3800</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>2500</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>2500</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>4900</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>5100</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>6200</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>206000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>275600</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>303500</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>332000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>332500</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>295700</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>342800</v>
       </c>
-      <c r="R62" s="3">
+      <c r="T62" s="3">
         <v>338200</v>
       </c>
-      <c r="S62" s="3">
+      <c r="U62" s="3">
         <v>459900</v>
       </c>
-      <c r="T62" s="3">
+      <c r="V62" s="3">
         <v>459600</v>
       </c>
-      <c r="U62" s="3">
+      <c r="W62" s="3">
         <v>456900</v>
       </c>
-      <c r="V62" s="3">
+      <c r="X62" s="3">
         <v>416100</v>
       </c>
-      <c r="W62" s="3">
+      <c r="Y62" s="3">
         <v>400400</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Z62" s="3">
         <v>421400</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="AA62" s="3">
         <v>337100</v>
       </c>
     </row>
-    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4294,8 +4591,14 @@
       <c r="Y63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4365,8 +4668,14 @@
       <c r="Y64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4436,79 +4745,91 @@
       <c r="Y65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>2768800</v>
+      </c>
+      <c r="E66" s="3">
+        <v>2682900</v>
+      </c>
+      <c r="F66" s="3">
         <v>1361700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>1284000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>1317300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>1328500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>1366800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>1423300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>1629300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>2114000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>1986700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>1906300</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>1840100</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>1840100</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>1542500</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>1643200</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>1642000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>1872200</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>1900600</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>1865900</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>1990400</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>2016500</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>1959400</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AA66" s="3">
         <v>1954100</v>
       </c>
     </row>
-    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4534,8 +4855,10 @@
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
-    </row>
-    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z67" s="3"/>
+      <c r="AA67" s="3"/>
+    </row>
+    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4605,8 +4928,14 @@
       <c r="Y68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4676,8 +5005,14 @@
       <c r="Y69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4747,8 +5082,14 @@
       <c r="Y70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4818,79 +5159,91 @@
       <c r="Y71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>611100</v>
+      </c>
+      <c r="E72" s="3">
+        <v>592200</v>
+      </c>
+      <c r="F72" s="3">
         <v>851100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>802500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>786800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>793500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>678500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>706600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>634600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>1289900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>1219000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>1146300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>1110200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>1060900</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>1142700</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>1084500</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>1151000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>1091000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>1068500</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>734000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>658700</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>474800</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>542500</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AA72" s="3">
         <v>686000</v>
       </c>
     </row>
-    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4960,8 +5313,14 @@
       <c r="Y73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5031,8 +5390,14 @@
       <c r="Y74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5102,79 +5467,91 @@
       <c r="Y75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>2054300</v>
+      </c>
+      <c r="E76" s="3">
+        <v>1990600</v>
+      </c>
+      <c r="F76" s="3">
         <v>1600300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>1509000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>1563600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>1576900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>1475400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>1536400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>1471000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>1977500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>1906600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>1814500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>1773000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>1709800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>1761300</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>1722500</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>1864300</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>1831200</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>1759300</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>1378200</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>1340800</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>1156900</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>1231200</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AA76" s="3">
         <v>1374700</v>
       </c>
     </row>
-    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5244,84 +5621,96 @@
       <c r="Y77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44469</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44286</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44104</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>43921</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>43738</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>43555</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>43373</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>43190</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>43008</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>42825</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>42643</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>42460</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>42277</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>42094</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>41912</v>
       </c>
     </row>
-    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -5346,53 +5735,59 @@
       <c r="J81" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K81" s="3">
+      <c r="K81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M81" s="3">
         <v>133800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>157500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>169600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>144500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>162500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>118300</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>98800</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>192300</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>175500</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>166400</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>160100</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>148700</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>63900</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>-50000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>89500</v>
       </c>
     </row>
-    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5418,79 +5813,87 @@
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
-    </row>
-    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z82" s="3"/>
+      <c r="AA82" s="3"/>
+    </row>
+    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3">
+      <c r="D83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F83" s="3">
         <v>17700</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>18400</v>
       </c>
-      <c r="F83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H83" s="3">
+      <c r="H83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J83" s="3">
         <v>16200</v>
       </c>
-      <c r="I83" s="3">
+      <c r="K83" s="3">
         <v>17600</v>
       </c>
-      <c r="J83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M83" s="3">
         <v>80000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="N83" s="3">
         <v>114200</v>
       </c>
-      <c r="M83" s="3">
+      <c r="O83" s="3">
         <v>112200</v>
       </c>
-      <c r="N83" s="3">
+      <c r="P83" s="3">
         <v>95000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="Q83" s="3">
         <v>120400</v>
       </c>
-      <c r="P83" s="3">
+      <c r="R83" s="3">
         <v>91100</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="S83" s="3">
         <v>91500</v>
       </c>
-      <c r="R83" s="3">
+      <c r="T83" s="3">
         <v>106400</v>
       </c>
-      <c r="S83" s="3">
+      <c r="U83" s="3">
         <v>107500</v>
       </c>
-      <c r="T83" s="3">
+      <c r="V83" s="3">
         <v>105700</v>
       </c>
-      <c r="U83" s="3">
+      <c r="W83" s="3">
         <v>85000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="X83" s="3">
         <v>78300</v>
       </c>
-      <c r="W83" s="3">
+      <c r="Y83" s="3">
         <v>71700</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Z83" s="3">
         <v>76400</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="AA83" s="3">
         <v>67200</v>
       </c>
     </row>
-    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5560,8 +5963,14 @@
       <c r="Y84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5631,8 +6040,14 @@
       <c r="Y85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5702,8 +6117,14 @@
       <c r="Y86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5773,8 +6194,14 @@
       <c r="Y87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5844,79 +6271,91 @@
       <c r="Y88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3">
+      <c r="D89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F89" s="3">
         <v>70400</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>66300</v>
       </c>
-      <c r="F89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H89" s="3">
+      <c r="H89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J89" s="3">
         <v>52500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>54600</v>
       </c>
-      <c r="J89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M89" s="3">
         <v>234900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>162700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>312400</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>196400</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>285400</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>140800</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>257400</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>105000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>295800</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>130800</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>245100</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>19600</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Y89" s="3">
         <v>225600</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Z89" s="3">
         <v>72400</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="AA89" s="3">
         <v>163300</v>
       </c>
     </row>
-    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5942,79 +6381,87 @@
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
-    </row>
-    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z90" s="3"/>
+      <c r="AA90" s="3"/>
+    </row>
+    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
+      <c r="D91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F91" s="3">
         <v>-31500</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-29700</v>
       </c>
-      <c r="F91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H91" s="3">
+      <c r="H91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J91" s="3">
         <v>-25600</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-26700</v>
       </c>
-      <c r="J91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M91" s="3">
         <v>-67000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-83000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-69000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="P91" s="3">
         <v>-94000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="Q91" s="3">
         <v>-73000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="R91" s="3">
         <v>-67400</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="S91" s="3">
         <v>-56100</v>
       </c>
-      <c r="R91" s="3">
+      <c r="T91" s="3">
         <v>-81800</v>
       </c>
-      <c r="S91" s="3">
+      <c r="U91" s="3">
         <v>-72200</v>
       </c>
-      <c r="T91" s="3">
+      <c r="V91" s="3">
         <v>-76600</v>
       </c>
-      <c r="U91" s="3">
+      <c r="W91" s="3">
         <v>-85000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="X91" s="3">
         <v>-133000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="Y91" s="3">
         <v>-100400</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Z91" s="3">
         <v>-216000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="AA91" s="3">
         <v>-192300</v>
       </c>
     </row>
-    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6084,8 +6531,14 @@
       <c r="Y92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6155,79 +6608,91 @@
       <c r="Y93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3">
+      <c r="D94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F94" s="3">
         <v>160200</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>151000</v>
       </c>
-      <c r="F94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H94" s="3">
+      <c r="H94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J94" s="3">
         <v>-7300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-7600</v>
       </c>
-      <c r="J94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M94" s="3">
         <v>-53800</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-190300</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-76500</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>-106500</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>-55800</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>-95800</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>-36600</v>
       </c>
-      <c r="R94" s="3">
+      <c r="T94" s="3">
         <v>-83200</v>
       </c>
-      <c r="S94" s="3">
+      <c r="U94" s="3">
         <v>-58000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="V94" s="3">
         <v>-87200</v>
       </c>
-      <c r="U94" s="3">
+      <c r="W94" s="3">
         <v>-59100</v>
       </c>
-      <c r="V94" s="3">
+      <c r="X94" s="3">
         <v>183900</v>
       </c>
-      <c r="W94" s="3">
+      <c r="Y94" s="3">
         <v>-71700</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Z94" s="3">
         <v>-108000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="AA94" s="3">
         <v>-108000</v>
       </c>
     </row>
-    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6253,79 +6718,87 @@
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
-    </row>
-    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z95" s="3"/>
+      <c r="AA95" s="3"/>
+    </row>
+    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
+      <c r="D96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F96" s="3">
         <v>34200</v>
       </c>
-      <c r="E96" s="3">
+      <c r="G96" s="3">
         <v>32200</v>
       </c>
-      <c r="F96" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G96" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H96" s="3">
+      <c r="H96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J96" s="3">
         <v>31700</v>
       </c>
-      <c r="I96" s="3">
+      <c r="K96" s="3">
         <v>33000</v>
       </c>
-      <c r="J96" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M96" s="3">
         <v>-133800</v>
       </c>
-      <c r="L96" s="3">
+      <c r="N96" s="3">
         <v>-52500</v>
       </c>
-      <c r="M96" s="3">
+      <c r="O96" s="3">
         <v>-123700</v>
       </c>
-      <c r="N96" s="3">
+      <c r="P96" s="3">
         <v>-50700</v>
       </c>
-      <c r="O96" s="3">
+      <c r="Q96" s="3">
         <v>-120400</v>
       </c>
-      <c r="P96" s="3">
+      <c r="R96" s="3">
         <v>-47300</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="S96" s="3">
         <v>-114700</v>
       </c>
-      <c r="R96" s="3">
+      <c r="T96" s="3">
         <v>-53200</v>
       </c>
-      <c r="S96" s="3">
+      <c r="U96" s="3">
         <v>-130200</v>
       </c>
-      <c r="T96" s="3">
+      <c r="V96" s="3">
         <v>-50200</v>
       </c>
-      <c r="U96" s="3">
+      <c r="W96" s="3">
         <v>-113300</v>
       </c>
-      <c r="V96" s="3">
+      <c r="X96" s="3">
         <v>-49600</v>
       </c>
-      <c r="W96" s="3">
+      <c r="Y96" s="3">
         <v>-120000</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Z96" s="3">
         <v>-50000</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="AA96" s="3">
         <v>-121100</v>
       </c>
     </row>
-    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6395,8 +6868,14 @@
       <c r="Y97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6466,8 +6945,14 @@
       <c r="Y98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6537,217 +7022,241 @@
       <c r="Y99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3">
+      <c r="D100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F100" s="3">
         <v>-103200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>-97300</v>
       </c>
-      <c r="F100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H100" s="3">
+      <c r="H100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J100" s="3">
         <v>-97000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>-101000</v>
       </c>
-      <c r="J100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M100" s="3">
         <v>-158800</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>-82700</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>43400</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>-188800</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>-153900</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>-46100</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>-123200</v>
       </c>
-      <c r="R100" s="3">
+      <c r="T100" s="3">
         <v>-80500</v>
       </c>
-      <c r="S100" s="3">
+      <c r="U100" s="3">
         <v>-244800</v>
       </c>
-      <c r="T100" s="3">
+      <c r="V100" s="3">
         <v>-93800</v>
       </c>
-      <c r="U100" s="3">
+      <c r="W100" s="3">
         <v>-247600</v>
       </c>
-      <c r="V100" s="3">
+      <c r="X100" s="3">
         <v>-116100</v>
       </c>
-      <c r="W100" s="3">
+      <c r="Y100" s="3">
         <v>-100400</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Z100" s="3">
         <v>-151400</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="AA100" s="3">
         <v>-92200</v>
       </c>
     </row>
-    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
+      <c r="D101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F101" s="3">
         <v>600</v>
       </c>
-      <c r="E101" s="3">
+      <c r="G101" s="3">
         <v>600</v>
       </c>
-      <c r="F101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H101" s="3">
+      <c r="H101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J101" s="3">
         <v>51300</v>
       </c>
-      <c r="I101" s="3">
+      <c r="K101" s="3">
         <v>55900</v>
       </c>
-      <c r="J101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M101" s="3">
         <v>10500</v>
       </c>
-      <c r="L101" s="3">
+      <c r="N101" s="3">
         <v>-38100</v>
       </c>
-      <c r="M101" s="3">
+      <c r="O101" s="3">
         <v>-7700</v>
       </c>
-      <c r="N101" s="3">
+      <c r="P101" s="3">
         <v>-15200</v>
       </c>
-      <c r="O101" s="3">
+      <c r="Q101" s="3">
         <v>18600</v>
       </c>
-      <c r="P101" s="3">
+      <c r="R101" s="3">
         <v>2400</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="S101" s="3">
         <v>17100</v>
       </c>
-      <c r="R101" s="3">
+      <c r="T101" s="3">
         <v>-12300</v>
       </c>
-      <c r="S101" s="3">
+      <c r="U101" s="3">
         <v>-19800</v>
       </c>
-      <c r="T101" s="3">
+      <c r="V101" s="3">
         <v>13200</v>
       </c>
-      <c r="U101" s="3">
+      <c r="W101" s="3">
         <v>27100</v>
       </c>
-      <c r="V101" s="3">
+      <c r="X101" s="3">
         <v>20900</v>
       </c>
-      <c r="W101" s="3">
+      <c r="Y101" s="3">
         <v>-2600</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Z101" s="3">
         <v>18400</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="AA101" s="3">
         <v>6600</v>
       </c>
     </row>
-    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>0</v>
+      </c>
+      <c r="E102" s="3">
+        <v>0</v>
+      </c>
+      <c r="F102" s="3">
         <v>105200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>99200</v>
       </c>
-      <c r="F102" s="3">
-        <v>0</v>
-      </c>
-      <c r="G102" s="3">
-        <v>0</v>
-      </c>
       <c r="H102" s="3">
+        <v>0</v>
+      </c>
+      <c r="I102" s="3">
+        <v>0</v>
+      </c>
+      <c r="J102" s="3">
         <v>-51300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-53400</v>
       </c>
-      <c r="J102" s="3">
-        <v>0</v>
-      </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
+        <v>0</v>
+      </c>
+      <c r="M102" s="3">
         <v>32800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>-148300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>271600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>-114100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>94300</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>1200</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>114700</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>-70900</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>-26900</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>-37000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>-34500</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>108300</v>
       </c>
-      <c r="W102" s="3">
+      <c r="Y102" s="3">
         <v>50900</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Z102" s="3">
         <v>-168500</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="AA102" s="3">
         <v>-30300</v>
       </c>
     </row>
